--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,45 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Uruguay Primera División</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Cerro Largo</t>
+  </si>
+  <si>
+    <t>Defensor Sporting</t>
+  </si>
+  <si>
+    <t>Juventud</t>
+  </si>
+  <si>
+    <t>Boston River</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['26', '90+6']</t>
+  </si>
+  <si>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>[]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +309,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +818,418 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7821441</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45688.79166666666</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2">
+        <v>2.4</v>
+      </c>
+      <c r="R2">
+        <v>2.1</v>
+      </c>
+      <c r="S2">
+        <v>5</v>
+      </c>
+      <c r="T2">
+        <v>1.44</v>
+      </c>
+      <c r="U2">
+        <v>2.63</v>
+      </c>
+      <c r="V2">
+        <v>3.25</v>
+      </c>
+      <c r="W2">
+        <v>1.33</v>
+      </c>
+      <c r="X2">
+        <v>10</v>
+      </c>
+      <c r="Y2">
+        <v>1.06</v>
+      </c>
+      <c r="Z2">
+        <v>1.75</v>
+      </c>
+      <c r="AA2">
+        <v>3.39</v>
+      </c>
+      <c r="AB2">
+        <v>4.9</v>
+      </c>
+      <c r="AC2">
+        <v>1.07</v>
+      </c>
+      <c r="AD2">
+        <v>7.5</v>
+      </c>
+      <c r="AE2">
+        <v>1.43</v>
+      </c>
+      <c r="AF2">
+        <v>2.7</v>
+      </c>
+      <c r="AG2">
+        <v>2.23</v>
+      </c>
+      <c r="AH2">
+        <v>1.58</v>
+      </c>
+      <c r="AI2">
+        <v>2</v>
+      </c>
+      <c r="AJ2">
+        <v>1.73</v>
+      </c>
+      <c r="AK2">
+        <v>1.19</v>
+      </c>
+      <c r="AL2">
+        <v>1.29</v>
+      </c>
+      <c r="AM2">
+        <v>1.98</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>4</v>
+      </c>
+      <c r="AV2">
+        <v>7</v>
+      </c>
+      <c r="AW2">
+        <v>8</v>
+      </c>
+      <c r="AX2">
+        <v>4</v>
+      </c>
+      <c r="AY2">
+        <v>12</v>
+      </c>
+      <c r="AZ2">
+        <v>11</v>
+      </c>
+      <c r="BA2">
+        <v>2</v>
+      </c>
+      <c r="BB2">
+        <v>2</v>
+      </c>
+      <c r="BC2">
+        <v>4</v>
+      </c>
+      <c r="BD2">
+        <v>1.32</v>
+      </c>
+      <c r="BE2">
+        <v>8</v>
+      </c>
+      <c r="BF2">
+        <v>4.05</v>
+      </c>
+      <c r="BG2">
+        <v>1.27</v>
+      </c>
+      <c r="BH2">
+        <v>3.35</v>
+      </c>
+      <c r="BI2">
+        <v>1.5</v>
+      </c>
+      <c r="BJ2">
+        <v>2.35</v>
+      </c>
+      <c r="BK2">
+        <v>1.92</v>
+      </c>
+      <c r="BL2">
+        <v>1.78</v>
+      </c>
+      <c r="BM2">
+        <v>2.58</v>
+      </c>
+      <c r="BN2">
+        <v>1.44</v>
+      </c>
+      <c r="BO2">
+        <v>3.55</v>
+      </c>
+      <c r="BP2">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7821436</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45688.89583333334</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q3">
+        <v>3.1</v>
+      </c>
+      <c r="R3">
+        <v>2.1</v>
+      </c>
+      <c r="S3">
+        <v>3.6</v>
+      </c>
+      <c r="T3">
+        <v>1.44</v>
+      </c>
+      <c r="U3">
+        <v>2.63</v>
+      </c>
+      <c r="V3">
+        <v>3.25</v>
+      </c>
+      <c r="W3">
+        <v>1.33</v>
+      </c>
+      <c r="X3">
+        <v>9</v>
+      </c>
+      <c r="Y3">
+        <v>1.07</v>
+      </c>
+      <c r="Z3">
+        <v>2.39</v>
+      </c>
+      <c r="AA3">
+        <v>3.08</v>
+      </c>
+      <c r="AB3">
+        <v>3.05</v>
+      </c>
+      <c r="AC3">
+        <v>1.08</v>
+      </c>
+      <c r="AD3">
+        <v>7</v>
+      </c>
+      <c r="AE3">
+        <v>1.4</v>
+      </c>
+      <c r="AF3">
+        <v>2.8</v>
+      </c>
+      <c r="AG3">
+        <v>2.2</v>
+      </c>
+      <c r="AH3">
+        <v>1.55</v>
+      </c>
+      <c r="AI3">
+        <v>1.8</v>
+      </c>
+      <c r="AJ3">
+        <v>1.91</v>
+      </c>
+      <c r="AK3">
+        <v>1.36</v>
+      </c>
+      <c r="AL3">
+        <v>1.34</v>
+      </c>
+      <c r="AM3">
+        <v>1.55</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>5</v>
+      </c>
+      <c r="AV3">
+        <v>4</v>
+      </c>
+      <c r="AW3">
+        <v>7</v>
+      </c>
+      <c r="AX3">
+        <v>6</v>
+      </c>
+      <c r="AY3">
+        <v>12</v>
+      </c>
+      <c r="AZ3">
+        <v>10</v>
+      </c>
+      <c r="BA3">
+        <v>3</v>
+      </c>
+      <c r="BB3">
+        <v>4</v>
+      </c>
+      <c r="BC3">
+        <v>7</v>
+      </c>
+      <c r="BD3">
+        <v>1.8</v>
+      </c>
+      <c r="BE3">
+        <v>8</v>
+      </c>
+      <c r="BF3">
+        <v>2.25</v>
+      </c>
+      <c r="BG3">
+        <v>1.26</v>
+      </c>
+      <c r="BH3">
+        <v>3.22</v>
+      </c>
+      <c r="BI3">
+        <v>1.5</v>
+      </c>
+      <c r="BJ3">
+        <v>2.28</v>
+      </c>
+      <c r="BK3">
+        <v>1.95</v>
+      </c>
+      <c r="BL3">
+        <v>1.77</v>
+      </c>
+      <c r="BM3">
+        <v>2.42</v>
+      </c>
+      <c r="BN3">
+        <v>1.44</v>
+      </c>
+      <c r="BO3">
+        <v>3.28</v>
+      </c>
+      <c r="BP3">
+        <v>1.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="86">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -232,22 +232,46 @@
     <t>Defensor Sporting</t>
   </si>
   <si>
+    <t>Danubio</t>
+  </si>
+  <si>
+    <t>Progreso</t>
+  </si>
+  <si>
     <t>Juventud</t>
   </si>
   <si>
     <t>Boston River</t>
   </si>
   <si>
+    <t>Liverpool FC Montevideo</t>
+  </si>
+  <si>
+    <t>Peñarol</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
     <t>['26', '90+6']</t>
   </si>
   <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
     <t>['68']</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['20', '62', '75']</t>
   </si>
 </sst>
 </file>
@@ -609,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP3"/>
+  <dimension ref="A1:BP5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -841,7 +865,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -862,10 +886,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1047,7 +1071,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1068,10 +1092,10 @@
         <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="P3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="Q3">
         <v>3.1</v>
@@ -1228,6 +1252,418 @@
       </c>
       <c r="BP3">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7821440</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45689.70833333334</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4" t="s">
+        <v>80</v>
+      </c>
+      <c r="P4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q4">
+        <v>3.2</v>
+      </c>
+      <c r="R4">
+        <v>1.91</v>
+      </c>
+      <c r="S4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>1.57</v>
+      </c>
+      <c r="U4">
+        <v>2.25</v>
+      </c>
+      <c r="V4">
+        <v>3.75</v>
+      </c>
+      <c r="W4">
+        <v>1.25</v>
+      </c>
+      <c r="X4">
+        <v>13</v>
+      </c>
+      <c r="Y4">
+        <v>1.04</v>
+      </c>
+      <c r="Z4">
+        <v>2.32</v>
+      </c>
+      <c r="AA4">
+        <v>2.96</v>
+      </c>
+      <c r="AB4">
+        <v>3.31</v>
+      </c>
+      <c r="AC4">
+        <v>1.11</v>
+      </c>
+      <c r="AD4">
+        <v>5</v>
+      </c>
+      <c r="AE4">
+        <v>1.5</v>
+      </c>
+      <c r="AF4">
+        <v>2.4</v>
+      </c>
+      <c r="AG4">
+        <v>2.3</v>
+      </c>
+      <c r="AH4">
+        <v>1.5</v>
+      </c>
+      <c r="AI4">
+        <v>2.1</v>
+      </c>
+      <c r="AJ4">
+        <v>1.67</v>
+      </c>
+      <c r="AK4">
+        <v>1.35</v>
+      </c>
+      <c r="AL4">
+        <v>1.36</v>
+      </c>
+      <c r="AM4">
+        <v>1.53</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>3</v>
+      </c>
+      <c r="AV4">
+        <v>3</v>
+      </c>
+      <c r="AW4">
+        <v>7</v>
+      </c>
+      <c r="AX4">
+        <v>2</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
+        <v>5</v>
+      </c>
+      <c r="BA4">
+        <v>2</v>
+      </c>
+      <c r="BB4">
+        <v>5</v>
+      </c>
+      <c r="BC4">
+        <v>7</v>
+      </c>
+      <c r="BD4">
+        <v>1.75</v>
+      </c>
+      <c r="BE4">
+        <v>8.5</v>
+      </c>
+      <c r="BF4">
+        <v>2.25</v>
+      </c>
+      <c r="BG4">
+        <v>1.25</v>
+      </c>
+      <c r="BH4">
+        <v>3.28</v>
+      </c>
+      <c r="BI4">
+        <v>1.7</v>
+      </c>
+      <c r="BJ4">
+        <v>2.05</v>
+      </c>
+      <c r="BK4">
+        <v>1.85</v>
+      </c>
+      <c r="BL4">
+        <v>1.85</v>
+      </c>
+      <c r="BM4">
+        <v>2.38</v>
+      </c>
+      <c r="BN4">
+        <v>1.46</v>
+      </c>
+      <c r="BO4">
+        <v>3.2</v>
+      </c>
+      <c r="BP4">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7821434</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45689.83333333334</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q5">
+        <v>8.5</v>
+      </c>
+      <c r="R5">
+        <v>2.3</v>
+      </c>
+      <c r="S5">
+        <v>1.83</v>
+      </c>
+      <c r="T5">
+        <v>1.4</v>
+      </c>
+      <c r="U5">
+        <v>2.75</v>
+      </c>
+      <c r="V5">
+        <v>2.75</v>
+      </c>
+      <c r="W5">
+        <v>1.4</v>
+      </c>
+      <c r="X5">
+        <v>8</v>
+      </c>
+      <c r="Y5">
+        <v>1.08</v>
+      </c>
+      <c r="Z5">
+        <v>8.9</v>
+      </c>
+      <c r="AA5">
+        <v>4.9</v>
+      </c>
+      <c r="AB5">
+        <v>1.33</v>
+      </c>
+      <c r="AC5">
+        <v>1.04</v>
+      </c>
+      <c r="AD5">
+        <v>9</v>
+      </c>
+      <c r="AE5">
+        <v>1.29</v>
+      </c>
+      <c r="AF5">
+        <v>3.4</v>
+      </c>
+      <c r="AG5">
+        <v>1.85</v>
+      </c>
+      <c r="AH5">
+        <v>1.89</v>
+      </c>
+      <c r="AI5">
+        <v>2.25</v>
+      </c>
+      <c r="AJ5">
+        <v>1.57</v>
+      </c>
+      <c r="AK5">
+        <v>3.3</v>
+      </c>
+      <c r="AL5">
+        <v>1.16</v>
+      </c>
+      <c r="AM5">
+        <v>1.06</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>4</v>
+      </c>
+      <c r="AV5">
+        <v>6</v>
+      </c>
+      <c r="AW5">
+        <v>4</v>
+      </c>
+      <c r="AX5">
+        <v>3</v>
+      </c>
+      <c r="AY5">
+        <v>8</v>
+      </c>
+      <c r="AZ5">
+        <v>9</v>
+      </c>
+      <c r="BA5">
+        <v>5</v>
+      </c>
+      <c r="BB5">
+        <v>3</v>
+      </c>
+      <c r="BC5">
+        <v>8</v>
+      </c>
+      <c r="BD5">
+        <v>4.2</v>
+      </c>
+      <c r="BE5">
+        <v>11</v>
+      </c>
+      <c r="BF5">
+        <v>1.25</v>
+      </c>
+      <c r="BG5">
+        <v>1.27</v>
+      </c>
+      <c r="BH5">
+        <v>3.14</v>
+      </c>
+      <c r="BI5">
+        <v>1.52</v>
+      </c>
+      <c r="BJ5">
+        <v>2.24</v>
+      </c>
+      <c r="BK5">
+        <v>1.95</v>
+      </c>
+      <c r="BL5">
+        <v>1.77</v>
+      </c>
+      <c r="BM5">
+        <v>2.46</v>
+      </c>
+      <c r="BN5">
+        <v>1.43</v>
+      </c>
+      <c r="BO5">
+        <v>3.42</v>
+      </c>
+      <c r="BP5">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -238,6 +238,18 @@
     <t>Progreso</t>
   </si>
   <si>
+    <t>Miramar Misiones</t>
+  </si>
+  <si>
+    <t>Torque</t>
+  </si>
+  <si>
+    <t>Wanderers</t>
+  </si>
+  <si>
+    <t>Cerro</t>
+  </si>
+  <si>
     <t>Juventud</t>
   </si>
   <si>
@@ -250,6 +262,18 @@
     <t>Peñarol</t>
   </si>
   <si>
+    <t>Plaza Colonia</t>
+  </si>
+  <si>
+    <t>Nacional</t>
+  </si>
+  <si>
+    <t>Racing</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -262,16 +286,28 @@
     <t>['90+2']</t>
   </si>
   <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['33']</t>
+  </si>
+  <si>
     <t>['68']</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
     <t>['11']</t>
   </si>
   <si>
     <t>['20', '62', '75']</t>
+  </si>
+  <si>
+    <t>['19']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
   </si>
 </sst>
 </file>
@@ -633,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP5"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -865,7 +901,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -886,10 +922,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1071,7 +1107,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1092,10 +1128,10 @@
         <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="Q3">
         <v>3.1</v>
@@ -1277,7 +1313,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1298,10 +1334,10 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1483,7 +1519,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1504,10 +1540,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1664,6 +1700,830 @@
       </c>
       <c r="BP5">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7821439</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45690.70833333334</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>90</v>
+      </c>
+      <c r="P6" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q6">
+        <v>3.4</v>
+      </c>
+      <c r="R6">
+        <v>1.95</v>
+      </c>
+      <c r="S6">
+        <v>3.75</v>
+      </c>
+      <c r="T6">
+        <v>1.57</v>
+      </c>
+      <c r="U6">
+        <v>2.25</v>
+      </c>
+      <c r="V6">
+        <v>3.75</v>
+      </c>
+      <c r="W6">
+        <v>1.25</v>
+      </c>
+      <c r="X6">
+        <v>11</v>
+      </c>
+      <c r="Y6">
+        <v>1.05</v>
+      </c>
+      <c r="Z6">
+        <v>2.48</v>
+      </c>
+      <c r="AA6">
+        <v>2.95</v>
+      </c>
+      <c r="AB6">
+        <v>3.04</v>
+      </c>
+      <c r="AC6">
+        <v>1.08</v>
+      </c>
+      <c r="AD6">
+        <v>7</v>
+      </c>
+      <c r="AE6">
+        <v>1.47</v>
+      </c>
+      <c r="AF6">
+        <v>2.55</v>
+      </c>
+      <c r="AG6">
+        <v>2.37</v>
+      </c>
+      <c r="AH6">
+        <v>1.48</v>
+      </c>
+      <c r="AI6">
+        <v>2.1</v>
+      </c>
+      <c r="AJ6">
+        <v>1.67</v>
+      </c>
+      <c r="AK6">
+        <v>1.37</v>
+      </c>
+      <c r="AL6">
+        <v>1.36</v>
+      </c>
+      <c r="AM6">
+        <v>1.52</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>3</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>3</v>
+      </c>
+      <c r="AV6">
+        <v>4</v>
+      </c>
+      <c r="AW6">
+        <v>5</v>
+      </c>
+      <c r="AX6">
+        <v>8</v>
+      </c>
+      <c r="AY6">
+        <v>8</v>
+      </c>
+      <c r="AZ6">
+        <v>12</v>
+      </c>
+      <c r="BA6">
+        <v>2</v>
+      </c>
+      <c r="BB6">
+        <v>5</v>
+      </c>
+      <c r="BC6">
+        <v>7</v>
+      </c>
+      <c r="BD6">
+        <v>2.07</v>
+      </c>
+      <c r="BE6">
+        <v>6.15</v>
+      </c>
+      <c r="BF6">
+        <v>2.12</v>
+      </c>
+      <c r="BG6">
+        <v>1.28</v>
+      </c>
+      <c r="BH6">
+        <v>3.08</v>
+      </c>
+      <c r="BI6">
+        <v>1.52</v>
+      </c>
+      <c r="BJ6">
+        <v>2.24</v>
+      </c>
+      <c r="BK6">
+        <v>1.91</v>
+      </c>
+      <c r="BL6">
+        <v>1.8</v>
+      </c>
+      <c r="BM6">
+        <v>2.49</v>
+      </c>
+      <c r="BN6">
+        <v>1.42</v>
+      </c>
+      <c r="BO6">
+        <v>3.42</v>
+      </c>
+      <c r="BP6">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7821435</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45690.8125</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>91</v>
+      </c>
+      <c r="P7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q7">
+        <v>6</v>
+      </c>
+      <c r="R7">
+        <v>2.4</v>
+      </c>
+      <c r="S7">
+        <v>2</v>
+      </c>
+      <c r="T7">
+        <v>1.33</v>
+      </c>
+      <c r="U7">
+        <v>3.25</v>
+      </c>
+      <c r="V7">
+        <v>2.5</v>
+      </c>
+      <c r="W7">
+        <v>1.5</v>
+      </c>
+      <c r="X7">
+        <v>6</v>
+      </c>
+      <c r="Y7">
+        <v>1.13</v>
+      </c>
+      <c r="Z7">
+        <v>6.9</v>
+      </c>
+      <c r="AA7">
+        <v>4.1</v>
+      </c>
+      <c r="AB7">
+        <v>1.46</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>1.66</v>
+      </c>
+      <c r="AH7">
+        <v>2.09</v>
+      </c>
+      <c r="AI7">
+        <v>1.8</v>
+      </c>
+      <c r="AJ7">
+        <v>1.91</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>3</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>3</v>
+      </c>
+      <c r="AV7">
+        <v>4</v>
+      </c>
+      <c r="AW7">
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <v>1</v>
+      </c>
+      <c r="AY7">
+        <v>4</v>
+      </c>
+      <c r="AZ7">
+        <v>5</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>2</v>
+      </c>
+      <c r="BC7">
+        <v>2</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7821438</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45690.90625</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>90</v>
+      </c>
+      <c r="P8" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q8">
+        <v>3.75</v>
+      </c>
+      <c r="R8">
+        <v>2</v>
+      </c>
+      <c r="S8">
+        <v>3.1</v>
+      </c>
+      <c r="T8">
+        <v>1.5</v>
+      </c>
+      <c r="U8">
+        <v>2.5</v>
+      </c>
+      <c r="V8">
+        <v>3.5</v>
+      </c>
+      <c r="W8">
+        <v>1.29</v>
+      </c>
+      <c r="X8">
+        <v>11</v>
+      </c>
+      <c r="Y8">
+        <v>1.05</v>
+      </c>
+      <c r="Z8">
+        <v>3.12</v>
+      </c>
+      <c r="AA8">
+        <v>3.18</v>
+      </c>
+      <c r="AB8">
+        <v>2.3</v>
+      </c>
+      <c r="AC8">
+        <v>1.08</v>
+      </c>
+      <c r="AD8">
+        <v>7</v>
+      </c>
+      <c r="AE8">
+        <v>1.4</v>
+      </c>
+      <c r="AF8">
+        <v>2.8</v>
+      </c>
+      <c r="AG8">
+        <v>2.2</v>
+      </c>
+      <c r="AH8">
+        <v>1.55</v>
+      </c>
+      <c r="AI8">
+        <v>1.91</v>
+      </c>
+      <c r="AJ8">
+        <v>1.8</v>
+      </c>
+      <c r="AK8">
+        <v>1.68</v>
+      </c>
+      <c r="AL8">
+        <v>1.33</v>
+      </c>
+      <c r="AM8">
+        <v>1.29</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>4</v>
+      </c>
+      <c r="AV8">
+        <v>4</v>
+      </c>
+      <c r="AW8">
+        <v>4</v>
+      </c>
+      <c r="AX8">
+        <v>8</v>
+      </c>
+      <c r="AY8">
+        <v>8</v>
+      </c>
+      <c r="AZ8">
+        <v>12</v>
+      </c>
+      <c r="BA8">
+        <v>2</v>
+      </c>
+      <c r="BB8">
+        <v>2</v>
+      </c>
+      <c r="BC8">
+        <v>4</v>
+      </c>
+      <c r="BD8">
+        <v>2.17</v>
+      </c>
+      <c r="BE8">
+        <v>6.25</v>
+      </c>
+      <c r="BF8">
+        <v>2.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.22</v>
+      </c>
+      <c r="BH8">
+        <v>3.5</v>
+      </c>
+      <c r="BI8">
+        <v>1.42</v>
+      </c>
+      <c r="BJ8">
+        <v>2.49</v>
+      </c>
+      <c r="BK8">
+        <v>1.85</v>
+      </c>
+      <c r="BL8">
+        <v>1.85</v>
+      </c>
+      <c r="BM8">
+        <v>2.21</v>
+      </c>
+      <c r="BN8">
+        <v>1.53</v>
+      </c>
+      <c r="BO8">
+        <v>2.97</v>
+      </c>
+      <c r="BP8">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7821437</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45691.8125</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="O9" t="s">
+        <v>92</v>
+      </c>
+      <c r="P9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q9">
+        <v>3.25</v>
+      </c>
+      <c r="R9">
+        <v>1.91</v>
+      </c>
+      <c r="S9">
+        <v>4</v>
+      </c>
+      <c r="T9">
+        <v>1.57</v>
+      </c>
+      <c r="U9">
+        <v>2.25</v>
+      </c>
+      <c r="V9">
+        <v>3.75</v>
+      </c>
+      <c r="W9">
+        <v>1.25</v>
+      </c>
+      <c r="X9">
+        <v>13</v>
+      </c>
+      <c r="Y9">
+        <v>1.04</v>
+      </c>
+      <c r="Z9">
+        <v>2.41</v>
+      </c>
+      <c r="AA9">
+        <v>2.96</v>
+      </c>
+      <c r="AB9">
+        <v>3.15</v>
+      </c>
+      <c r="AC9">
+        <v>1.08</v>
+      </c>
+      <c r="AD9">
+        <v>7</v>
+      </c>
+      <c r="AE9">
+        <v>1.51</v>
+      </c>
+      <c r="AF9">
+        <v>2.46</v>
+      </c>
+      <c r="AG9">
+        <v>2.37</v>
+      </c>
+      <c r="AH9">
+        <v>1.48</v>
+      </c>
+      <c r="AI9">
+        <v>2.2</v>
+      </c>
+      <c r="AJ9">
+        <v>1.62</v>
+      </c>
+      <c r="AK9">
+        <v>1.35</v>
+      </c>
+      <c r="AL9">
+        <v>1.35</v>
+      </c>
+      <c r="AM9">
+        <v>1.55</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>1</v>
+      </c>
+      <c r="AQ9">
+        <v>1</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>3</v>
+      </c>
+      <c r="AV9">
+        <v>3</v>
+      </c>
+      <c r="AW9">
+        <v>3</v>
+      </c>
+      <c r="AX9">
+        <v>5</v>
+      </c>
+      <c r="AY9">
+        <v>6</v>
+      </c>
+      <c r="AZ9">
+        <v>8</v>
+      </c>
+      <c r="BA9">
+        <v>2</v>
+      </c>
+      <c r="BB9">
+        <v>4</v>
+      </c>
+      <c r="BC9">
+        <v>6</v>
+      </c>
+      <c r="BD9">
+        <v>1.74</v>
+      </c>
+      <c r="BE9">
+        <v>6.35</v>
+      </c>
+      <c r="BF9">
+        <v>2.59</v>
+      </c>
+      <c r="BG9">
+        <v>1.27</v>
+      </c>
+      <c r="BH9">
+        <v>3.14</v>
+      </c>
+      <c r="BI9">
+        <v>1.51</v>
+      </c>
+      <c r="BJ9">
+        <v>2.26</v>
+      </c>
+      <c r="BK9">
+        <v>1.95</v>
+      </c>
+      <c r="BL9">
+        <v>1.77</v>
+      </c>
+      <c r="BM9">
+        <v>2.43</v>
+      </c>
+      <c r="BN9">
+        <v>1.44</v>
+      </c>
+      <c r="BO9">
+        <v>3.34</v>
+      </c>
+      <c r="BP9">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -250,6 +250,9 @@
     <t>Cerro</t>
   </si>
   <si>
+    <t>Plaza Colonia</t>
+  </si>
+  <si>
     <t>Juventud</t>
   </si>
   <si>
@@ -262,9 +265,6 @@
     <t>Peñarol</t>
   </si>
   <si>
-    <t>Plaza Colonia</t>
-  </si>
-  <si>
     <t>Nacional</t>
   </si>
   <si>
@@ -295,6 +295,12 @@
     <t>['33']</t>
   </si>
   <si>
+    <t>['8', '33', '35', '58']</t>
+  </si>
+  <si>
+    <t>['62', '87']</t>
+  </si>
+  <si>
     <t>['68']</t>
   </si>
   <si>
@@ -308,6 +314,9 @@
   </si>
   <si>
     <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['56']</t>
   </si>
 </sst>
 </file>
@@ -669,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP9"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -901,7 +910,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -925,7 +934,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1003,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1107,7 +1116,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1313,7 +1322,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1337,7 +1346,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1519,7 +1528,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1543,7 +1552,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1725,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1749,7 +1758,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2367,7 +2376,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2524,6 +2533,418 @@
       </c>
       <c r="BP9">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7821442</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45695.79166666666</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>3</v>
+      </c>
+      <c r="L10">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10" t="s">
+        <v>93</v>
+      </c>
+      <c r="P10" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>2.74</v>
+      </c>
+      <c r="R10">
+        <v>2.03</v>
+      </c>
+      <c r="S10">
+        <v>4.86</v>
+      </c>
+      <c r="T10">
+        <v>1.52</v>
+      </c>
+      <c r="U10">
+        <v>2.51</v>
+      </c>
+      <c r="V10">
+        <v>3.3</v>
+      </c>
+      <c r="W10">
+        <v>1.29</v>
+      </c>
+      <c r="X10">
+        <v>9.1</v>
+      </c>
+      <c r="Y10">
+        <v>1.03</v>
+      </c>
+      <c r="Z10">
+        <v>1.94</v>
+      </c>
+      <c r="AA10">
+        <v>3.06</v>
+      </c>
+      <c r="AB10">
+        <v>4.4</v>
+      </c>
+      <c r="AC10">
+        <v>1.1</v>
+      </c>
+      <c r="AD10">
+        <v>6.82</v>
+      </c>
+      <c r="AE10">
+        <v>1.61</v>
+      </c>
+      <c r="AF10">
+        <v>2.23</v>
+      </c>
+      <c r="AG10">
+        <v>2.25</v>
+      </c>
+      <c r="AH10">
+        <v>1.53</v>
+      </c>
+      <c r="AI10">
+        <v>2.03</v>
+      </c>
+      <c r="AJ10">
+        <v>1.71</v>
+      </c>
+      <c r="AK10">
+        <v>1.23</v>
+      </c>
+      <c r="AL10">
+        <v>1.33</v>
+      </c>
+      <c r="AM10">
+        <v>1.69</v>
+      </c>
+      <c r="AN10">
+        <v>1</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>2</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>1.56</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>1.56</v>
+      </c>
+      <c r="AU10">
+        <v>12</v>
+      </c>
+      <c r="AV10">
+        <v>4</v>
+      </c>
+      <c r="AW10">
+        <v>5</v>
+      </c>
+      <c r="AX10">
+        <v>4</v>
+      </c>
+      <c r="AY10">
+        <v>17</v>
+      </c>
+      <c r="AZ10">
+        <v>8</v>
+      </c>
+      <c r="BA10">
+        <v>5</v>
+      </c>
+      <c r="BB10">
+        <v>2</v>
+      </c>
+      <c r="BC10">
+        <v>7</v>
+      </c>
+      <c r="BD10">
+        <v>1.73</v>
+      </c>
+      <c r="BE10">
+        <v>7.5</v>
+      </c>
+      <c r="BF10">
+        <v>2.5</v>
+      </c>
+      <c r="BG10">
+        <v>1.44</v>
+      </c>
+      <c r="BH10">
+        <v>2.67</v>
+      </c>
+      <c r="BI10">
+        <v>1.77</v>
+      </c>
+      <c r="BJ10">
+        <v>1.95</v>
+      </c>
+      <c r="BK10">
+        <v>2.22</v>
+      </c>
+      <c r="BL10">
+        <v>1.62</v>
+      </c>
+      <c r="BM10">
+        <v>2.92</v>
+      </c>
+      <c r="BN10">
+        <v>1.38</v>
+      </c>
+      <c r="BO10">
+        <v>4.1</v>
+      </c>
+      <c r="BP10">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7821445</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45695.89583333334</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11" t="s">
+        <v>94</v>
+      </c>
+      <c r="P11" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q11">
+        <v>3.2</v>
+      </c>
+      <c r="R11">
+        <v>2.06</v>
+      </c>
+      <c r="S11">
+        <v>3.3</v>
+      </c>
+      <c r="T11">
+        <v>1.46</v>
+      </c>
+      <c r="U11">
+        <v>2.5</v>
+      </c>
+      <c r="V11">
+        <v>3.1</v>
+      </c>
+      <c r="W11">
+        <v>1.31</v>
+      </c>
+      <c r="X11">
+        <v>8.5</v>
+      </c>
+      <c r="Y11">
+        <v>1.04</v>
+      </c>
+      <c r="Z11">
+        <v>2.96</v>
+      </c>
+      <c r="AA11">
+        <v>3.1</v>
+      </c>
+      <c r="AB11">
+        <v>2.44</v>
+      </c>
+      <c r="AC11">
+        <v>1.05</v>
+      </c>
+      <c r="AD11">
+        <v>7.6</v>
+      </c>
+      <c r="AE11">
+        <v>1.4</v>
+      </c>
+      <c r="AF11">
+        <v>2.7</v>
+      </c>
+      <c r="AG11">
+        <v>2.37</v>
+      </c>
+      <c r="AH11">
+        <v>1.48</v>
+      </c>
+      <c r="AI11">
+        <v>1.96</v>
+      </c>
+      <c r="AJ11">
+        <v>1.8</v>
+      </c>
+      <c r="AK11">
+        <v>1.4</v>
+      </c>
+      <c r="AL11">
+        <v>1.32</v>
+      </c>
+      <c r="AM11">
+        <v>1.46</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>3</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>3</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>4</v>
+      </c>
+      <c r="AX11">
+        <v>7</v>
+      </c>
+      <c r="AY11">
+        <v>7</v>
+      </c>
+      <c r="AZ11">
+        <v>7</v>
+      </c>
+      <c r="BA11">
+        <v>4</v>
+      </c>
+      <c r="BB11">
+        <v>3</v>
+      </c>
+      <c r="BC11">
+        <v>7</v>
+      </c>
+      <c r="BD11">
+        <v>1.98</v>
+      </c>
+      <c r="BE11">
+        <v>6.25</v>
+      </c>
+      <c r="BF11">
+        <v>2</v>
+      </c>
+      <c r="BG11">
+        <v>1.53</v>
+      </c>
+      <c r="BH11">
+        <v>2.3</v>
+      </c>
+      <c r="BI11">
+        <v>1.9</v>
+      </c>
+      <c r="BJ11">
+        <v>1.79</v>
+      </c>
+      <c r="BK11">
+        <v>2.43</v>
+      </c>
+      <c r="BL11">
+        <v>1.48</v>
+      </c>
+      <c r="BM11">
+        <v>3.2</v>
+      </c>
+      <c r="BN11">
+        <v>1.29</v>
+      </c>
+      <c r="BO11">
+        <v>4.35</v>
+      </c>
+      <c r="BP11">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="103">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -253,15 +253,15 @@
     <t>Plaza Colonia</t>
   </si>
   <si>
+    <t>Liverpool FC Montevideo</t>
+  </si>
+  <si>
     <t>Juventud</t>
   </si>
   <si>
     <t>Boston River</t>
   </si>
   <si>
-    <t>Liverpool FC Montevideo</t>
-  </si>
-  <si>
     <t>Peñarol</t>
   </si>
   <si>
@@ -301,6 +301,9 @@
     <t>['62', '87']</t>
   </si>
   <si>
+    <t>['35', '45']</t>
+  </si>
+  <si>
     <t>['68']</t>
   </si>
   <si>
@@ -317,6 +320,9 @@
   </si>
   <si>
     <t>['56']</t>
+  </si>
+  <si>
+    <t>['27']</t>
   </si>
 </sst>
 </file>
@@ -678,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -910,7 +916,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -934,7 +940,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1116,7 +1122,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1322,7 +1328,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1346,7 +1352,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1552,7 +1558,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1758,7 +1764,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2376,7 +2382,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2582,7 +2588,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -2945,6 +2951,212 @@
       </c>
       <c r="BP11">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7821444</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45696.40625</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>3</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12" t="s">
+        <v>95</v>
+      </c>
+      <c r="P12" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q12">
+        <v>2.59</v>
+      </c>
+      <c r="R12">
+        <v>2.12</v>
+      </c>
+      <c r="S12">
+        <v>4.88</v>
+      </c>
+      <c r="T12">
+        <v>1.46</v>
+      </c>
+      <c r="U12">
+        <v>2.67</v>
+      </c>
+      <c r="V12">
+        <v>3.34</v>
+      </c>
+      <c r="W12">
+        <v>1.32</v>
+      </c>
+      <c r="X12">
+        <v>8.6</v>
+      </c>
+      <c r="Y12">
+        <v>1.05</v>
+      </c>
+      <c r="Z12">
+        <v>1.92</v>
+      </c>
+      <c r="AA12">
+        <v>3.28</v>
+      </c>
+      <c r="AB12">
+        <v>4.1</v>
+      </c>
+      <c r="AC12">
+        <v>1.06</v>
+      </c>
+      <c r="AD12">
+        <v>7.5</v>
+      </c>
+      <c r="AE12">
+        <v>1.4</v>
+      </c>
+      <c r="AF12">
+        <v>2.9</v>
+      </c>
+      <c r="AG12">
+        <v>2.2</v>
+      </c>
+      <c r="AH12">
+        <v>1.55</v>
+      </c>
+      <c r="AI12">
+        <v>1.97</v>
+      </c>
+      <c r="AJ12">
+        <v>1.75</v>
+      </c>
+      <c r="AK12">
+        <v>1.22</v>
+      </c>
+      <c r="AL12">
+        <v>1.3</v>
+      </c>
+      <c r="AM12">
+        <v>1.8</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>3</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>6</v>
+      </c>
+      <c r="AV12">
+        <v>4</v>
+      </c>
+      <c r="AW12">
+        <v>7</v>
+      </c>
+      <c r="AX12">
+        <v>9</v>
+      </c>
+      <c r="AY12">
+        <v>13</v>
+      </c>
+      <c r="AZ12">
+        <v>13</v>
+      </c>
+      <c r="BA12">
+        <v>5</v>
+      </c>
+      <c r="BB12">
+        <v>3</v>
+      </c>
+      <c r="BC12">
+        <v>8</v>
+      </c>
+      <c r="BD12">
+        <v>1.63</v>
+      </c>
+      <c r="BE12">
+        <v>6.4</v>
+      </c>
+      <c r="BF12">
+        <v>2.55</v>
+      </c>
+      <c r="BG12">
+        <v>1.49</v>
+      </c>
+      <c r="BH12">
+        <v>2.43</v>
+      </c>
+      <c r="BI12">
+        <v>1.79</v>
+      </c>
+      <c r="BJ12">
+        <v>1.9</v>
+      </c>
+      <c r="BK12">
+        <v>2.25</v>
+      </c>
+      <c r="BL12">
+        <v>1.55</v>
+      </c>
+      <c r="BM12">
+        <v>2.9</v>
+      </c>
+      <c r="BN12">
+        <v>1.34</v>
+      </c>
+      <c r="BO12">
+        <v>3.95</v>
+      </c>
+      <c r="BP12">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="105">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -256,6 +256,12 @@
     <t>Liverpool FC Montevideo</t>
   </si>
   <si>
+    <t>Racing</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
     <t>Juventud</t>
   </si>
   <si>
@@ -268,12 +274,6 @@
     <t>Nacional</t>
   </si>
   <si>
-    <t>Racing</t>
-  </si>
-  <si>
-    <t>River Plate</t>
-  </si>
-  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -295,13 +295,13 @@
     <t>['33']</t>
   </si>
   <si>
-    <t>['8', '33', '35', '58']</t>
+    <t>['6', '32', '33', '59']</t>
   </si>
   <si>
     <t>['62', '87']</t>
   </si>
   <si>
-    <t>['35', '45']</t>
+    <t>['34', '44']</t>
   </si>
   <si>
     <t>['68']</t>
@@ -319,10 +319,16 @@
     <t>['90+4']</t>
   </si>
   <si>
-    <t>['56']</t>
-  </si>
-  <si>
-    <t>['27']</t>
+    <t>['55']</t>
+  </si>
+  <si>
+    <t>['26']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
+    <t>['52']</t>
   </si>
 </sst>
 </file>
@@ -684,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP12"/>
+  <dimension ref="A1:BP14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -916,7 +922,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1122,7 +1128,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1534,7 +1540,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1946,7 +1952,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -2152,7 +2158,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2358,7 +2364,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -3157,6 +3163,418 @@
       </c>
       <c r="BP12">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7821446</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45696.70833333334</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>90</v>
+      </c>
+      <c r="P13" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q13">
+        <v>2.75</v>
+      </c>
+      <c r="R13">
+        <v>1.91</v>
+      </c>
+      <c r="S13">
+        <v>4.5</v>
+      </c>
+      <c r="T13">
+        <v>1.53</v>
+      </c>
+      <c r="U13">
+        <v>2.47</v>
+      </c>
+      <c r="V13">
+        <v>3.45</v>
+      </c>
+      <c r="W13">
+        <v>1.25</v>
+      </c>
+      <c r="X13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y13">
+        <v>1.03</v>
+      </c>
+      <c r="Z13">
+        <v>2.16</v>
+      </c>
+      <c r="AA13">
+        <v>3.03</v>
+      </c>
+      <c r="AB13">
+        <v>3.6</v>
+      </c>
+      <c r="AC13">
+        <v>1.07</v>
+      </c>
+      <c r="AD13">
+        <v>7</v>
+      </c>
+      <c r="AE13">
+        <v>1.48</v>
+      </c>
+      <c r="AF13">
+        <v>2.5</v>
+      </c>
+      <c r="AG13">
+        <v>2.4</v>
+      </c>
+      <c r="AH13">
+        <v>1.5</v>
+      </c>
+      <c r="AI13">
+        <v>2.1</v>
+      </c>
+      <c r="AJ13">
+        <v>1.67</v>
+      </c>
+      <c r="AK13">
+        <v>1.22</v>
+      </c>
+      <c r="AL13">
+        <v>1.3</v>
+      </c>
+      <c r="AM13">
+        <v>1.75</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>3</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>2</v>
+      </c>
+      <c r="AV13">
+        <v>4</v>
+      </c>
+      <c r="AW13">
+        <v>7</v>
+      </c>
+      <c r="AX13">
+        <v>1</v>
+      </c>
+      <c r="AY13">
+        <v>9</v>
+      </c>
+      <c r="AZ13">
+        <v>5</v>
+      </c>
+      <c r="BA13">
+        <v>2</v>
+      </c>
+      <c r="BB13">
+        <v>5</v>
+      </c>
+      <c r="BC13">
+        <v>7</v>
+      </c>
+      <c r="BD13">
+        <v>1.65</v>
+      </c>
+      <c r="BE13">
+        <v>6.4</v>
+      </c>
+      <c r="BF13">
+        <v>2.55</v>
+      </c>
+      <c r="BG13">
+        <v>1.5</v>
+      </c>
+      <c r="BH13">
+        <v>2.35</v>
+      </c>
+      <c r="BI13">
+        <v>1.84</v>
+      </c>
+      <c r="BJ13">
+        <v>1.84</v>
+      </c>
+      <c r="BK13">
+        <v>2.4</v>
+      </c>
+      <c r="BL13">
+        <v>1.5</v>
+      </c>
+      <c r="BM13">
+        <v>3.15</v>
+      </c>
+      <c r="BN13">
+        <v>1.3</v>
+      </c>
+      <c r="BO13">
+        <v>4.35</v>
+      </c>
+      <c r="BP13">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7821447</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45696.8125</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="s">
+        <v>90</v>
+      </c>
+      <c r="P14" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q14">
+        <v>3.78</v>
+      </c>
+      <c r="R14">
+        <v>2.12</v>
+      </c>
+      <c r="S14">
+        <v>3.08</v>
+      </c>
+      <c r="T14">
+        <v>1.44</v>
+      </c>
+      <c r="U14">
+        <v>2.73</v>
+      </c>
+      <c r="V14">
+        <v>3.25</v>
+      </c>
+      <c r="W14">
+        <v>1.33</v>
+      </c>
+      <c r="X14">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y14">
+        <v>1.05</v>
+      </c>
+      <c r="Z14">
+        <v>3.39</v>
+      </c>
+      <c r="AA14">
+        <v>3.21</v>
+      </c>
+      <c r="AB14">
+        <v>2.15</v>
+      </c>
+      <c r="AC14">
+        <v>1.07</v>
+      </c>
+      <c r="AD14">
+        <v>7.5</v>
+      </c>
+      <c r="AE14">
+        <v>1.38</v>
+      </c>
+      <c r="AF14">
+        <v>2.9</v>
+      </c>
+      <c r="AG14">
+        <v>2.05</v>
+      </c>
+      <c r="AH14">
+        <v>1.65</v>
+      </c>
+      <c r="AI14">
+        <v>1.84</v>
+      </c>
+      <c r="AJ14">
+        <v>1.92</v>
+      </c>
+      <c r="AK14">
+        <v>1.58</v>
+      </c>
+      <c r="AL14">
+        <v>1.3</v>
+      </c>
+      <c r="AM14">
+        <v>1.33</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>3</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>2</v>
+      </c>
+      <c r="AV14">
+        <v>3</v>
+      </c>
+      <c r="AW14">
+        <v>3</v>
+      </c>
+      <c r="AX14">
+        <v>2</v>
+      </c>
+      <c r="AY14">
+        <v>5</v>
+      </c>
+      <c r="AZ14">
+        <v>5</v>
+      </c>
+      <c r="BA14">
+        <v>5</v>
+      </c>
+      <c r="BB14">
+        <v>2</v>
+      </c>
+      <c r="BC14">
+        <v>7</v>
+      </c>
+      <c r="BD14">
+        <v>2.32</v>
+      </c>
+      <c r="BE14">
+        <v>6.25</v>
+      </c>
+      <c r="BF14">
+        <v>1.76</v>
+      </c>
+      <c r="BG14">
+        <v>1.45</v>
+      </c>
+      <c r="BH14">
+        <v>2.55</v>
+      </c>
+      <c r="BI14">
+        <v>1.75</v>
+      </c>
+      <c r="BJ14">
+        <v>1.95</v>
+      </c>
+      <c r="BK14">
+        <v>2.23</v>
+      </c>
+      <c r="BL14">
+        <v>1.57</v>
+      </c>
+      <c r="BM14">
+        <v>2.9</v>
+      </c>
+      <c r="BN14">
+        <v>1.35</v>
+      </c>
+      <c r="BO14">
+        <v>3.9</v>
+      </c>
+      <c r="BP14">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="109">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -268,12 +268,12 @@
     <t>Boston River</t>
   </si>
   <si>
+    <t>Nacional</t>
+  </si>
+  <si>
     <t>Peñarol</t>
   </si>
   <si>
-    <t>Nacional</t>
-  </si>
-  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -304,6 +304,12 @@
     <t>['34', '44']</t>
   </si>
   <si>
+    <t>['60', '84']</t>
+  </si>
+  <si>
+    <t>['61']</t>
+  </si>
+  <si>
     <t>['68']</t>
   </si>
   <si>
@@ -325,10 +331,16 @@
     <t>['26']</t>
   </si>
   <si>
-    <t>['89']</t>
+    <t>['90']</t>
   </si>
   <si>
     <t>['52']</t>
+  </si>
+  <si>
+    <t>['30', '38']</t>
+  </si>
+  <si>
+    <t>['50']</t>
   </si>
 </sst>
 </file>
@@ -690,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP14"/>
+  <dimension ref="A1:BP17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -946,7 +958,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1358,7 +1370,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1540,7 +1552,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1564,7 +1576,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1645,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="AQ5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1770,7 +1782,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -1952,7 +1964,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -2388,7 +2400,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2594,7 +2606,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3006,7 +3018,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3212,7 +3224,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3418,7 +3430,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q14">
         <v>3.78</v>
@@ -3575,6 +3587,624 @@
       </c>
       <c r="BP14">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7821443</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45697.40625</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>4</v>
+      </c>
+      <c r="O15" t="s">
+        <v>96</v>
+      </c>
+      <c r="P15" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q15">
+        <v>3.8</v>
+      </c>
+      <c r="R15">
+        <v>1.89</v>
+      </c>
+      <c r="S15">
+        <v>3.08</v>
+      </c>
+      <c r="T15">
+        <v>1.53</v>
+      </c>
+      <c r="U15">
+        <v>2.4</v>
+      </c>
+      <c r="V15">
+        <v>3.62</v>
+      </c>
+      <c r="W15">
+        <v>1.26</v>
+      </c>
+      <c r="X15">
+        <v>10.5</v>
+      </c>
+      <c r="Y15">
+        <v>1.03</v>
+      </c>
+      <c r="Z15">
+        <v>3.02</v>
+      </c>
+      <c r="AA15">
+        <v>2.99</v>
+      </c>
+      <c r="AB15">
+        <v>2.47</v>
+      </c>
+      <c r="AC15">
+        <v>1.08</v>
+      </c>
+      <c r="AD15">
+        <v>7</v>
+      </c>
+      <c r="AE15">
+        <v>1.49</v>
+      </c>
+      <c r="AF15">
+        <v>2.5</v>
+      </c>
+      <c r="AG15">
+        <v>2.25</v>
+      </c>
+      <c r="AH15">
+        <v>1.53</v>
+      </c>
+      <c r="AI15">
+        <v>2.03</v>
+      </c>
+      <c r="AJ15">
+        <v>1.75</v>
+      </c>
+      <c r="AK15">
+        <v>1.52</v>
+      </c>
+      <c r="AL15">
+        <v>1.33</v>
+      </c>
+      <c r="AM15">
+        <v>1.34</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>1</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>3</v>
+      </c>
+      <c r="AV15">
+        <v>6</v>
+      </c>
+      <c r="AW15">
+        <v>7</v>
+      </c>
+      <c r="AX15">
+        <v>3</v>
+      </c>
+      <c r="AY15">
+        <v>10</v>
+      </c>
+      <c r="AZ15">
+        <v>9</v>
+      </c>
+      <c r="BA15">
+        <v>3</v>
+      </c>
+      <c r="BB15">
+        <v>6</v>
+      </c>
+      <c r="BC15">
+        <v>9</v>
+      </c>
+      <c r="BD15">
+        <v>2.2</v>
+      </c>
+      <c r="BE15">
+        <v>7.5</v>
+      </c>
+      <c r="BF15">
+        <v>1.91</v>
+      </c>
+      <c r="BG15">
+        <v>1.4</v>
+      </c>
+      <c r="BH15">
+        <v>2.82</v>
+      </c>
+      <c r="BI15">
+        <v>1.68</v>
+      </c>
+      <c r="BJ15">
+        <v>2.12</v>
+      </c>
+      <c r="BK15">
+        <v>2.11</v>
+      </c>
+      <c r="BL15">
+        <v>1.68</v>
+      </c>
+      <c r="BM15">
+        <v>2.75</v>
+      </c>
+      <c r="BN15">
+        <v>1.42</v>
+      </c>
+      <c r="BO15">
+        <v>3.8</v>
+      </c>
+      <c r="BP15">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7821448</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45697.70833333334</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>90</v>
+      </c>
+      <c r="P16" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q16">
+        <v>3.24</v>
+      </c>
+      <c r="R16">
+        <v>2.01</v>
+      </c>
+      <c r="S16">
+        <v>3.24</v>
+      </c>
+      <c r="T16">
+        <v>1.44</v>
+      </c>
+      <c r="U16">
+        <v>2.66</v>
+      </c>
+      <c r="V16">
+        <v>3.04</v>
+      </c>
+      <c r="W16">
+        <v>1.35</v>
+      </c>
+      <c r="X16">
+        <v>8</v>
+      </c>
+      <c r="Y16">
+        <v>1.06</v>
+      </c>
+      <c r="Z16">
+        <v>2.65</v>
+      </c>
+      <c r="AA16">
+        <v>3.17</v>
+      </c>
+      <c r="AB16">
+        <v>2.66</v>
+      </c>
+      <c r="AC16">
+        <v>1.02</v>
+      </c>
+      <c r="AD16">
+        <v>7.8</v>
+      </c>
+      <c r="AE16">
+        <v>1.32</v>
+      </c>
+      <c r="AF16">
+        <v>3</v>
+      </c>
+      <c r="AG16">
+        <v>2.06</v>
+      </c>
+      <c r="AH16">
+        <v>1.68</v>
+      </c>
+      <c r="AI16">
+        <v>1.8</v>
+      </c>
+      <c r="AJ16">
+        <v>1.96</v>
+      </c>
+      <c r="AK16">
+        <v>1.44</v>
+      </c>
+      <c r="AL16">
+        <v>1.3</v>
+      </c>
+      <c r="AM16">
+        <v>1.44</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>1</v>
+      </c>
+      <c r="AQ16">
+        <v>1</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>2</v>
+      </c>
+      <c r="AV16">
+        <v>5</v>
+      </c>
+      <c r="AW16">
+        <v>6</v>
+      </c>
+      <c r="AX16">
+        <v>3</v>
+      </c>
+      <c r="AY16">
+        <v>8</v>
+      </c>
+      <c r="AZ16">
+        <v>8</v>
+      </c>
+      <c r="BA16">
+        <v>4</v>
+      </c>
+      <c r="BB16">
+        <v>1</v>
+      </c>
+      <c r="BC16">
+        <v>5</v>
+      </c>
+      <c r="BD16">
+        <v>1.98</v>
+      </c>
+      <c r="BE16">
+        <v>7.45</v>
+      </c>
+      <c r="BF16">
+        <v>2.12</v>
+      </c>
+      <c r="BG16">
+        <v>1.51</v>
+      </c>
+      <c r="BH16">
+        <v>2.45</v>
+      </c>
+      <c r="BI16">
+        <v>1.87</v>
+      </c>
+      <c r="BJ16">
+        <v>1.87</v>
+      </c>
+      <c r="BK16">
+        <v>2.42</v>
+      </c>
+      <c r="BL16">
+        <v>1.53</v>
+      </c>
+      <c r="BM16">
+        <v>3.3</v>
+      </c>
+      <c r="BN16">
+        <v>1.3</v>
+      </c>
+      <c r="BO16">
+        <v>4.65</v>
+      </c>
+      <c r="BP16">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7821449</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45697.8125</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17" t="s">
+        <v>97</v>
+      </c>
+      <c r="P17" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q17">
+        <v>3.4</v>
+      </c>
+      <c r="R17">
+        <v>2</v>
+      </c>
+      <c r="S17">
+        <v>3.5</v>
+      </c>
+      <c r="T17">
+        <v>1.5</v>
+      </c>
+      <c r="U17">
+        <v>2.5</v>
+      </c>
+      <c r="V17">
+        <v>3.5</v>
+      </c>
+      <c r="W17">
+        <v>1.29</v>
+      </c>
+      <c r="X17">
+        <v>10</v>
+      </c>
+      <c r="Y17">
+        <v>1.06</v>
+      </c>
+      <c r="Z17">
+        <v>2.58</v>
+      </c>
+      <c r="AA17">
+        <v>3.01</v>
+      </c>
+      <c r="AB17">
+        <v>2.85</v>
+      </c>
+      <c r="AC17">
+        <v>1.07</v>
+      </c>
+      <c r="AD17">
+        <v>7.5</v>
+      </c>
+      <c r="AE17">
+        <v>1.41</v>
+      </c>
+      <c r="AF17">
+        <v>2.75</v>
+      </c>
+      <c r="AG17">
+        <v>2.2</v>
+      </c>
+      <c r="AH17">
+        <v>1.55</v>
+      </c>
+      <c r="AI17">
+        <v>1.91</v>
+      </c>
+      <c r="AJ17">
+        <v>1.8</v>
+      </c>
+      <c r="AK17">
+        <v>1.39</v>
+      </c>
+      <c r="AL17">
+        <v>1.33</v>
+      </c>
+      <c r="AM17">
+        <v>1.53</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>3</v>
+      </c>
+      <c r="AP17">
+        <v>1</v>
+      </c>
+      <c r="AQ17">
+        <v>2</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>1.32</v>
+      </c>
+      <c r="AT17">
+        <v>1.32</v>
+      </c>
+      <c r="AU17">
+        <v>5</v>
+      </c>
+      <c r="AV17">
+        <v>3</v>
+      </c>
+      <c r="AW17">
+        <v>3</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>8</v>
+      </c>
+      <c r="AZ17">
+        <v>3</v>
+      </c>
+      <c r="BA17">
+        <v>7</v>
+      </c>
+      <c r="BB17">
+        <v>5</v>
+      </c>
+      <c r="BC17">
+        <v>12</v>
+      </c>
+      <c r="BD17">
+        <v>1.95</v>
+      </c>
+      <c r="BE17">
+        <v>6.6</v>
+      </c>
+      <c r="BF17">
+        <v>2.12</v>
+      </c>
+      <c r="BG17">
+        <v>1.38</v>
+      </c>
+      <c r="BH17">
+        <v>2.7</v>
+      </c>
+      <c r="BI17">
+        <v>1.71</v>
+      </c>
+      <c r="BJ17">
+        <v>1.95</v>
+      </c>
+      <c r="BK17">
+        <v>2.25</v>
+      </c>
+      <c r="BL17">
+        <v>1.53</v>
+      </c>
+      <c r="BM17">
+        <v>3.1</v>
+      </c>
+      <c r="BN17">
+        <v>1.3</v>
+      </c>
+      <c r="BO17">
+        <v>4.5</v>
+      </c>
+      <c r="BP17">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="111">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -341,6 +341,12 @@
   </si>
   <si>
     <t>['50']</t>
+  </si>
+  <si>
+    <t>['85']</t>
+  </si>
+  <si>
+    <t>['45+4']</t>
   </si>
 </sst>
 </file>
@@ -702,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP17"/>
+  <dimension ref="A1:BP20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2478,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -4205,6 +4211,624 @@
       </c>
       <c r="BP17">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7821454</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45702.79166666666</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>90</v>
+      </c>
+      <c r="P18" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q18">
+        <v>3.25</v>
+      </c>
+      <c r="R18">
+        <v>1.91</v>
+      </c>
+      <c r="S18">
+        <v>4</v>
+      </c>
+      <c r="T18">
+        <v>1.62</v>
+      </c>
+      <c r="U18">
+        <v>2.2</v>
+      </c>
+      <c r="V18">
+        <v>4</v>
+      </c>
+      <c r="W18">
+        <v>1.22</v>
+      </c>
+      <c r="X18">
+        <v>13</v>
+      </c>
+      <c r="Y18">
+        <v>1.04</v>
+      </c>
+      <c r="Z18">
+        <v>2.2</v>
+      </c>
+      <c r="AA18">
+        <v>3.2</v>
+      </c>
+      <c r="AB18">
+        <v>3.3</v>
+      </c>
+      <c r="AC18">
+        <v>1.06</v>
+      </c>
+      <c r="AD18">
+        <v>6.1</v>
+      </c>
+      <c r="AE18">
+        <v>1.5</v>
+      </c>
+      <c r="AF18">
+        <v>2.3</v>
+      </c>
+      <c r="AG18">
+        <v>2.35</v>
+      </c>
+      <c r="AH18">
+        <v>1.52</v>
+      </c>
+      <c r="AI18">
+        <v>2.25</v>
+      </c>
+      <c r="AJ18">
+        <v>1.57</v>
+      </c>
+      <c r="AK18">
+        <v>1.34</v>
+      </c>
+      <c r="AL18">
+        <v>1.37</v>
+      </c>
+      <c r="AM18">
+        <v>1.53</v>
+      </c>
+      <c r="AN18">
+        <v>1</v>
+      </c>
+      <c r="AO18">
+        <v>3</v>
+      </c>
+      <c r="AP18">
+        <v>0.5</v>
+      </c>
+      <c r="AQ18">
+        <v>3</v>
+      </c>
+      <c r="AR18">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS18">
+        <v>1.5</v>
+      </c>
+      <c r="AT18">
+        <v>2.44</v>
+      </c>
+      <c r="AU18">
+        <v>6</v>
+      </c>
+      <c r="AV18">
+        <v>3</v>
+      </c>
+      <c r="AW18">
+        <v>1</v>
+      </c>
+      <c r="AX18">
+        <v>4</v>
+      </c>
+      <c r="AY18">
+        <v>7</v>
+      </c>
+      <c r="AZ18">
+        <v>7</v>
+      </c>
+      <c r="BA18">
+        <v>3</v>
+      </c>
+      <c r="BB18">
+        <v>4</v>
+      </c>
+      <c r="BC18">
+        <v>7</v>
+      </c>
+      <c r="BD18">
+        <v>1.9</v>
+      </c>
+      <c r="BE18">
+        <v>6.1</v>
+      </c>
+      <c r="BF18">
+        <v>2.15</v>
+      </c>
+      <c r="BG18">
+        <v>1.54</v>
+      </c>
+      <c r="BH18">
+        <v>2.28</v>
+      </c>
+      <c r="BI18">
+        <v>1.92</v>
+      </c>
+      <c r="BJ18">
+        <v>1.77</v>
+      </c>
+      <c r="BK18">
+        <v>2.45</v>
+      </c>
+      <c r="BL18">
+        <v>1.48</v>
+      </c>
+      <c r="BM18">
+        <v>3.3</v>
+      </c>
+      <c r="BN18">
+        <v>1.28</v>
+      </c>
+      <c r="BO18">
+        <v>4.35</v>
+      </c>
+      <c r="BP18">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7821455</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45702.88541666666</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19" t="s">
+        <v>98</v>
+      </c>
+      <c r="P19" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q19">
+        <v>3.35</v>
+      </c>
+      <c r="R19">
+        <v>2.02</v>
+      </c>
+      <c r="S19">
+        <v>3.2</v>
+      </c>
+      <c r="T19">
+        <v>1.48</v>
+      </c>
+      <c r="U19">
+        <v>2.5</v>
+      </c>
+      <c r="V19">
+        <v>3.24</v>
+      </c>
+      <c r="W19">
+        <v>1.33</v>
+      </c>
+      <c r="X19">
+        <v>9.5</v>
+      </c>
+      <c r="Y19">
+        <v>1.04</v>
+      </c>
+      <c r="Z19">
+        <v>2.65</v>
+      </c>
+      <c r="AA19">
+        <v>3.32</v>
+      </c>
+      <c r="AB19">
+        <v>2.55</v>
+      </c>
+      <c r="AC19">
+        <v>1.05</v>
+      </c>
+      <c r="AD19">
+        <v>8</v>
+      </c>
+      <c r="AE19">
+        <v>1.37</v>
+      </c>
+      <c r="AF19">
+        <v>2.95</v>
+      </c>
+      <c r="AG19">
+        <v>2</v>
+      </c>
+      <c r="AH19">
+        <v>1.67</v>
+      </c>
+      <c r="AI19">
+        <v>1.85</v>
+      </c>
+      <c r="AJ19">
+        <v>1.86</v>
+      </c>
+      <c r="AK19">
+        <v>1.45</v>
+      </c>
+      <c r="AL19">
+        <v>1.31</v>
+      </c>
+      <c r="AM19">
+        <v>1.44</v>
+      </c>
+      <c r="AN19">
+        <v>1</v>
+      </c>
+      <c r="AO19">
+        <v>1</v>
+      </c>
+      <c r="AP19">
+        <v>1</v>
+      </c>
+      <c r="AQ19">
+        <v>1</v>
+      </c>
+      <c r="AR19">
+        <v>1.03</v>
+      </c>
+      <c r="AS19">
+        <v>1.07</v>
+      </c>
+      <c r="AT19">
+        <v>2.1</v>
+      </c>
+      <c r="AU19">
+        <v>6</v>
+      </c>
+      <c r="AV19">
+        <v>6</v>
+      </c>
+      <c r="AW19">
+        <v>3</v>
+      </c>
+      <c r="AX19">
+        <v>4</v>
+      </c>
+      <c r="AY19">
+        <v>9</v>
+      </c>
+      <c r="AZ19">
+        <v>10</v>
+      </c>
+      <c r="BA19">
+        <v>4</v>
+      </c>
+      <c r="BB19">
+        <v>3</v>
+      </c>
+      <c r="BC19">
+        <v>7</v>
+      </c>
+      <c r="BD19">
+        <v>1.98</v>
+      </c>
+      <c r="BE19">
+        <v>6.4</v>
+      </c>
+      <c r="BF19">
+        <v>2</v>
+      </c>
+      <c r="BG19">
+        <v>1.46</v>
+      </c>
+      <c r="BH19">
+        <v>2.5</v>
+      </c>
+      <c r="BI19">
+        <v>1.76</v>
+      </c>
+      <c r="BJ19">
+        <v>1.93</v>
+      </c>
+      <c r="BK19">
+        <v>2.23</v>
+      </c>
+      <c r="BL19">
+        <v>1.57</v>
+      </c>
+      <c r="BM19">
+        <v>2.9</v>
+      </c>
+      <c r="BN19">
+        <v>1.35</v>
+      </c>
+      <c r="BO19">
+        <v>3.8</v>
+      </c>
+      <c r="BP19">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7821457</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45703.70833333334</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>90</v>
+      </c>
+      <c r="P20" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q20">
+        <v>3.25</v>
+      </c>
+      <c r="R20">
+        <v>1.91</v>
+      </c>
+      <c r="S20">
+        <v>4</v>
+      </c>
+      <c r="T20">
+        <v>1.57</v>
+      </c>
+      <c r="U20">
+        <v>2.25</v>
+      </c>
+      <c r="V20">
+        <v>3.75</v>
+      </c>
+      <c r="W20">
+        <v>1.25</v>
+      </c>
+      <c r="X20">
+        <v>13</v>
+      </c>
+      <c r="Y20">
+        <v>1.04</v>
+      </c>
+      <c r="Z20">
+        <v>2.53</v>
+      </c>
+      <c r="AA20">
+        <v>2.91</v>
+      </c>
+      <c r="AB20">
+        <v>3.03</v>
+      </c>
+      <c r="AC20">
+        <v>1.12</v>
+      </c>
+      <c r="AD20">
+        <v>6.01</v>
+      </c>
+      <c r="AE20">
+        <v>1.5</v>
+      </c>
+      <c r="AF20">
+        <v>2.4</v>
+      </c>
+      <c r="AG20">
+        <v>2.3</v>
+      </c>
+      <c r="AH20">
+        <v>1.5</v>
+      </c>
+      <c r="AI20">
+        <v>2.2</v>
+      </c>
+      <c r="AJ20">
+        <v>1.62</v>
+      </c>
+      <c r="AK20">
+        <v>1.35</v>
+      </c>
+      <c r="AL20">
+        <v>1.36</v>
+      </c>
+      <c r="AM20">
+        <v>1.55</v>
+      </c>
+      <c r="AN20">
+        <v>1</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>1</v>
+      </c>
+      <c r="AQ20">
+        <v>1</v>
+      </c>
+      <c r="AR20">
+        <v>1.31</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>1.31</v>
+      </c>
+      <c r="AU20">
+        <v>8</v>
+      </c>
+      <c r="AV20">
+        <v>5</v>
+      </c>
+      <c r="AW20">
+        <v>7</v>
+      </c>
+      <c r="AX20">
+        <v>5</v>
+      </c>
+      <c r="AY20">
+        <v>15</v>
+      </c>
+      <c r="AZ20">
+        <v>10</v>
+      </c>
+      <c r="BA20">
+        <v>6</v>
+      </c>
+      <c r="BB20">
+        <v>6</v>
+      </c>
+      <c r="BC20">
+        <v>12</v>
+      </c>
+      <c r="BD20">
+        <v>1.88</v>
+      </c>
+      <c r="BE20">
+        <v>5.8</v>
+      </c>
+      <c r="BF20">
+        <v>2.17</v>
+      </c>
+      <c r="BG20">
+        <v>1.52</v>
+      </c>
+      <c r="BH20">
+        <v>2.32</v>
+      </c>
+      <c r="BI20">
+        <v>1.88</v>
+      </c>
+      <c r="BJ20">
+        <v>1.81</v>
+      </c>
+      <c r="BK20">
+        <v>2.4</v>
+      </c>
+      <c r="BL20">
+        <v>1.49</v>
+      </c>
+      <c r="BM20">
+        <v>3.15</v>
+      </c>
+      <c r="BN20">
+        <v>1.29</v>
+      </c>
+      <c r="BO20">
+        <v>4.3</v>
+      </c>
+      <c r="BP20">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="114">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -313,6 +313,12 @@
     <t>['68']</t>
   </si>
   <si>
+    <t>['48']</t>
+  </si>
+  <si>
+    <t>['45', '84']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -346,7 +352,10 @@
     <t>['85']</t>
   </si>
   <si>
-    <t>['45+4']</t>
+    <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['51']</t>
   </si>
 </sst>
 </file>
@@ -708,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP20"/>
+  <dimension ref="A1:BP22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1251,7 +1260,7 @@
         <v>3</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1376,7 +1385,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1582,7 +1591,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1788,7 +1797,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2281,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2406,7 +2415,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2612,7 +2621,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3024,7 +3033,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3230,7 +3239,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3436,7 +3445,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q14">
         <v>3.78</v>
@@ -3642,7 +3651,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4054,7 +4063,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4260,7 +4269,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -4466,7 +4475,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4829,6 +4838,418 @@
       </c>
       <c r="BP20">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7821451</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45703.8125</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" t="s">
+        <v>83</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+      <c r="O21" t="s">
+        <v>99</v>
+      </c>
+      <c r="P21" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q21">
+        <v>1.85</v>
+      </c>
+      <c r="R21">
+        <v>2.3</v>
+      </c>
+      <c r="S21">
+        <v>8</v>
+      </c>
+      <c r="T21">
+        <v>1.36</v>
+      </c>
+      <c r="U21">
+        <v>2.9</v>
+      </c>
+      <c r="V21">
+        <v>2.75</v>
+      </c>
+      <c r="W21">
+        <v>1.4</v>
+      </c>
+      <c r="X21">
+        <v>7</v>
+      </c>
+      <c r="Y21">
+        <v>1.1</v>
+      </c>
+      <c r="Z21">
+        <v>1.36</v>
+      </c>
+      <c r="AA21">
+        <v>4.6</v>
+      </c>
+      <c r="AB21">
+        <v>8.6</v>
+      </c>
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AD21">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE21">
+        <v>1.23</v>
+      </c>
+      <c r="AF21">
+        <v>3.42</v>
+      </c>
+      <c r="AG21">
+        <v>1.91</v>
+      </c>
+      <c r="AH21">
+        <v>1.83</v>
+      </c>
+      <c r="AI21">
+        <v>2.1</v>
+      </c>
+      <c r="AJ21">
+        <v>1.67</v>
+      </c>
+      <c r="AK21">
+        <v>1.07</v>
+      </c>
+      <c r="AL21">
+        <v>1.2</v>
+      </c>
+      <c r="AM21">
+        <v>3</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>1</v>
+      </c>
+      <c r="AQ21">
+        <v>0.5</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>1.26</v>
+      </c>
+      <c r="AT21">
+        <v>1.26</v>
+      </c>
+      <c r="AU21">
+        <v>4</v>
+      </c>
+      <c r="AV21">
+        <v>3</v>
+      </c>
+      <c r="AW21">
+        <v>9</v>
+      </c>
+      <c r="AX21">
+        <v>3</v>
+      </c>
+      <c r="AY21">
+        <v>13</v>
+      </c>
+      <c r="AZ21">
+        <v>6</v>
+      </c>
+      <c r="BA21">
+        <v>5</v>
+      </c>
+      <c r="BB21">
+        <v>3</v>
+      </c>
+      <c r="BC21">
+        <v>8</v>
+      </c>
+      <c r="BD21">
+        <v>1.29</v>
+      </c>
+      <c r="BE21">
+        <v>7</v>
+      </c>
+      <c r="BF21">
+        <v>3.95</v>
+      </c>
+      <c r="BG21">
+        <v>1.42</v>
+      </c>
+      <c r="BH21">
+        <v>2.65</v>
+      </c>
+      <c r="BI21">
+        <v>1.7</v>
+      </c>
+      <c r="BJ21">
+        <v>2.02</v>
+      </c>
+      <c r="BK21">
+        <v>2.1</v>
+      </c>
+      <c r="BL21">
+        <v>1.64</v>
+      </c>
+      <c r="BM21">
+        <v>2.7</v>
+      </c>
+      <c r="BN21">
+        <v>1.4</v>
+      </c>
+      <c r="BO21">
+        <v>3.55</v>
+      </c>
+      <c r="BP21">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7821453</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45703.90625</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>2</v>
+      </c>
+      <c r="O22" t="s">
+        <v>100</v>
+      </c>
+      <c r="P22" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q22">
+        <v>2.95</v>
+      </c>
+      <c r="R22">
+        <v>1.95</v>
+      </c>
+      <c r="S22">
+        <v>3.7</v>
+      </c>
+      <c r="T22">
+        <v>1.49</v>
+      </c>
+      <c r="U22">
+        <v>2.4</v>
+      </c>
+      <c r="V22">
+        <v>3.3</v>
+      </c>
+      <c r="W22">
+        <v>1.28</v>
+      </c>
+      <c r="X22">
+        <v>9.25</v>
+      </c>
+      <c r="Y22">
+        <v>1.05</v>
+      </c>
+      <c r="Z22">
+        <v>2.36</v>
+      </c>
+      <c r="AA22">
+        <v>3.06</v>
+      </c>
+      <c r="AB22">
+        <v>3.13</v>
+      </c>
+      <c r="AC22">
+        <v>1.03</v>
+      </c>
+      <c r="AD22">
+        <v>7.4</v>
+      </c>
+      <c r="AE22">
+        <v>1.45</v>
+      </c>
+      <c r="AF22">
+        <v>2.65</v>
+      </c>
+      <c r="AG22">
+        <v>2.35</v>
+      </c>
+      <c r="AH22">
+        <v>1.52</v>
+      </c>
+      <c r="AI22">
+        <v>2.05</v>
+      </c>
+      <c r="AJ22">
+        <v>1.68</v>
+      </c>
+      <c r="AK22">
+        <v>1.34</v>
+      </c>
+      <c r="AL22">
+        <v>1.34</v>
+      </c>
+      <c r="AM22">
+        <v>1.58</v>
+      </c>
+      <c r="AN22">
+        <v>3</v>
+      </c>
+      <c r="AO22">
+        <v>1</v>
+      </c>
+      <c r="AP22">
+        <v>3</v>
+      </c>
+      <c r="AQ22">
+        <v>0.5</v>
+      </c>
+      <c r="AR22">
+        <v>1.38</v>
+      </c>
+      <c r="AS22">
+        <v>1.35</v>
+      </c>
+      <c r="AT22">
+        <v>2.73</v>
+      </c>
+      <c r="AU22">
+        <v>7</v>
+      </c>
+      <c r="AV22">
+        <v>3</v>
+      </c>
+      <c r="AW22">
+        <v>7</v>
+      </c>
+      <c r="AX22">
+        <v>13</v>
+      </c>
+      <c r="AY22">
+        <v>14</v>
+      </c>
+      <c r="AZ22">
+        <v>16</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>2</v>
+      </c>
+      <c r="BC22">
+        <v>2</v>
+      </c>
+      <c r="BD22">
+        <v>1.73</v>
+      </c>
+      <c r="BE22">
+        <v>6.25</v>
+      </c>
+      <c r="BF22">
+        <v>2.4</v>
+      </c>
+      <c r="BG22">
+        <v>1.43</v>
+      </c>
+      <c r="BH22">
+        <v>2.55</v>
+      </c>
+      <c r="BI22">
+        <v>1.72</v>
+      </c>
+      <c r="BJ22">
+        <v>1.98</v>
+      </c>
+      <c r="BK22">
+        <v>2.15</v>
+      </c>
+      <c r="BL22">
+        <v>1.61</v>
+      </c>
+      <c r="BM22">
+        <v>2.8</v>
+      </c>
+      <c r="BN22">
+        <v>1.38</v>
+      </c>
+      <c r="BO22">
+        <v>3.65</v>
+      </c>
+      <c r="BP22">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="115">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -319,6 +319,9 @@
     <t>['45', '84']</t>
   </si>
   <si>
+    <t>['52']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -340,9 +343,6 @@
     <t>['90']</t>
   </si>
   <si>
-    <t>['52']</t>
-  </si>
-  <si>
     <t>['30', '38']</t>
   </si>
   <si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>['51']</t>
+  </si>
+  <si>
+    <t>['11', '17', '35', '63', '84']</t>
   </si>
 </sst>
 </file>
@@ -717,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP22"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1385,7 +1388,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1591,7 +1594,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1797,7 +1800,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2084,7 +2087,7 @@
         <v>3</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2415,7 +2418,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2621,7 +2624,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3033,7 +3036,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3239,7 +3242,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3445,7 +3448,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="Q14">
         <v>3.78</v>
@@ -5250,6 +5253,212 @@
       </c>
       <c r="BP22">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7821450</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45704.70833333334</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23">
+        <v>3</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>5</v>
+      </c>
+      <c r="N23">
+        <v>6</v>
+      </c>
+      <c r="O23" t="s">
+        <v>101</v>
+      </c>
+      <c r="P23" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q23">
+        <v>8.5</v>
+      </c>
+      <c r="R23">
+        <v>2.38</v>
+      </c>
+      <c r="S23">
+        <v>1.83</v>
+      </c>
+      <c r="T23">
+        <v>1.36</v>
+      </c>
+      <c r="U23">
+        <v>3</v>
+      </c>
+      <c r="V23">
+        <v>2.75</v>
+      </c>
+      <c r="W23">
+        <v>1.4</v>
+      </c>
+      <c r="X23">
+        <v>7</v>
+      </c>
+      <c r="Y23">
+        <v>1.1</v>
+      </c>
+      <c r="Z23">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA23">
+        <v>4.8</v>
+      </c>
+      <c r="AB23">
+        <v>1.35</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>1.83</v>
+      </c>
+      <c r="AH23">
+        <v>1.91</v>
+      </c>
+      <c r="AI23">
+        <v>2.2</v>
+      </c>
+      <c r="AJ23">
+        <v>1.62</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>1.5</v>
+      </c>
+      <c r="AR23">
+        <v>1.13</v>
+      </c>
+      <c r="AS23">
+        <v>1.15</v>
+      </c>
+      <c r="AT23">
+        <v>2.28</v>
+      </c>
+      <c r="AU23">
+        <v>4</v>
+      </c>
+      <c r="AV23">
+        <v>11</v>
+      </c>
+      <c r="AW23">
+        <v>3</v>
+      </c>
+      <c r="AX23">
+        <v>2</v>
+      </c>
+      <c r="AY23">
+        <v>7</v>
+      </c>
+      <c r="AZ23">
+        <v>13</v>
+      </c>
+      <c r="BA23">
+        <v>4</v>
+      </c>
+      <c r="BB23">
+        <v>6</v>
+      </c>
+      <c r="BC23">
+        <v>10</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="119">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -322,6 +322,12 @@
     <t>['52']</t>
   </si>
   <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['38', '72']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -359,6 +365,12 @@
   </si>
   <si>
     <t>['11', '17', '35', '63', '84']</t>
+  </si>
+  <si>
+    <t>['33', '88']</t>
+  </si>
+  <si>
+    <t>['36']</t>
   </si>
 </sst>
 </file>
@@ -720,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP23"/>
+  <dimension ref="A1:BP25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1057,7 +1069,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1388,7 +1400,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1594,7 +1606,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1800,7 +1812,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2418,7 +2430,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2499,7 +2511,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2624,7 +2636,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3036,7 +3048,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3242,7 +3254,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3654,7 +3666,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4066,7 +4078,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4272,7 +4284,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -4478,7 +4490,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4890,7 +4902,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5302,7 +5314,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5459,6 +5471,418 @@
       </c>
       <c r="BP23">
         <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7821456</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45704.8125</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24" t="s">
+        <v>82</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>2</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24">
+        <v>3</v>
+      </c>
+      <c r="O24" t="s">
+        <v>102</v>
+      </c>
+      <c r="P24" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q24">
+        <v>3.1</v>
+      </c>
+      <c r="R24">
+        <v>1.95</v>
+      </c>
+      <c r="S24">
+        <v>4</v>
+      </c>
+      <c r="T24">
+        <v>1.53</v>
+      </c>
+      <c r="U24">
+        <v>2.38</v>
+      </c>
+      <c r="V24">
+        <v>3.75</v>
+      </c>
+      <c r="W24">
+        <v>1.25</v>
+      </c>
+      <c r="X24">
+        <v>11</v>
+      </c>
+      <c r="Y24">
+        <v>1.05</v>
+      </c>
+      <c r="Z24">
+        <v>2.31</v>
+      </c>
+      <c r="AA24">
+        <v>3.3</v>
+      </c>
+      <c r="AB24">
+        <v>3</v>
+      </c>
+      <c r="AC24">
+        <v>1.09</v>
+      </c>
+      <c r="AD24">
+        <v>6.75</v>
+      </c>
+      <c r="AE24">
+        <v>1.46</v>
+      </c>
+      <c r="AF24">
+        <v>2.5</v>
+      </c>
+      <c r="AG24">
+        <v>2.3</v>
+      </c>
+      <c r="AH24">
+        <v>1.5</v>
+      </c>
+      <c r="AI24">
+        <v>2.1</v>
+      </c>
+      <c r="AJ24">
+        <v>1.67</v>
+      </c>
+      <c r="AK24">
+        <v>1.33</v>
+      </c>
+      <c r="AL24">
+        <v>1.34</v>
+      </c>
+      <c r="AM24">
+        <v>1.6</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>1</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>2</v>
+      </c>
+      <c r="AR24">
+        <v>1.43</v>
+      </c>
+      <c r="AS24">
+        <v>1.58</v>
+      </c>
+      <c r="AT24">
+        <v>3.01</v>
+      </c>
+      <c r="AU24">
+        <v>5</v>
+      </c>
+      <c r="AV24">
+        <v>7</v>
+      </c>
+      <c r="AW24">
+        <v>3</v>
+      </c>
+      <c r="AX24">
+        <v>2</v>
+      </c>
+      <c r="AY24">
+        <v>8</v>
+      </c>
+      <c r="AZ24">
+        <v>9</v>
+      </c>
+      <c r="BA24">
+        <v>1</v>
+      </c>
+      <c r="BB24">
+        <v>8</v>
+      </c>
+      <c r="BC24">
+        <v>9</v>
+      </c>
+      <c r="BD24">
+        <v>1.95</v>
+      </c>
+      <c r="BE24">
+        <v>7.5</v>
+      </c>
+      <c r="BF24">
+        <v>2.1</v>
+      </c>
+      <c r="BG24">
+        <v>1.42</v>
+      </c>
+      <c r="BH24">
+        <v>2.65</v>
+      </c>
+      <c r="BI24">
+        <v>1.73</v>
+      </c>
+      <c r="BJ24">
+        <v>2.03</v>
+      </c>
+      <c r="BK24">
+        <v>2.2</v>
+      </c>
+      <c r="BL24">
+        <v>1.63</v>
+      </c>
+      <c r="BM24">
+        <v>2.83</v>
+      </c>
+      <c r="BN24">
+        <v>1.37</v>
+      </c>
+      <c r="BO24">
+        <v>3.85</v>
+      </c>
+      <c r="BP24">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7821452</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45704.90625</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" t="s">
+        <v>81</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>2</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>3</v>
+      </c>
+      <c r="O25" t="s">
+        <v>103</v>
+      </c>
+      <c r="P25" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q25">
+        <v>2.63</v>
+      </c>
+      <c r="R25">
+        <v>2.1</v>
+      </c>
+      <c r="S25">
+        <v>4.5</v>
+      </c>
+      <c r="T25">
+        <v>1.44</v>
+      </c>
+      <c r="U25">
+        <v>2.63</v>
+      </c>
+      <c r="V25">
+        <v>3.25</v>
+      </c>
+      <c r="W25">
+        <v>1.33</v>
+      </c>
+      <c r="X25">
+        <v>9</v>
+      </c>
+      <c r="Y25">
+        <v>1.07</v>
+      </c>
+      <c r="Z25">
+        <v>2</v>
+      </c>
+      <c r="AA25">
+        <v>3.45</v>
+      </c>
+      <c r="AB25">
+        <v>3.58</v>
+      </c>
+      <c r="AC25">
+        <v>1.07</v>
+      </c>
+      <c r="AD25">
+        <v>7.75</v>
+      </c>
+      <c r="AE25">
+        <v>1.36</v>
+      </c>
+      <c r="AF25">
+        <v>3.1</v>
+      </c>
+      <c r="AG25">
+        <v>2.27</v>
+      </c>
+      <c r="AH25">
+        <v>1.56</v>
+      </c>
+      <c r="AI25">
+        <v>1.91</v>
+      </c>
+      <c r="AJ25">
+        <v>1.8</v>
+      </c>
+      <c r="AK25">
+        <v>1.26</v>
+      </c>
+      <c r="AL25">
+        <v>1.27</v>
+      </c>
+      <c r="AM25">
+        <v>1.75</v>
+      </c>
+      <c r="AN25">
+        <v>3</v>
+      </c>
+      <c r="AO25">
+        <v>1</v>
+      </c>
+      <c r="AP25">
+        <v>3</v>
+      </c>
+      <c r="AQ25">
+        <v>0.5</v>
+      </c>
+      <c r="AR25">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AS25">
+        <v>1.16</v>
+      </c>
+      <c r="AT25">
+        <v>1.97</v>
+      </c>
+      <c r="AU25">
+        <v>9</v>
+      </c>
+      <c r="AV25">
+        <v>3</v>
+      </c>
+      <c r="AW25">
+        <v>7</v>
+      </c>
+      <c r="AX25">
+        <v>3</v>
+      </c>
+      <c r="AY25">
+        <v>16</v>
+      </c>
+      <c r="AZ25">
+        <v>6</v>
+      </c>
+      <c r="BA25">
+        <v>6</v>
+      </c>
+      <c r="BB25">
+        <v>6</v>
+      </c>
+      <c r="BC25">
+        <v>12</v>
+      </c>
+      <c r="BD25">
+        <v>1.71</v>
+      </c>
+      <c r="BE25">
+        <v>6.25</v>
+      </c>
+      <c r="BF25">
+        <v>2.4</v>
+      </c>
+      <c r="BG25">
+        <v>1.47</v>
+      </c>
+      <c r="BH25">
+        <v>2.48</v>
+      </c>
+      <c r="BI25">
+        <v>1.77</v>
+      </c>
+      <c r="BJ25">
+        <v>1.92</v>
+      </c>
+      <c r="BK25">
+        <v>2.23</v>
+      </c>
+      <c r="BL25">
+        <v>1.56</v>
+      </c>
+      <c r="BM25">
+        <v>2.9</v>
+      </c>
+      <c r="BN25">
+        <v>1.34</v>
+      </c>
+      <c r="BO25">
+        <v>3.9</v>
+      </c>
+      <c r="BP25">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -322,10 +322,10 @@
     <t>['52']</t>
   </si>
   <si>
-    <t>['42']</t>
-  </si>
-  <si>
-    <t>['38', '72']</t>
+    <t>['41']</t>
+  </si>
+  <si>
+    <t>['37', '72']</t>
   </si>
   <si>
     <t>['11']</t>
@@ -364,13 +364,13 @@
     <t>['51']</t>
   </si>
   <si>
-    <t>['11', '17', '35', '63', '84']</t>
-  </si>
-  <si>
-    <t>['33', '88']</t>
-  </si>
-  <si>
-    <t>['36']</t>
+    <t>['10', '16', '35', '63', '84']</t>
+  </si>
+  <si>
+    <t>['32', '88']</t>
+  </si>
+  <si>
+    <t>['35']</t>
   </si>
 </sst>
 </file>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="121">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -328,6 +328,9 @@
     <t>['37', '72']</t>
   </si>
   <si>
+    <t>['15', '54', '75']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -371,6 +374,9 @@
   </si>
   <si>
     <t>['35']</t>
+  </si>
+  <si>
+    <t>['56']</t>
   </si>
 </sst>
 </file>
@@ -732,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1400,7 +1406,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1606,7 +1612,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1812,7 +1818,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2430,7 +2436,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2636,7 +2642,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3048,7 +3054,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3254,7 +3260,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3332,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
         <v>3</v>
@@ -3666,7 +3672,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -3953,7 +3959,7 @@
         <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4078,7 +4084,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4284,7 +4290,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -4490,7 +4496,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4902,7 +4908,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5314,7 +5320,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5520,7 +5526,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5726,7 +5732,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5883,6 +5889,212 @@
       </c>
       <c r="BP25">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7821463</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45709.70833333334</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>3</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>4</v>
+      </c>
+      <c r="O26" t="s">
+        <v>104</v>
+      </c>
+      <c r="P26" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q26">
+        <v>3.25</v>
+      </c>
+      <c r="R26">
+        <v>1.91</v>
+      </c>
+      <c r="S26">
+        <v>4</v>
+      </c>
+      <c r="T26">
+        <v>1.57</v>
+      </c>
+      <c r="U26">
+        <v>2.25</v>
+      </c>
+      <c r="V26">
+        <v>3.75</v>
+      </c>
+      <c r="W26">
+        <v>1.25</v>
+      </c>
+      <c r="X26">
+        <v>13</v>
+      </c>
+      <c r="Y26">
+        <v>1.04</v>
+      </c>
+      <c r="Z26">
+        <v>2.41</v>
+      </c>
+      <c r="AA26">
+        <v>2.75</v>
+      </c>
+      <c r="AB26">
+        <v>3.45</v>
+      </c>
+      <c r="AC26">
+        <v>1.01</v>
+      </c>
+      <c r="AD26">
+        <v>8.5</v>
+      </c>
+      <c r="AE26">
+        <v>1.36</v>
+      </c>
+      <c r="AF26">
+        <v>2.7</v>
+      </c>
+      <c r="AG26">
+        <v>2.25</v>
+      </c>
+      <c r="AH26">
+        <v>1.53</v>
+      </c>
+      <c r="AI26">
+        <v>2.1</v>
+      </c>
+      <c r="AJ26">
+        <v>1.67</v>
+      </c>
+      <c r="AK26">
+        <v>1.44</v>
+      </c>
+      <c r="AL26">
+        <v>1.33</v>
+      </c>
+      <c r="AM26">
+        <v>1.46</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>1</v>
+      </c>
+      <c r="AP26">
+        <v>1.5</v>
+      </c>
+      <c r="AQ26">
+        <v>0.5</v>
+      </c>
+      <c r="AR26">
+        <v>1.13</v>
+      </c>
+      <c r="AS26">
+        <v>1.37</v>
+      </c>
+      <c r="AT26">
+        <v>2.5</v>
+      </c>
+      <c r="AU26">
+        <v>9</v>
+      </c>
+      <c r="AV26">
+        <v>4</v>
+      </c>
+      <c r="AW26">
+        <v>6</v>
+      </c>
+      <c r="AX26">
+        <v>3</v>
+      </c>
+      <c r="AY26">
+        <v>15</v>
+      </c>
+      <c r="AZ26">
+        <v>7</v>
+      </c>
+      <c r="BA26">
+        <v>5</v>
+      </c>
+      <c r="BB26">
+        <v>6</v>
+      </c>
+      <c r="BC26">
+        <v>11</v>
+      </c>
+      <c r="BD26">
+        <v>2.05</v>
+      </c>
+      <c r="BE26">
+        <v>6.1</v>
+      </c>
+      <c r="BF26">
+        <v>1.98</v>
+      </c>
+      <c r="BG26">
+        <v>1.54</v>
+      </c>
+      <c r="BH26">
+        <v>2.3</v>
+      </c>
+      <c r="BI26">
+        <v>1.91</v>
+      </c>
+      <c r="BJ26">
+        <v>1.78</v>
+      </c>
+      <c r="BK26">
+        <v>2.43</v>
+      </c>
+      <c r="BL26">
+        <v>1.49</v>
+      </c>
+      <c r="BM26">
+        <v>3.2</v>
+      </c>
+      <c r="BN26">
+        <v>1.28</v>
+      </c>
+      <c r="BO26">
+        <v>3.9</v>
+      </c>
+      <c r="BP26">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="126">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -328,7 +328,16 @@
     <t>['37', '72']</t>
   </si>
   <si>
-    <t>['15', '54', '75']</t>
+    <t>['13', '53', '75']</t>
+  </si>
+  <si>
+    <t>['80', '90+6']</t>
+  </si>
+  <si>
+    <t>['41', '54']</t>
+  </si>
+  <si>
+    <t>['16', '72', '81']</t>
   </si>
   <si>
     <t>['11']</t>
@@ -377,6 +386,12 @@
   </si>
   <si>
     <t>['56']</t>
+  </si>
+  <si>
+    <t>['45+3', '49', '85']</t>
+  </si>
+  <si>
+    <t>['7', '45+3']</t>
   </si>
 </sst>
 </file>
@@ -738,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP26"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1072,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ2">
         <v>2</v>
@@ -1406,7 +1421,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1612,7 +1627,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1818,7 +1833,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2105,7 +2120,7 @@
         <v>3</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2436,7 +2451,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2642,7 +2657,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -2720,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ10">
         <v>0</v>
@@ -3054,7 +3069,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3260,7 +3275,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3341,7 +3356,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ13">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3672,7 +3687,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -3956,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ16">
         <v>0.5</v>
@@ -4084,7 +4099,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4290,7 +4305,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -4496,7 +4511,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4908,7 +4923,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5320,7 +5335,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5401,7 +5416,7 @@
         <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR23">
         <v>1.13</v>
@@ -5526,7 +5541,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5732,7 +5747,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5938,7 +5953,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6095,6 +6110,624 @@
       </c>
       <c r="BP26">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7821461</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45710.40625</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>2</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27" t="s">
+        <v>105</v>
+      </c>
+      <c r="P27" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q27">
+        <v>2.7</v>
+      </c>
+      <c r="R27">
+        <v>1.94</v>
+      </c>
+      <c r="S27">
+        <v>4.6</v>
+      </c>
+      <c r="T27">
+        <v>1.56</v>
+      </c>
+      <c r="U27">
+        <v>2.3</v>
+      </c>
+      <c r="V27">
+        <v>3.54</v>
+      </c>
+      <c r="W27">
+        <v>1.26</v>
+      </c>
+      <c r="X27">
+        <v>9.6</v>
+      </c>
+      <c r="Y27">
+        <v>1</v>
+      </c>
+      <c r="Z27">
+        <v>2.01</v>
+      </c>
+      <c r="AA27">
+        <v>3.13</v>
+      </c>
+      <c r="AB27">
+        <v>3.95</v>
+      </c>
+      <c r="AC27">
+        <v>1.1</v>
+      </c>
+      <c r="AD27">
+        <v>6.4</v>
+      </c>
+      <c r="AE27">
+        <v>1.48</v>
+      </c>
+      <c r="AF27">
+        <v>2.55</v>
+      </c>
+      <c r="AG27">
+        <v>2.37</v>
+      </c>
+      <c r="AH27">
+        <v>1.48</v>
+      </c>
+      <c r="AI27">
+        <v>2.11</v>
+      </c>
+      <c r="AJ27">
+        <v>1.66</v>
+      </c>
+      <c r="AK27">
+        <v>1.24</v>
+      </c>
+      <c r="AL27">
+        <v>1.33</v>
+      </c>
+      <c r="AM27">
+        <v>1.69</v>
+      </c>
+      <c r="AN27">
+        <v>3</v>
+      </c>
+      <c r="AO27">
+        <v>3</v>
+      </c>
+      <c r="AP27">
+        <v>3</v>
+      </c>
+      <c r="AQ27">
+        <v>1.5</v>
+      </c>
+      <c r="AR27">
+        <v>1.68</v>
+      </c>
+      <c r="AS27">
+        <v>1.05</v>
+      </c>
+      <c r="AT27">
+        <v>2.73</v>
+      </c>
+      <c r="AU27">
+        <v>3</v>
+      </c>
+      <c r="AV27">
+        <v>2</v>
+      </c>
+      <c r="AW27">
+        <v>4</v>
+      </c>
+      <c r="AX27">
+        <v>3</v>
+      </c>
+      <c r="AY27">
+        <v>7</v>
+      </c>
+      <c r="AZ27">
+        <v>5</v>
+      </c>
+      <c r="BA27">
+        <v>8</v>
+      </c>
+      <c r="BB27">
+        <v>2</v>
+      </c>
+      <c r="BC27">
+        <v>10</v>
+      </c>
+      <c r="BD27">
+        <v>1.67</v>
+      </c>
+      <c r="BE27">
+        <v>6.25</v>
+      </c>
+      <c r="BF27">
+        <v>2.5</v>
+      </c>
+      <c r="BG27">
+        <v>1.54</v>
+      </c>
+      <c r="BH27">
+        <v>2.3</v>
+      </c>
+      <c r="BI27">
+        <v>1.9</v>
+      </c>
+      <c r="BJ27">
+        <v>1.79</v>
+      </c>
+      <c r="BK27">
+        <v>2.43</v>
+      </c>
+      <c r="BL27">
+        <v>1.48</v>
+      </c>
+      <c r="BM27">
+        <v>3.2</v>
+      </c>
+      <c r="BN27">
+        <v>1.28</v>
+      </c>
+      <c r="BO27">
+        <v>4.35</v>
+      </c>
+      <c r="BP27">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>7821465</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45710.70833333334</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" t="s">
+        <v>84</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="M28">
+        <v>3</v>
+      </c>
+      <c r="N28">
+        <v>5</v>
+      </c>
+      <c r="O28" t="s">
+        <v>106</v>
+      </c>
+      <c r="P28" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q28">
+        <v>6.5</v>
+      </c>
+      <c r="R28">
+        <v>2.25</v>
+      </c>
+      <c r="S28">
+        <v>2.1</v>
+      </c>
+      <c r="T28">
+        <v>1.4</v>
+      </c>
+      <c r="U28">
+        <v>2.75</v>
+      </c>
+      <c r="V28">
+        <v>3</v>
+      </c>
+      <c r="W28">
+        <v>1.36</v>
+      </c>
+      <c r="X28">
+        <v>8</v>
+      </c>
+      <c r="Y28">
+        <v>1.08</v>
+      </c>
+      <c r="Z28">
+        <v>5.7</v>
+      </c>
+      <c r="AA28">
+        <v>3.98</v>
+      </c>
+      <c r="AB28">
+        <v>1.56</v>
+      </c>
+      <c r="AC28">
+        <v>1.05</v>
+      </c>
+      <c r="AD28">
+        <v>8.5</v>
+      </c>
+      <c r="AE28">
+        <v>1.29</v>
+      </c>
+      <c r="AF28">
+        <v>3.4</v>
+      </c>
+      <c r="AG28">
+        <v>1.92</v>
+      </c>
+      <c r="AH28">
+        <v>1.82</v>
+      </c>
+      <c r="AI28">
+        <v>2.1</v>
+      </c>
+      <c r="AJ28">
+        <v>1.67</v>
+      </c>
+      <c r="AK28">
+        <v>2.7</v>
+      </c>
+      <c r="AL28">
+        <v>1.2</v>
+      </c>
+      <c r="AM28">
+        <v>1.1</v>
+      </c>
+      <c r="AN28">
+        <v>1</v>
+      </c>
+      <c r="AO28">
+        <v>1.5</v>
+      </c>
+      <c r="AP28">
+        <v>0.5</v>
+      </c>
+      <c r="AQ28">
+        <v>2</v>
+      </c>
+      <c r="AR28">
+        <v>1.09</v>
+      </c>
+      <c r="AS28">
+        <v>1.57</v>
+      </c>
+      <c r="AT28">
+        <v>2.66</v>
+      </c>
+      <c r="AU28">
+        <v>4</v>
+      </c>
+      <c r="AV28">
+        <v>10</v>
+      </c>
+      <c r="AW28">
+        <v>8</v>
+      </c>
+      <c r="AX28">
+        <v>16</v>
+      </c>
+      <c r="AY28">
+        <v>12</v>
+      </c>
+      <c r="AZ28">
+        <v>26</v>
+      </c>
+      <c r="BA28">
+        <v>1</v>
+      </c>
+      <c r="BB28">
+        <v>7</v>
+      </c>
+      <c r="BC28">
+        <v>8</v>
+      </c>
+      <c r="BD28">
+        <v>4.15</v>
+      </c>
+      <c r="BE28">
+        <v>6.6</v>
+      </c>
+      <c r="BF28">
+        <v>1.36</v>
+      </c>
+      <c r="BG28">
+        <v>1.41</v>
+      </c>
+      <c r="BH28">
+        <v>2.65</v>
+      </c>
+      <c r="BI28">
+        <v>1.75</v>
+      </c>
+      <c r="BJ28">
+        <v>1.92</v>
+      </c>
+      <c r="BK28">
+        <v>2.35</v>
+      </c>
+      <c r="BL28">
+        <v>1.5</v>
+      </c>
+      <c r="BM28">
+        <v>3.35</v>
+      </c>
+      <c r="BN28">
+        <v>1.27</v>
+      </c>
+      <c r="BO28">
+        <v>4.35</v>
+      </c>
+      <c r="BP28">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7821459</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45710.8125</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29">
+        <v>3</v>
+      </c>
+      <c r="L29">
+        <v>3</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29">
+        <v>5</v>
+      </c>
+      <c r="O29" t="s">
+        <v>107</v>
+      </c>
+      <c r="P29" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q29">
+        <v>2.65</v>
+      </c>
+      <c r="R29">
+        <v>2</v>
+      </c>
+      <c r="S29">
+        <v>4.35</v>
+      </c>
+      <c r="T29">
+        <v>1.49</v>
+      </c>
+      <c r="U29">
+        <v>2.4</v>
+      </c>
+      <c r="V29">
+        <v>3.3</v>
+      </c>
+      <c r="W29">
+        <v>1.27</v>
+      </c>
+      <c r="X29">
+        <v>8.5</v>
+      </c>
+      <c r="Y29">
+        <v>1.04</v>
+      </c>
+      <c r="Z29">
+        <v>1.96</v>
+      </c>
+      <c r="AA29">
+        <v>3.09</v>
+      </c>
+      <c r="AB29">
+        <v>4.2</v>
+      </c>
+      <c r="AC29">
+        <v>1.07</v>
+      </c>
+      <c r="AD29">
+        <v>7</v>
+      </c>
+      <c r="AE29">
+        <v>1.44</v>
+      </c>
+      <c r="AF29">
+        <v>2.6</v>
+      </c>
+      <c r="AG29">
+        <v>2.37</v>
+      </c>
+      <c r="AH29">
+        <v>1.48</v>
+      </c>
+      <c r="AI29">
+        <v>2.04</v>
+      </c>
+      <c r="AJ29">
+        <v>1.65</v>
+      </c>
+      <c r="AK29">
+        <v>1.24</v>
+      </c>
+      <c r="AL29">
+        <v>1.34</v>
+      </c>
+      <c r="AM29">
+        <v>1.8</v>
+      </c>
+      <c r="AN29">
+        <v>2</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>2.33</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>2.06</v>
+      </c>
+      <c r="AS29">
+        <v>1.49</v>
+      </c>
+      <c r="AT29">
+        <v>3.55</v>
+      </c>
+      <c r="AU29">
+        <v>6</v>
+      </c>
+      <c r="AV29">
+        <v>4</v>
+      </c>
+      <c r="AW29">
+        <v>6</v>
+      </c>
+      <c r="AX29">
+        <v>8</v>
+      </c>
+      <c r="AY29">
+        <v>12</v>
+      </c>
+      <c r="AZ29">
+        <v>12</v>
+      </c>
+      <c r="BA29">
+        <v>9</v>
+      </c>
+      <c r="BB29">
+        <v>5</v>
+      </c>
+      <c r="BC29">
+        <v>14</v>
+      </c>
+      <c r="BD29">
+        <v>1.64</v>
+      </c>
+      <c r="BE29">
+        <v>6.25</v>
+      </c>
+      <c r="BF29">
+        <v>2.55</v>
+      </c>
+      <c r="BG29">
+        <v>1.52</v>
+      </c>
+      <c r="BH29">
+        <v>2.33</v>
+      </c>
+      <c r="BI29">
+        <v>1.88</v>
+      </c>
+      <c r="BJ29">
+        <v>1.81</v>
+      </c>
+      <c r="BK29">
+        <v>2.4</v>
+      </c>
+      <c r="BL29">
+        <v>1.5</v>
+      </c>
+      <c r="BM29">
+        <v>3.15</v>
+      </c>
+      <c r="BN29">
+        <v>1.3</v>
+      </c>
+      <c r="BO29">
+        <v>4.2</v>
+      </c>
+      <c r="BP29">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="132">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -331,13 +331,25 @@
     <t>['13', '53', '75']</t>
   </si>
   <si>
-    <t>['80', '90+6']</t>
-  </si>
-  <si>
-    <t>['41', '54']</t>
-  </si>
-  <si>
-    <t>['16', '72', '81']</t>
+    <t>['79', '90+6']</t>
+  </si>
+  <si>
+    <t>['40', '54']</t>
+  </si>
+  <si>
+    <t>['15', '72', '81']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['18']</t>
+  </si>
+  <si>
+    <t>['85']</t>
   </si>
   <si>
     <t>['11']</t>
@@ -367,9 +379,6 @@
     <t>['50']</t>
   </si>
   <si>
-    <t>['85']</t>
-  </si>
-  <si>
     <t>['45+3']</t>
   </si>
   <si>
@@ -388,10 +397,19 @@
     <t>['56']</t>
   </si>
   <si>
-    <t>['45+3', '49', '85']</t>
-  </si>
-  <si>
-    <t>['7', '45+3']</t>
+    <t>['45+2', '49', '85']</t>
+  </si>
+  <si>
+    <t>['6', '45+2']</t>
+  </si>
+  <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['3', '45+2']</t>
+  </si>
+  <si>
+    <t>['30']</t>
   </si>
 </sst>
 </file>
@@ -753,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BP33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1421,7 +1439,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1627,7 +1645,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1708,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="AQ5">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1833,7 +1851,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2451,7 +2469,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2657,7 +2675,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -2738,7 +2756,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR10">
         <v>1.56</v>
@@ -2941,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -3069,7 +3087,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3275,7 +3293,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3559,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ14">
         <v>3</v>
@@ -3687,7 +3705,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -3765,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4099,7 +4117,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4180,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="AQ17">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4305,7 +4323,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -4511,7 +4529,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4923,7 +4941,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5335,7 +5353,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5541,7 +5559,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5747,7 +5765,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5953,7 +5971,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6159,7 +6177,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6365,7 +6383,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6571,7 +6589,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6728,6 +6746,830 @@
       </c>
       <c r="BP29">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>7821458</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45711.40625</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
+      </c>
+      <c r="O30" t="s">
+        <v>108</v>
+      </c>
+      <c r="P30" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q30">
+        <v>2.4</v>
+      </c>
+      <c r="R30">
+        <v>1.91</v>
+      </c>
+      <c r="S30">
+        <v>5</v>
+      </c>
+      <c r="T30">
+        <v>1.5</v>
+      </c>
+      <c r="U30">
+        <v>2.4</v>
+      </c>
+      <c r="V30">
+        <v>3.2</v>
+      </c>
+      <c r="W30">
+        <v>1.3</v>
+      </c>
+      <c r="X30">
+        <v>8.5</v>
+      </c>
+      <c r="Y30">
+        <v>1.04</v>
+      </c>
+      <c r="Z30">
+        <v>1.79</v>
+      </c>
+      <c r="AA30">
+        <v>3.38</v>
+      </c>
+      <c r="AB30">
+        <v>4.6</v>
+      </c>
+      <c r="AC30">
+        <v>1.03</v>
+      </c>
+      <c r="AD30">
+        <v>7.7</v>
+      </c>
+      <c r="AE30">
+        <v>1.39</v>
+      </c>
+      <c r="AF30">
+        <v>2.59</v>
+      </c>
+      <c r="AG30">
+        <v>2.2</v>
+      </c>
+      <c r="AH30">
+        <v>1.53</v>
+      </c>
+      <c r="AI30">
+        <v>2.1</v>
+      </c>
+      <c r="AJ30">
+        <v>1.67</v>
+      </c>
+      <c r="AK30">
+        <v>1.22</v>
+      </c>
+      <c r="AL30">
+        <v>1.3</v>
+      </c>
+      <c r="AM30">
+        <v>1.95</v>
+      </c>
+      <c r="AN30">
+        <v>1</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>1</v>
+      </c>
+      <c r="AQ30">
+        <v>0.5</v>
+      </c>
+      <c r="AR30">
+        <v>1.6</v>
+      </c>
+      <c r="AS30">
+        <v>1.37</v>
+      </c>
+      <c r="AT30">
+        <v>2.97</v>
+      </c>
+      <c r="AU30">
+        <v>4</v>
+      </c>
+      <c r="AV30">
+        <v>4</v>
+      </c>
+      <c r="AW30">
+        <v>1</v>
+      </c>
+      <c r="AX30">
+        <v>1</v>
+      </c>
+      <c r="AY30">
+        <v>5</v>
+      </c>
+      <c r="AZ30">
+        <v>5</v>
+      </c>
+      <c r="BA30">
+        <v>9</v>
+      </c>
+      <c r="BB30">
+        <v>6</v>
+      </c>
+      <c r="BC30">
+        <v>15</v>
+      </c>
+      <c r="BD30">
+        <v>1.58</v>
+      </c>
+      <c r="BE30">
+        <v>6.25</v>
+      </c>
+      <c r="BF30">
+        <v>2.65</v>
+      </c>
+      <c r="BG30">
+        <v>1.54</v>
+      </c>
+      <c r="BH30">
+        <v>2.3</v>
+      </c>
+      <c r="BI30">
+        <v>1.92</v>
+      </c>
+      <c r="BJ30">
+        <v>1.78</v>
+      </c>
+      <c r="BK30">
+        <v>2.45</v>
+      </c>
+      <c r="BL30">
+        <v>1.48</v>
+      </c>
+      <c r="BM30">
+        <v>3.3</v>
+      </c>
+      <c r="BN30">
+        <v>1.28</v>
+      </c>
+      <c r="BO30">
+        <v>4.4</v>
+      </c>
+      <c r="BP30">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>7821460</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45711.70833333334</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" t="s">
+        <v>76</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31" t="s">
+        <v>109</v>
+      </c>
+      <c r="P31" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q31">
+        <v>3.1</v>
+      </c>
+      <c r="R31">
+        <v>1.95</v>
+      </c>
+      <c r="S31">
+        <v>4</v>
+      </c>
+      <c r="T31">
+        <v>1.53</v>
+      </c>
+      <c r="U31">
+        <v>2.38</v>
+      </c>
+      <c r="V31">
+        <v>3.75</v>
+      </c>
+      <c r="W31">
+        <v>1.25</v>
+      </c>
+      <c r="X31">
+        <v>11</v>
+      </c>
+      <c r="Y31">
+        <v>1.05</v>
+      </c>
+      <c r="Z31">
+        <v>2.25</v>
+      </c>
+      <c r="AA31">
+        <v>3.32</v>
+      </c>
+      <c r="AB31">
+        <v>3.08</v>
+      </c>
+      <c r="AC31">
+        <v>1.05</v>
+      </c>
+      <c r="AD31">
+        <v>6.65</v>
+      </c>
+      <c r="AE31">
+        <v>1.41</v>
+      </c>
+      <c r="AF31">
+        <v>2.52</v>
+      </c>
+      <c r="AG31">
+        <v>2.25</v>
+      </c>
+      <c r="AH31">
+        <v>1.53</v>
+      </c>
+      <c r="AI31">
+        <v>2</v>
+      </c>
+      <c r="AJ31">
+        <v>1.73</v>
+      </c>
+      <c r="AK31">
+        <v>1.33</v>
+      </c>
+      <c r="AL31">
+        <v>1.35</v>
+      </c>
+      <c r="AM31">
+        <v>1.58</v>
+      </c>
+      <c r="AN31">
+        <v>1</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>2</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>1.31</v>
+      </c>
+      <c r="AS31">
+        <v>1</v>
+      </c>
+      <c r="AT31">
+        <v>2.31</v>
+      </c>
+      <c r="AU31">
+        <v>7</v>
+      </c>
+      <c r="AV31">
+        <v>3</v>
+      </c>
+      <c r="AW31">
+        <v>7</v>
+      </c>
+      <c r="AX31">
+        <v>1</v>
+      </c>
+      <c r="AY31">
+        <v>14</v>
+      </c>
+      <c r="AZ31">
+        <v>4</v>
+      </c>
+      <c r="BA31">
+        <v>10</v>
+      </c>
+      <c r="BB31">
+        <v>1</v>
+      </c>
+      <c r="BC31">
+        <v>11</v>
+      </c>
+      <c r="BD31">
+        <v>1.83</v>
+      </c>
+      <c r="BE31">
+        <v>6.1</v>
+      </c>
+      <c r="BF31">
+        <v>2.2</v>
+      </c>
+      <c r="BG31">
+        <v>1.52</v>
+      </c>
+      <c r="BH31">
+        <v>2.33</v>
+      </c>
+      <c r="BI31">
+        <v>1.86</v>
+      </c>
+      <c r="BJ31">
+        <v>1.82</v>
+      </c>
+      <c r="BK31">
+        <v>2.38</v>
+      </c>
+      <c r="BL31">
+        <v>1.5</v>
+      </c>
+      <c r="BM31">
+        <v>3.15</v>
+      </c>
+      <c r="BN31">
+        <v>1.3</v>
+      </c>
+      <c r="BO31">
+        <v>4.1</v>
+      </c>
+      <c r="BP31">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>7821462</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45711.80208333334</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" t="s">
+        <v>71</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32">
+        <v>3</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>2</v>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+      <c r="O32" t="s">
+        <v>110</v>
+      </c>
+      <c r="P32" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q32">
+        <v>3.5</v>
+      </c>
+      <c r="R32">
+        <v>1.95</v>
+      </c>
+      <c r="S32">
+        <v>3.6</v>
+      </c>
+      <c r="T32">
+        <v>1.53</v>
+      </c>
+      <c r="U32">
+        <v>2.38</v>
+      </c>
+      <c r="V32">
+        <v>3.75</v>
+      </c>
+      <c r="W32">
+        <v>1.25</v>
+      </c>
+      <c r="X32">
+        <v>11</v>
+      </c>
+      <c r="Y32">
+        <v>1.05</v>
+      </c>
+      <c r="Z32">
+        <v>2.42</v>
+      </c>
+      <c r="AA32">
+        <v>3.29</v>
+      </c>
+      <c r="AB32">
+        <v>2.84</v>
+      </c>
+      <c r="AC32">
+        <v>1.05</v>
+      </c>
+      <c r="AD32">
+        <v>6.5</v>
+      </c>
+      <c r="AE32">
+        <v>1.43</v>
+      </c>
+      <c r="AF32">
+        <v>2.46</v>
+      </c>
+      <c r="AG32">
+        <v>2.25</v>
+      </c>
+      <c r="AH32">
+        <v>1.53</v>
+      </c>
+      <c r="AI32">
+        <v>2</v>
+      </c>
+      <c r="AJ32">
+        <v>1.73</v>
+      </c>
+      <c r="AK32">
+        <v>1.4</v>
+      </c>
+      <c r="AL32">
+        <v>1.34</v>
+      </c>
+      <c r="AM32">
+        <v>1.5</v>
+      </c>
+      <c r="AN32">
+        <v>3</v>
+      </c>
+      <c r="AO32">
+        <v>3</v>
+      </c>
+      <c r="AP32">
+        <v>1.5</v>
+      </c>
+      <c r="AQ32">
+        <v>3</v>
+      </c>
+      <c r="AR32">
+        <v>1.03</v>
+      </c>
+      <c r="AS32">
+        <v>0.9</v>
+      </c>
+      <c r="AT32">
+        <v>1.93</v>
+      </c>
+      <c r="AU32">
+        <v>6</v>
+      </c>
+      <c r="AV32">
+        <v>7</v>
+      </c>
+      <c r="AW32">
+        <v>10</v>
+      </c>
+      <c r="AX32">
+        <v>10</v>
+      </c>
+      <c r="AY32">
+        <v>16</v>
+      </c>
+      <c r="AZ32">
+        <v>17</v>
+      </c>
+      <c r="BA32">
+        <v>3</v>
+      </c>
+      <c r="BB32">
+        <v>6</v>
+      </c>
+      <c r="BC32">
+        <v>9</v>
+      </c>
+      <c r="BD32">
+        <v>1.96</v>
+      </c>
+      <c r="BE32">
+        <v>6.1</v>
+      </c>
+      <c r="BF32">
+        <v>2.07</v>
+      </c>
+      <c r="BG32">
+        <v>1.53</v>
+      </c>
+      <c r="BH32">
+        <v>2.3</v>
+      </c>
+      <c r="BI32">
+        <v>1.9</v>
+      </c>
+      <c r="BJ32">
+        <v>1.79</v>
+      </c>
+      <c r="BK32">
+        <v>2.4</v>
+      </c>
+      <c r="BL32">
+        <v>1.49</v>
+      </c>
+      <c r="BM32">
+        <v>3.15</v>
+      </c>
+      <c r="BN32">
+        <v>1.29</v>
+      </c>
+      <c r="BO32">
+        <v>4.35</v>
+      </c>
+      <c r="BP32">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7821464</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45711.89583333334</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>81</v>
+      </c>
+      <c r="H33" t="s">
+        <v>85</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>2</v>
+      </c>
+      <c r="O33" t="s">
+        <v>111</v>
+      </c>
+      <c r="P33" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q33">
+        <v>7</v>
+      </c>
+      <c r="R33">
+        <v>2.2</v>
+      </c>
+      <c r="S33">
+        <v>2.1</v>
+      </c>
+      <c r="T33">
+        <v>1.44</v>
+      </c>
+      <c r="U33">
+        <v>2.63</v>
+      </c>
+      <c r="V33">
+        <v>3.25</v>
+      </c>
+      <c r="W33">
+        <v>1.33</v>
+      </c>
+      <c r="X33">
+        <v>9</v>
+      </c>
+      <c r="Y33">
+        <v>1.07</v>
+      </c>
+      <c r="Z33">
+        <v>6.4</v>
+      </c>
+      <c r="AA33">
+        <v>4.1</v>
+      </c>
+      <c r="AB33">
+        <v>1.5</v>
+      </c>
+      <c r="AC33">
+        <v>1.01</v>
+      </c>
+      <c r="AD33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE33">
+        <v>1.33</v>
+      </c>
+      <c r="AF33">
+        <v>3.15</v>
+      </c>
+      <c r="AG33">
+        <v>2</v>
+      </c>
+      <c r="AH33">
+        <v>1.75</v>
+      </c>
+      <c r="AI33">
+        <v>2.2</v>
+      </c>
+      <c r="AJ33">
+        <v>1.62</v>
+      </c>
+      <c r="AK33">
+        <v>2.38</v>
+      </c>
+      <c r="AL33">
+        <v>1.22</v>
+      </c>
+      <c r="AM33">
+        <v>1.12</v>
+      </c>
+      <c r="AN33">
+        <v>0</v>
+      </c>
+      <c r="AO33">
+        <v>2</v>
+      </c>
+      <c r="AP33">
+        <v>0.5</v>
+      </c>
+      <c r="AQ33">
+        <v>1.67</v>
+      </c>
+      <c r="AR33">
+        <v>0.93</v>
+      </c>
+      <c r="AS33">
+        <v>1.05</v>
+      </c>
+      <c r="AT33">
+        <v>1.98</v>
+      </c>
+      <c r="AU33">
+        <v>5</v>
+      </c>
+      <c r="AV33">
+        <v>7</v>
+      </c>
+      <c r="AW33">
+        <v>5</v>
+      </c>
+      <c r="AX33">
+        <v>7</v>
+      </c>
+      <c r="AY33">
+        <v>10</v>
+      </c>
+      <c r="AZ33">
+        <v>14</v>
+      </c>
+      <c r="BA33">
+        <v>3</v>
+      </c>
+      <c r="BB33">
+        <v>4</v>
+      </c>
+      <c r="BC33">
+        <v>7</v>
+      </c>
+      <c r="BD33">
+        <v>3.2</v>
+      </c>
+      <c r="BE33">
+        <v>6.75</v>
+      </c>
+      <c r="BF33">
+        <v>1.42</v>
+      </c>
+      <c r="BG33">
+        <v>1.47</v>
+      </c>
+      <c r="BH33">
+        <v>2.48</v>
+      </c>
+      <c r="BI33">
+        <v>1.76</v>
+      </c>
+      <c r="BJ33">
+        <v>1.93</v>
+      </c>
+      <c r="BK33">
+        <v>2.2</v>
+      </c>
+      <c r="BL33">
+        <v>1.57</v>
+      </c>
+      <c r="BM33">
+        <v>2.9</v>
+      </c>
+      <c r="BN33">
+        <v>1.35</v>
+      </c>
+      <c r="BO33">
+        <v>3.8</v>
+      </c>
+      <c r="BP33">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="130">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -340,13 +340,10 @@
     <t>['15', '72', '81']</t>
   </si>
   <si>
-    <t>['90+5']</t>
-  </si>
-  <si>
-    <t>['38']</t>
-  </si>
-  <si>
-    <t>['18']</t>
+    <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['37']</t>
   </si>
   <si>
     <t>['85']</t>
@@ -361,9 +358,6 @@
     <t>['19']</t>
   </si>
   <si>
-    <t>['90+4']</t>
-  </si>
-  <si>
     <t>['55']</t>
   </si>
   <si>
@@ -406,10 +400,10 @@
     <t>['53']</t>
   </si>
   <si>
-    <t>['3', '45+2']</t>
-  </si>
-  <si>
-    <t>['30']</t>
+    <t>['2', '45+1']</t>
+  </si>
+  <si>
+    <t>['29']</t>
   </si>
 </sst>
 </file>
@@ -1439,7 +1433,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1645,7 +1639,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1851,7 +1845,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2469,7 +2463,7 @@
         <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -2675,7 +2669,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3087,7 +3081,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3293,7 +3287,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3705,7 +3699,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4117,7 +4111,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4323,7 +4317,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -4529,7 +4523,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4941,7 +4935,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5353,7 +5347,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5559,7 +5553,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5765,7 +5759,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5971,7 +5965,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6177,7 +6171,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6383,7 +6377,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6589,7 +6583,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6795,7 +6789,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7204,10 +7198,10 @@
         <v>3</v>
       </c>
       <c r="O32" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7410,10 +7404,10 @@
         <v>2</v>
       </c>
       <c r="O33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q33">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="134">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -349,6 +349,12 @@
     <t>['85']</t>
   </si>
   <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['55', '80']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -404,6 +410,12 @@
   </si>
   <si>
     <t>['29']</t>
+  </si>
+  <si>
+    <t>['67']</t>
+  </si>
+  <si>
+    <t>['81']</t>
   </si>
 </sst>
 </file>
@@ -765,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP33"/>
+  <dimension ref="A1:BP36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1102,7 +1114,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1305,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>0.5</v>
@@ -1433,7 +1445,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1514,7 +1526,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1639,7 +1651,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1845,7 +1857,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -1926,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="AQ6">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2129,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ7">
         <v>2</v>
@@ -2541,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9">
         <v>0.5</v>
@@ -2669,7 +2681,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3081,7 +3093,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3287,7 +3299,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3699,7 +3711,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4111,7 +4123,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4395,10 +4407,10 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR18">
         <v>0.9399999999999999</v>
@@ -4523,7 +4535,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4604,7 +4616,7 @@
         <v>1</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AR19">
         <v>1.03</v>
@@ -4935,7 +4947,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5219,7 +5231,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ22">
         <v>0.5</v>
@@ -5347,7 +5359,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5553,7 +5565,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5634,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="AQ24">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR24">
         <v>1.43</v>
@@ -5759,7 +5771,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5837,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ25">
         <v>0.5</v>
@@ -5965,7 +5977,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6171,7 +6183,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6377,7 +6389,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6583,7 +6595,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6789,7 +6801,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7201,7 +7213,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7407,7 +7419,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7564,6 +7576,624 @@
       </c>
       <c r="BP33">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>7821469</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45723.70833333334</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34" t="s">
+        <v>75</v>
+      </c>
+      <c r="H34" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>2</v>
+      </c>
+      <c r="O34" t="s">
+        <v>111</v>
+      </c>
+      <c r="P34" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q34">
+        <v>2.35</v>
+      </c>
+      <c r="R34">
+        <v>2.1</v>
+      </c>
+      <c r="S34">
+        <v>5</v>
+      </c>
+      <c r="T34">
+        <v>1.46</v>
+      </c>
+      <c r="U34">
+        <v>2.55</v>
+      </c>
+      <c r="V34">
+        <v>3.3</v>
+      </c>
+      <c r="W34">
+        <v>1.28</v>
+      </c>
+      <c r="X34">
+        <v>9</v>
+      </c>
+      <c r="Y34">
+        <v>1</v>
+      </c>
+      <c r="Z34">
+        <v>1.79</v>
+      </c>
+      <c r="AA34">
+        <v>3.45</v>
+      </c>
+      <c r="AB34">
+        <v>4.5</v>
+      </c>
+      <c r="AC34">
+        <v>1.05</v>
+      </c>
+      <c r="AD34">
+        <v>7.5</v>
+      </c>
+      <c r="AE34">
+        <v>1.36</v>
+      </c>
+      <c r="AF34">
+        <v>3</v>
+      </c>
+      <c r="AG34">
+        <v>2.15</v>
+      </c>
+      <c r="AH34">
+        <v>1.57</v>
+      </c>
+      <c r="AI34">
+        <v>1.95</v>
+      </c>
+      <c r="AJ34">
+        <v>1.77</v>
+      </c>
+      <c r="AK34">
+        <v>1.19</v>
+      </c>
+      <c r="AL34">
+        <v>1.28</v>
+      </c>
+      <c r="AM34">
+        <v>1.89</v>
+      </c>
+      <c r="AN34">
+        <v>3</v>
+      </c>
+      <c r="AO34">
+        <v>3</v>
+      </c>
+      <c r="AP34">
+        <v>2.33</v>
+      </c>
+      <c r="AQ34">
+        <v>2.33</v>
+      </c>
+      <c r="AR34">
+        <v>1.43</v>
+      </c>
+      <c r="AS34">
+        <v>1.23</v>
+      </c>
+      <c r="AT34">
+        <v>2.66</v>
+      </c>
+      <c r="AU34">
+        <v>4</v>
+      </c>
+      <c r="AV34">
+        <v>4</v>
+      </c>
+      <c r="AW34">
+        <v>3</v>
+      </c>
+      <c r="AX34">
+        <v>4</v>
+      </c>
+      <c r="AY34">
+        <v>7</v>
+      </c>
+      <c r="AZ34">
+        <v>8</v>
+      </c>
+      <c r="BA34">
+        <v>4</v>
+      </c>
+      <c r="BB34">
+        <v>5</v>
+      </c>
+      <c r="BC34">
+        <v>9</v>
+      </c>
+      <c r="BD34">
+        <v>1.4</v>
+      </c>
+      <c r="BE34">
+        <v>8.5</v>
+      </c>
+      <c r="BF34">
+        <v>3.6</v>
+      </c>
+      <c r="BG34">
+        <v>1.39</v>
+      </c>
+      <c r="BH34">
+        <v>2.77</v>
+      </c>
+      <c r="BI34">
+        <v>1.68</v>
+      </c>
+      <c r="BJ34">
+        <v>2.11</v>
+      </c>
+      <c r="BK34">
+        <v>2.11</v>
+      </c>
+      <c r="BL34">
+        <v>1.68</v>
+      </c>
+      <c r="BM34">
+        <v>2.7</v>
+      </c>
+      <c r="BN34">
+        <v>1.41</v>
+      </c>
+      <c r="BO34">
+        <v>3.65</v>
+      </c>
+      <c r="BP34">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7821470</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45723.8125</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35" t="s">
+        <v>71</v>
+      </c>
+      <c r="H35" t="s">
+        <v>79</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35" t="s">
+        <v>90</v>
+      </c>
+      <c r="P35" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q35">
+        <v>2.75</v>
+      </c>
+      <c r="R35">
+        <v>2.1</v>
+      </c>
+      <c r="S35">
+        <v>3.6</v>
+      </c>
+      <c r="T35">
+        <v>1.39</v>
+      </c>
+      <c r="U35">
+        <v>2.75</v>
+      </c>
+      <c r="V35">
+        <v>2.8</v>
+      </c>
+      <c r="W35">
+        <v>1.38</v>
+      </c>
+      <c r="X35">
+        <v>7.25</v>
+      </c>
+      <c r="Y35">
+        <v>1.08</v>
+      </c>
+      <c r="Z35">
+        <v>2.21</v>
+      </c>
+      <c r="AA35">
+        <v>3.27</v>
+      </c>
+      <c r="AB35">
+        <v>3.21</v>
+      </c>
+      <c r="AC35">
+        <v>1.03</v>
+      </c>
+      <c r="AD35">
+        <v>9</v>
+      </c>
+      <c r="AE35">
+        <v>1.24</v>
+      </c>
+      <c r="AF35">
+        <v>3.8</v>
+      </c>
+      <c r="AG35">
+        <v>1.91</v>
+      </c>
+      <c r="AH35">
+        <v>1.83</v>
+      </c>
+      <c r="AI35">
+        <v>1.73</v>
+      </c>
+      <c r="AJ35">
+        <v>1.98</v>
+      </c>
+      <c r="AK35">
+        <v>1.35</v>
+      </c>
+      <c r="AL35">
+        <v>1.29</v>
+      </c>
+      <c r="AM35">
+        <v>1.63</v>
+      </c>
+      <c r="AN35">
+        <v>3</v>
+      </c>
+      <c r="AO35">
+        <v>1</v>
+      </c>
+      <c r="AP35">
+        <v>2</v>
+      </c>
+      <c r="AQ35">
+        <v>1.67</v>
+      </c>
+      <c r="AR35">
+        <v>1.59</v>
+      </c>
+      <c r="AS35">
+        <v>1.3</v>
+      </c>
+      <c r="AT35">
+        <v>2.89</v>
+      </c>
+      <c r="AU35">
+        <v>3</v>
+      </c>
+      <c r="AV35">
+        <v>4</v>
+      </c>
+      <c r="AW35">
+        <v>7</v>
+      </c>
+      <c r="AX35">
+        <v>5</v>
+      </c>
+      <c r="AY35">
+        <v>10</v>
+      </c>
+      <c r="AZ35">
+        <v>9</v>
+      </c>
+      <c r="BA35">
+        <v>5</v>
+      </c>
+      <c r="BB35">
+        <v>3</v>
+      </c>
+      <c r="BC35">
+        <v>8</v>
+      </c>
+      <c r="BD35">
+        <v>1.77</v>
+      </c>
+      <c r="BE35">
+        <v>7.55</v>
+      </c>
+      <c r="BF35">
+        <v>2.41</v>
+      </c>
+      <c r="BG35">
+        <v>1.5</v>
+      </c>
+      <c r="BH35">
+        <v>2.41</v>
+      </c>
+      <c r="BI35">
+        <v>1.87</v>
+      </c>
+      <c r="BJ35">
+        <v>1.87</v>
+      </c>
+      <c r="BK35">
+        <v>2.42</v>
+      </c>
+      <c r="BL35">
+        <v>1.53</v>
+      </c>
+      <c r="BM35">
+        <v>3.25</v>
+      </c>
+      <c r="BN35">
+        <v>1.29</v>
+      </c>
+      <c r="BO35">
+        <v>4.4</v>
+      </c>
+      <c r="BP35">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7821471</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45724.70833333334</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>77</v>
+      </c>
+      <c r="H36" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>2</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36" t="s">
+        <v>112</v>
+      </c>
+      <c r="P36" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q36">
+        <v>3.25</v>
+      </c>
+      <c r="R36">
+        <v>1.96</v>
+      </c>
+      <c r="S36">
+        <v>3.5</v>
+      </c>
+      <c r="T36">
+        <v>1.53</v>
+      </c>
+      <c r="U36">
+        <v>2.38</v>
+      </c>
+      <c r="V36">
+        <v>3.65</v>
+      </c>
+      <c r="W36">
+        <v>1.22</v>
+      </c>
+      <c r="X36">
+        <v>10</v>
+      </c>
+      <c r="Y36">
+        <v>1.02</v>
+      </c>
+      <c r="Z36">
+        <v>2.55</v>
+      </c>
+      <c r="AA36">
+        <v>2.85</v>
+      </c>
+      <c r="AB36">
+        <v>3.06</v>
+      </c>
+      <c r="AC36">
+        <v>1.08</v>
+      </c>
+      <c r="AD36">
+        <v>6.5</v>
+      </c>
+      <c r="AE36">
+        <v>1.5</v>
+      </c>
+      <c r="AF36">
+        <v>2.4</v>
+      </c>
+      <c r="AG36">
+        <v>2.25</v>
+      </c>
+      <c r="AH36">
+        <v>1.5</v>
+      </c>
+      <c r="AI36">
+        <v>1.93</v>
+      </c>
+      <c r="AJ36">
+        <v>1.78</v>
+      </c>
+      <c r="AK36">
+        <v>1.39</v>
+      </c>
+      <c r="AL36">
+        <v>1.35</v>
+      </c>
+      <c r="AM36">
+        <v>1.45</v>
+      </c>
+      <c r="AN36">
+        <v>0.5</v>
+      </c>
+      <c r="AO36">
+        <v>2</v>
+      </c>
+      <c r="AP36">
+        <v>1.33</v>
+      </c>
+      <c r="AQ36">
+        <v>1.33</v>
+      </c>
+      <c r="AR36">
+        <v>1.16</v>
+      </c>
+      <c r="AS36">
+        <v>1.56</v>
+      </c>
+      <c r="AT36">
+        <v>2.72</v>
+      </c>
+      <c r="AU36">
+        <v>3</v>
+      </c>
+      <c r="AV36">
+        <v>3</v>
+      </c>
+      <c r="AW36">
+        <v>0</v>
+      </c>
+      <c r="AX36">
+        <v>5</v>
+      </c>
+      <c r="AY36">
+        <v>3</v>
+      </c>
+      <c r="AZ36">
+        <v>8</v>
+      </c>
+      <c r="BA36">
+        <v>2</v>
+      </c>
+      <c r="BB36">
+        <v>9</v>
+      </c>
+      <c r="BC36">
+        <v>11</v>
+      </c>
+      <c r="BD36">
+        <v>1.85</v>
+      </c>
+      <c r="BE36">
+        <v>7.6</v>
+      </c>
+      <c r="BF36">
+        <v>2.28</v>
+      </c>
+      <c r="BG36">
+        <v>1.43</v>
+      </c>
+      <c r="BH36">
+        <v>2.63</v>
+      </c>
+      <c r="BI36">
+        <v>1.74</v>
+      </c>
+      <c r="BJ36">
+        <v>2.02</v>
+      </c>
+      <c r="BK36">
+        <v>2.22</v>
+      </c>
+      <c r="BL36">
+        <v>1.62</v>
+      </c>
+      <c r="BM36">
+        <v>2.85</v>
+      </c>
+      <c r="BN36">
+        <v>1.37</v>
+      </c>
+      <c r="BO36">
+        <v>3.9</v>
+      </c>
+      <c r="BP36">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="136">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -355,6 +355,9 @@
     <t>['55', '80']</t>
   </si>
   <si>
+    <t>['19', '35', '57']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -416,6 +419,9 @@
   </si>
   <si>
     <t>['81']</t>
+  </si>
+  <si>
+    <t>['5', '33', '69']</t>
   </si>
 </sst>
 </file>
@@ -777,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP36"/>
+  <dimension ref="A1:BP37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1445,7 +1451,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1651,7 +1657,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1857,7 +1863,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2556,7 +2562,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2681,7 +2687,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3093,7 +3099,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3299,7 +3305,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3711,7 +3717,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4123,7 +4129,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4535,7 +4541,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4947,7 +4953,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5359,7 +5365,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5565,7 +5571,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5771,7 +5777,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5852,7 +5858,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ25">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR25">
         <v>0.8100000000000001</v>
@@ -5977,7 +5983,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6183,7 +6189,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6389,7 +6395,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6595,7 +6601,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6801,7 +6807,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7213,7 +7219,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7419,7 +7425,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7625,7 +7631,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7831,7 +7837,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8194,6 +8200,212 @@
       </c>
       <c r="BP36">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7821467</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45724.83333333334</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37" t="s">
+        <v>84</v>
+      </c>
+      <c r="H37" t="s">
+        <v>81</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37">
+        <v>4</v>
+      </c>
+      <c r="L37">
+        <v>3</v>
+      </c>
+      <c r="M37">
+        <v>3</v>
+      </c>
+      <c r="N37">
+        <v>6</v>
+      </c>
+      <c r="O37" t="s">
+        <v>113</v>
+      </c>
+      <c r="P37" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q37">
+        <v>1.73</v>
+      </c>
+      <c r="R37">
+        <v>2.6</v>
+      </c>
+      <c r="S37">
+        <v>8</v>
+      </c>
+      <c r="T37">
+        <v>1.29</v>
+      </c>
+      <c r="U37">
+        <v>3.5</v>
+      </c>
+      <c r="V37">
+        <v>2.38</v>
+      </c>
+      <c r="W37">
+        <v>1.53</v>
+      </c>
+      <c r="X37">
+        <v>5.5</v>
+      </c>
+      <c r="Y37">
+        <v>1.14</v>
+      </c>
+      <c r="Z37">
+        <v>1.28</v>
+      </c>
+      <c r="AA37">
+        <v>5.5</v>
+      </c>
+      <c r="AB37">
+        <v>9.1</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>1.53</v>
+      </c>
+      <c r="AH37">
+        <v>2.25</v>
+      </c>
+      <c r="AI37">
+        <v>1.91</v>
+      </c>
+      <c r="AJ37">
+        <v>1.8</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>1</v>
+      </c>
+      <c r="AO37">
+        <v>0.5</v>
+      </c>
+      <c r="AP37">
+        <v>1</v>
+      </c>
+      <c r="AQ37">
+        <v>0.67</v>
+      </c>
+      <c r="AR37">
+        <v>1.46</v>
+      </c>
+      <c r="AS37">
+        <v>1</v>
+      </c>
+      <c r="AT37">
+        <v>2.46</v>
+      </c>
+      <c r="AU37">
+        <v>11</v>
+      </c>
+      <c r="AV37">
+        <v>8</v>
+      </c>
+      <c r="AW37">
+        <v>5</v>
+      </c>
+      <c r="AX37">
+        <v>3</v>
+      </c>
+      <c r="AY37">
+        <v>16</v>
+      </c>
+      <c r="AZ37">
+        <v>11</v>
+      </c>
+      <c r="BA37">
+        <v>3</v>
+      </c>
+      <c r="BB37">
+        <v>4</v>
+      </c>
+      <c r="BC37">
+        <v>7</v>
+      </c>
+      <c r="BD37">
+        <v>0</v>
+      </c>
+      <c r="BE37">
+        <v>0</v>
+      </c>
+      <c r="BF37">
+        <v>0</v>
+      </c>
+      <c r="BG37">
+        <v>0</v>
+      </c>
+      <c r="BH37">
+        <v>0</v>
+      </c>
+      <c r="BI37">
+        <v>0</v>
+      </c>
+      <c r="BJ37">
+        <v>0</v>
+      </c>
+      <c r="BK37">
+        <v>0</v>
+      </c>
+      <c r="BL37">
+        <v>0</v>
+      </c>
+      <c r="BM37">
+        <v>0</v>
+      </c>
+      <c r="BN37">
+        <v>0</v>
+      </c>
+      <c r="BO37">
+        <v>0</v>
+      </c>
+      <c r="BP37">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="141">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -355,7 +355,13 @@
     <t>['55', '80']</t>
   </si>
   <si>
-    <t>['19', '35', '57']</t>
+    <t>['18', '34', '57']</t>
+  </si>
+  <si>
+    <t>['2', '90+1']</t>
+  </si>
+  <si>
+    <t>['88']</t>
   </si>
   <si>
     <t>['11']</t>
@@ -421,7 +427,16 @@
     <t>['81']</t>
   </si>
   <si>
-    <t>['5', '33', '69']</t>
+    <t>['32']</t>
+  </si>
+  <si>
+    <t>['5', '31', '69']</t>
+  </si>
+  <si>
+    <t>['73', '90+9']</t>
+  </si>
+  <si>
+    <t>['42', '74']</t>
   </si>
 </sst>
 </file>
@@ -783,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP37"/>
+  <dimension ref="A1:BP40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1326,7 +1341,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1451,7 +1466,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1657,7 +1672,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1735,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ5">
         <v>1.67</v>
@@ -1863,7 +1878,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -1941,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ6">
         <v>2.33</v>
@@ -2356,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2687,7 +2702,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3099,7 +3114,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3305,7 +3320,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3717,7 +3732,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -3798,7 +3813,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4129,7 +4144,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4541,7 +4556,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4953,7 +4968,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5031,10 +5046,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ21">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5240,7 +5255,7 @@
         <v>2</v>
       </c>
       <c r="AQ22">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR22">
         <v>1.38</v>
@@ -5365,7 +5380,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5443,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ23">
         <v>2</v>
@@ -5571,7 +5586,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5649,7 +5664,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
         <v>1.33</v>
@@ -5777,7 +5792,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5983,7 +5998,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6189,7 +6204,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6395,7 +6410,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6601,7 +6616,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6807,7 +6822,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7219,7 +7234,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7425,7 +7440,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7631,7 +7646,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7837,7 +7852,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8043,7 +8058,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8249,7 +8264,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8406,6 +8421,624 @@
       </c>
       <c r="BP37">
         <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:68">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7821466</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45725.70833333334</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H38" t="s">
+        <v>83</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>2</v>
+      </c>
+      <c r="M38">
+        <v>2</v>
+      </c>
+      <c r="N38">
+        <v>4</v>
+      </c>
+      <c r="O38" t="s">
+        <v>114</v>
+      </c>
+      <c r="P38" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q38">
+        <v>3.25</v>
+      </c>
+      <c r="R38">
+        <v>2.05</v>
+      </c>
+      <c r="S38">
+        <v>3.5</v>
+      </c>
+      <c r="T38">
+        <v>1.44</v>
+      </c>
+      <c r="U38">
+        <v>2.63</v>
+      </c>
+      <c r="V38">
+        <v>3.4</v>
+      </c>
+      <c r="W38">
+        <v>1.3</v>
+      </c>
+      <c r="X38">
+        <v>10</v>
+      </c>
+      <c r="Y38">
+        <v>1.06</v>
+      </c>
+      <c r="Z38">
+        <v>2.53</v>
+      </c>
+      <c r="AA38">
+        <v>3.36</v>
+      </c>
+      <c r="AB38">
+        <v>2.65</v>
+      </c>
+      <c r="AC38">
+        <v>1.06</v>
+      </c>
+      <c r="AD38">
+        <v>8</v>
+      </c>
+      <c r="AE38">
+        <v>1.35</v>
+      </c>
+      <c r="AF38">
+        <v>3</v>
+      </c>
+      <c r="AG38">
+        <v>1.8</v>
+      </c>
+      <c r="AH38">
+        <v>1.91</v>
+      </c>
+      <c r="AI38">
+        <v>1.83</v>
+      </c>
+      <c r="AJ38">
+        <v>1.83</v>
+      </c>
+      <c r="AK38">
+        <v>1.47</v>
+      </c>
+      <c r="AL38">
+        <v>1.3</v>
+      </c>
+      <c r="AM38">
+        <v>1.47</v>
+      </c>
+      <c r="AN38">
+        <v>0</v>
+      </c>
+      <c r="AO38">
+        <v>0.5</v>
+      </c>
+      <c r="AP38">
+        <v>0.33</v>
+      </c>
+      <c r="AQ38">
+        <v>0.67</v>
+      </c>
+      <c r="AR38">
+        <v>1.12</v>
+      </c>
+      <c r="AS38">
+        <v>1.12</v>
+      </c>
+      <c r="AT38">
+        <v>2.24</v>
+      </c>
+      <c r="AU38">
+        <v>6</v>
+      </c>
+      <c r="AV38">
+        <v>7</v>
+      </c>
+      <c r="AW38">
+        <v>4</v>
+      </c>
+      <c r="AX38">
+        <v>4</v>
+      </c>
+      <c r="AY38">
+        <v>10</v>
+      </c>
+      <c r="AZ38">
+        <v>11</v>
+      </c>
+      <c r="BA38">
+        <v>4</v>
+      </c>
+      <c r="BB38">
+        <v>7</v>
+      </c>
+      <c r="BC38">
+        <v>11</v>
+      </c>
+      <c r="BD38">
+        <v>2</v>
+      </c>
+      <c r="BE38">
+        <v>6.05</v>
+      </c>
+      <c r="BF38">
+        <v>2.21</v>
+      </c>
+      <c r="BG38">
+        <v>1.36</v>
+      </c>
+      <c r="BH38">
+        <v>2.7</v>
+      </c>
+      <c r="BI38">
+        <v>1.7</v>
+      </c>
+      <c r="BJ38">
+        <v>2.05</v>
+      </c>
+      <c r="BK38">
+        <v>2.14</v>
+      </c>
+      <c r="BL38">
+        <v>1.57</v>
+      </c>
+      <c r="BM38">
+        <v>2.88</v>
+      </c>
+      <c r="BN38">
+        <v>1.32</v>
+      </c>
+      <c r="BO38">
+        <v>3.55</v>
+      </c>
+      <c r="BP38">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7821468</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45725.8125</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39" t="s">
+        <v>85</v>
+      </c>
+      <c r="H39" t="s">
+        <v>80</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>2</v>
+      </c>
+      <c r="N39">
+        <v>2</v>
+      </c>
+      <c r="O39" t="s">
+        <v>90</v>
+      </c>
+      <c r="P39" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q39">
+        <v>2.05</v>
+      </c>
+      <c r="R39">
+        <v>2.15</v>
+      </c>
+      <c r="S39">
+        <v>6.25</v>
+      </c>
+      <c r="T39">
+        <v>1.42</v>
+      </c>
+      <c r="U39">
+        <v>2.65</v>
+      </c>
+      <c r="V39">
+        <v>3</v>
+      </c>
+      <c r="W39">
+        <v>1.34</v>
+      </c>
+      <c r="X39">
+        <v>8</v>
+      </c>
+      <c r="Y39">
+        <v>1.07</v>
+      </c>
+      <c r="Z39">
+        <v>1.47</v>
+      </c>
+      <c r="AA39">
+        <v>4.2</v>
+      </c>
+      <c r="AB39">
+        <v>6.8</v>
+      </c>
+      <c r="AC39">
+        <v>1.02</v>
+      </c>
+      <c r="AD39">
+        <v>8</v>
+      </c>
+      <c r="AE39">
+        <v>1.28</v>
+      </c>
+      <c r="AF39">
+        <v>3.45</v>
+      </c>
+      <c r="AG39">
+        <v>1.8</v>
+      </c>
+      <c r="AH39">
+        <v>1.85</v>
+      </c>
+      <c r="AI39">
+        <v>2.25</v>
+      </c>
+      <c r="AJ39">
+        <v>1.57</v>
+      </c>
+      <c r="AK39">
+        <v>1.11</v>
+      </c>
+      <c r="AL39">
+        <v>1.22</v>
+      </c>
+      <c r="AM39">
+        <v>2.55</v>
+      </c>
+      <c r="AN39">
+        <v>1</v>
+      </c>
+      <c r="AO39">
+        <v>0.5</v>
+      </c>
+      <c r="AP39">
+        <v>0.5</v>
+      </c>
+      <c r="AQ39">
+        <v>1.33</v>
+      </c>
+      <c r="AR39">
+        <v>1.68</v>
+      </c>
+      <c r="AS39">
+        <v>1.55</v>
+      </c>
+      <c r="AT39">
+        <v>3.23</v>
+      </c>
+      <c r="AU39">
+        <v>4</v>
+      </c>
+      <c r="AV39">
+        <v>4</v>
+      </c>
+      <c r="AW39">
+        <v>4</v>
+      </c>
+      <c r="AX39">
+        <v>5</v>
+      </c>
+      <c r="AY39">
+        <v>8</v>
+      </c>
+      <c r="AZ39">
+        <v>9</v>
+      </c>
+      <c r="BA39">
+        <v>10</v>
+      </c>
+      <c r="BB39">
+        <v>4</v>
+      </c>
+      <c r="BC39">
+        <v>14</v>
+      </c>
+      <c r="BD39">
+        <v>1.16</v>
+      </c>
+      <c r="BE39">
+        <v>11</v>
+      </c>
+      <c r="BF39">
+        <v>6.25</v>
+      </c>
+      <c r="BG39">
+        <v>1.37</v>
+      </c>
+      <c r="BH39">
+        <v>2.66</v>
+      </c>
+      <c r="BI39">
+        <v>1.69</v>
+      </c>
+      <c r="BJ39">
+        <v>2</v>
+      </c>
+      <c r="BK39">
+        <v>2.14</v>
+      </c>
+      <c r="BL39">
+        <v>1.57</v>
+      </c>
+      <c r="BM39">
+        <v>2.88</v>
+      </c>
+      <c r="BN39">
+        <v>1.32</v>
+      </c>
+      <c r="BO39">
+        <v>3.3</v>
+      </c>
+      <c r="BP39">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:68">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>7821473</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45725.90625</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40" t="s">
+        <v>74</v>
+      </c>
+      <c r="H40" t="s">
+        <v>72</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40" t="s">
+        <v>115</v>
+      </c>
+      <c r="P40" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q40">
+        <v>3.9</v>
+      </c>
+      <c r="R40">
+        <v>1.95</v>
+      </c>
+      <c r="S40">
+        <v>2.8</v>
+      </c>
+      <c r="T40">
+        <v>1.47</v>
+      </c>
+      <c r="U40">
+        <v>2.45</v>
+      </c>
+      <c r="V40">
+        <v>3.2</v>
+      </c>
+      <c r="W40">
+        <v>1.3</v>
+      </c>
+      <c r="X40">
+        <v>8.75</v>
+      </c>
+      <c r="Y40">
+        <v>1.06</v>
+      </c>
+      <c r="Z40">
+        <v>3.41</v>
+      </c>
+      <c r="AA40">
+        <v>3.2</v>
+      </c>
+      <c r="AB40">
+        <v>2.15</v>
+      </c>
+      <c r="AC40">
+        <v>1.07</v>
+      </c>
+      <c r="AD40">
+        <v>7.5</v>
+      </c>
+      <c r="AE40">
+        <v>1.41</v>
+      </c>
+      <c r="AF40">
+        <v>2.8</v>
+      </c>
+      <c r="AG40">
+        <v>2.15</v>
+      </c>
+      <c r="AH40">
+        <v>1.57</v>
+      </c>
+      <c r="AI40">
+        <v>1.98</v>
+      </c>
+      <c r="AJ40">
+        <v>1.73</v>
+      </c>
+      <c r="AK40">
+        <v>1.65</v>
+      </c>
+      <c r="AL40">
+        <v>1.33</v>
+      </c>
+      <c r="AM40">
+        <v>1.3</v>
+      </c>
+      <c r="AN40">
+        <v>0</v>
+      </c>
+      <c r="AO40">
+        <v>1</v>
+      </c>
+      <c r="AP40">
+        <v>1</v>
+      </c>
+      <c r="AQ40">
+        <v>0.5</v>
+      </c>
+      <c r="AR40">
+        <v>1.35</v>
+      </c>
+      <c r="AS40">
+        <v>1.49</v>
+      </c>
+      <c r="AT40">
+        <v>2.84</v>
+      </c>
+      <c r="AU40">
+        <v>6</v>
+      </c>
+      <c r="AV40">
+        <v>2</v>
+      </c>
+      <c r="AW40">
+        <v>1</v>
+      </c>
+      <c r="AX40">
+        <v>2</v>
+      </c>
+      <c r="AY40">
+        <v>7</v>
+      </c>
+      <c r="AZ40">
+        <v>4</v>
+      </c>
+      <c r="BA40">
+        <v>3</v>
+      </c>
+      <c r="BB40">
+        <v>3</v>
+      </c>
+      <c r="BC40">
+        <v>6</v>
+      </c>
+      <c r="BD40">
+        <v>2.54</v>
+      </c>
+      <c r="BE40">
+        <v>6.15</v>
+      </c>
+      <c r="BF40">
+        <v>1.78</v>
+      </c>
+      <c r="BG40">
+        <v>1.37</v>
+      </c>
+      <c r="BH40">
+        <v>2.66</v>
+      </c>
+      <c r="BI40">
+        <v>1.77</v>
+      </c>
+      <c r="BJ40">
+        <v>1.95</v>
+      </c>
+      <c r="BK40">
+        <v>2.15</v>
+      </c>
+      <c r="BL40">
+        <v>1.56</v>
+      </c>
+      <c r="BM40">
+        <v>2.92</v>
+      </c>
+      <c r="BN40">
+        <v>1.31</v>
+      </c>
+      <c r="BO40">
+        <v>3.95</v>
+      </c>
+      <c r="BP40">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -436,7 +436,7 @@
     <t>['73', '90+9']</t>
   </si>
   <si>
-    <t>['42', '74']</t>
+    <t>['41', '74']</t>
   </si>
 </sst>
 </file>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="142">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>['88']</t>
+  </si>
+  <si>
+    <t>['18', '61', '78']</t>
   </si>
   <si>
     <t>['11']</t>
@@ -798,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP40"/>
+  <dimension ref="A1:BP41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1466,7 +1469,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1672,7 +1675,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1878,7 +1881,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2368,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8">
         <v>1.33</v>
@@ -2702,7 +2705,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3114,7 +3117,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3320,7 +3323,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3732,7 +3735,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4144,7 +4147,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4556,7 +4559,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4634,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19">
         <v>1.67</v>
@@ -4843,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR20">
         <v>1.31</v>
@@ -4968,7 +4971,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5380,7 +5383,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5586,7 +5589,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5792,7 +5795,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5998,7 +6001,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6204,7 +6207,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6410,7 +6413,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6616,7 +6619,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6822,7 +6825,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7234,7 +7237,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7440,7 +7443,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7646,7 +7649,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7852,7 +7855,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8058,7 +8061,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8264,7 +8267,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8470,7 +8473,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8676,7 +8679,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -9039,6 +9042,212 @@
       </c>
       <c r="BP40">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:68">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>7821472</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45726.83333333334</v>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41" t="s">
+        <v>76</v>
+      </c>
+      <c r="H41" t="s">
+        <v>70</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>3</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>3</v>
+      </c>
+      <c r="O41" t="s">
+        <v>116</v>
+      </c>
+      <c r="P41" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q41">
+        <v>2.9</v>
+      </c>
+      <c r="R41">
+        <v>2</v>
+      </c>
+      <c r="S41">
+        <v>3.5</v>
+      </c>
+      <c r="T41">
+        <v>1.44</v>
+      </c>
+      <c r="U41">
+        <v>2.6</v>
+      </c>
+      <c r="V41">
+        <v>3</v>
+      </c>
+      <c r="W41">
+        <v>1.34</v>
+      </c>
+      <c r="X41">
+        <v>8</v>
+      </c>
+      <c r="Y41">
+        <v>1.07</v>
+      </c>
+      <c r="Z41">
+        <v>2.77</v>
+      </c>
+      <c r="AA41">
+        <v>3.26</v>
+      </c>
+      <c r="AB41">
+        <v>2.49</v>
+      </c>
+      <c r="AC41">
+        <v>1.02</v>
+      </c>
+      <c r="AD41">
+        <v>7.9</v>
+      </c>
+      <c r="AE41">
+        <v>1.35</v>
+      </c>
+      <c r="AF41">
+        <v>3.05</v>
+      </c>
+      <c r="AG41">
+        <v>1.91</v>
+      </c>
+      <c r="AH41">
+        <v>1.73</v>
+      </c>
+      <c r="AI41">
+        <v>1.83</v>
+      </c>
+      <c r="AJ41">
+        <v>1.85</v>
+      </c>
+      <c r="AK41">
+        <v>1.36</v>
+      </c>
+      <c r="AL41">
+        <v>1.32</v>
+      </c>
+      <c r="AM41">
+        <v>1.58</v>
+      </c>
+      <c r="AN41">
+        <v>1</v>
+      </c>
+      <c r="AO41">
+        <v>1</v>
+      </c>
+      <c r="AP41">
+        <v>1.67</v>
+      </c>
+      <c r="AQ41">
+        <v>0.5</v>
+      </c>
+      <c r="AR41">
+        <v>1.25</v>
+      </c>
+      <c r="AS41">
+        <v>1.32</v>
+      </c>
+      <c r="AT41">
+        <v>2.57</v>
+      </c>
+      <c r="AU41">
+        <v>5</v>
+      </c>
+      <c r="AV41">
+        <v>3</v>
+      </c>
+      <c r="AW41">
+        <v>1</v>
+      </c>
+      <c r="AX41">
+        <v>4</v>
+      </c>
+      <c r="AY41">
+        <v>6</v>
+      </c>
+      <c r="AZ41">
+        <v>7</v>
+      </c>
+      <c r="BA41">
+        <v>4</v>
+      </c>
+      <c r="BB41">
+        <v>5</v>
+      </c>
+      <c r="BC41">
+        <v>9</v>
+      </c>
+      <c r="BD41">
+        <v>2.32</v>
+      </c>
+      <c r="BE41">
+        <v>6</v>
+      </c>
+      <c r="BF41">
+        <v>1.92</v>
+      </c>
+      <c r="BG41">
+        <v>1.39</v>
+      </c>
+      <c r="BH41">
+        <v>2.59</v>
+      </c>
+      <c r="BI41">
+        <v>1.73</v>
+      </c>
+      <c r="BJ41">
+        <v>1.95</v>
+      </c>
+      <c r="BK41">
+        <v>2.21</v>
+      </c>
+      <c r="BL41">
+        <v>1.53</v>
+      </c>
+      <c r="BM41">
+        <v>2.97</v>
+      </c>
+      <c r="BN41">
+        <v>1.3</v>
+      </c>
+      <c r="BO41">
+        <v>4.6</v>
+      </c>
+      <c r="BP41">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="145">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -367,6 +367,12 @@
     <t>['18', '61', '78']</t>
   </si>
   <si>
+    <t>['35', '42', '66', '90+13']</t>
+  </si>
+  <si>
+    <t>['75']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -440,6 +446,9 @@
   </si>
   <si>
     <t>['41', '74']</t>
+  </si>
+  <si>
+    <t>['59']</t>
   </si>
 </sst>
 </file>
@@ -801,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP41"/>
+  <dimension ref="A1:BP44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1469,7 +1478,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1675,7 +1684,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1756,7 +1765,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ5">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1881,7 +1890,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2705,7 +2714,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -2786,7 +2795,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ10">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR10">
         <v>1.56</v>
@@ -2989,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -3117,7 +3126,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3323,7 +3332,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3735,7 +3744,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4022,7 +4031,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ16">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4147,7 +4156,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4228,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="AQ17">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4559,7 +4568,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4971,7 +4980,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5383,7 +5392,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5589,7 +5598,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5795,7 +5804,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6001,7 +6010,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6082,7 +6091,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ26">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR26">
         <v>1.13</v>
@@ -6207,7 +6216,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6413,7 +6422,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6619,7 +6628,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6825,7 +6834,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -6906,7 +6915,7 @@
         <v>1</v>
       </c>
       <c r="AQ30">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR30">
         <v>1.6</v>
@@ -7237,7 +7246,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7315,7 +7324,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
         <v>3</v>
@@ -7443,7 +7452,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7524,7 +7533,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ33">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR33">
         <v>0.93</v>
@@ -7649,7 +7658,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7855,7 +7864,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8061,7 +8070,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8267,7 +8276,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8473,7 +8482,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8679,7 +8688,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -9248,6 +9257,624 @@
       </c>
       <c r="BP41">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:68">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>7821478</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45731.70833333334</v>
+      </c>
+      <c r="F42">
+        <v>6</v>
+      </c>
+      <c r="G42" t="s">
+        <v>79</v>
+      </c>
+      <c r="H42" t="s">
+        <v>75</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>3</v>
+      </c>
+      <c r="L42">
+        <v>4</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>5</v>
+      </c>
+      <c r="O42" t="s">
+        <v>117</v>
+      </c>
+      <c r="P42" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q42">
+        <v>2.88</v>
+      </c>
+      <c r="R42">
+        <v>2.38</v>
+      </c>
+      <c r="S42">
+        <v>3.25</v>
+      </c>
+      <c r="T42">
+        <v>1.3</v>
+      </c>
+      <c r="U42">
+        <v>3.4</v>
+      </c>
+      <c r="V42">
+        <v>2.38</v>
+      </c>
+      <c r="W42">
+        <v>1.53</v>
+      </c>
+      <c r="X42">
+        <v>6</v>
+      </c>
+      <c r="Y42">
+        <v>1.13</v>
+      </c>
+      <c r="Z42">
+        <v>2.51</v>
+      </c>
+      <c r="AA42">
+        <v>3.31</v>
+      </c>
+      <c r="AB42">
+        <v>2.71</v>
+      </c>
+      <c r="AC42">
+        <v>1.05</v>
+      </c>
+      <c r="AD42">
+        <v>8.5</v>
+      </c>
+      <c r="AE42">
+        <v>1.25</v>
+      </c>
+      <c r="AF42">
+        <v>3.7</v>
+      </c>
+      <c r="AG42">
+        <v>1.8</v>
+      </c>
+      <c r="AH42">
+        <v>1.94</v>
+      </c>
+      <c r="AI42">
+        <v>1.5</v>
+      </c>
+      <c r="AJ42">
+        <v>2.5</v>
+      </c>
+      <c r="AK42">
+        <v>1.44</v>
+      </c>
+      <c r="AL42">
+        <v>1.3</v>
+      </c>
+      <c r="AM42">
+        <v>1.51</v>
+      </c>
+      <c r="AN42">
+        <v>3</v>
+      </c>
+      <c r="AO42">
+        <v>0.5</v>
+      </c>
+      <c r="AP42">
+        <v>3</v>
+      </c>
+      <c r="AQ42">
+        <v>0.33</v>
+      </c>
+      <c r="AR42">
+        <v>1.5</v>
+      </c>
+      <c r="AS42">
+        <v>1.22</v>
+      </c>
+      <c r="AT42">
+        <v>2.72</v>
+      </c>
+      <c r="AU42">
+        <v>6</v>
+      </c>
+      <c r="AV42">
+        <v>6</v>
+      </c>
+      <c r="AW42">
+        <v>3</v>
+      </c>
+      <c r="AX42">
+        <v>7</v>
+      </c>
+      <c r="AY42">
+        <v>9</v>
+      </c>
+      <c r="AZ42">
+        <v>13</v>
+      </c>
+      <c r="BA42">
+        <v>0</v>
+      </c>
+      <c r="BB42">
+        <v>8</v>
+      </c>
+      <c r="BC42">
+        <v>8</v>
+      </c>
+      <c r="BD42">
+        <v>1.97</v>
+      </c>
+      <c r="BE42">
+        <v>6.4</v>
+      </c>
+      <c r="BF42">
+        <v>2.02</v>
+      </c>
+      <c r="BG42">
+        <v>1.34</v>
+      </c>
+      <c r="BH42">
+        <v>2.9</v>
+      </c>
+      <c r="BI42">
+        <v>1.58</v>
+      </c>
+      <c r="BJ42">
+        <v>2.18</v>
+      </c>
+      <c r="BK42">
+        <v>1.96</v>
+      </c>
+      <c r="BL42">
+        <v>1.74</v>
+      </c>
+      <c r="BM42">
+        <v>2.48</v>
+      </c>
+      <c r="BN42">
+        <v>1.47</v>
+      </c>
+      <c r="BO42">
+        <v>3.2</v>
+      </c>
+      <c r="BP42">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:68">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7821479</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2">
+        <v>45731.8125</v>
+      </c>
+      <c r="F43">
+        <v>6</v>
+      </c>
+      <c r="G43" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" t="s">
+        <v>85</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43" t="s">
+        <v>118</v>
+      </c>
+      <c r="P43" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q43">
+        <v>6</v>
+      </c>
+      <c r="R43">
+        <v>2.1</v>
+      </c>
+      <c r="S43">
+        <v>2.3</v>
+      </c>
+      <c r="T43">
+        <v>1.44</v>
+      </c>
+      <c r="U43">
+        <v>2.63</v>
+      </c>
+      <c r="V43">
+        <v>3.25</v>
+      </c>
+      <c r="W43">
+        <v>1.33</v>
+      </c>
+      <c r="X43">
+        <v>10</v>
+      </c>
+      <c r="Y43">
+        <v>1.06</v>
+      </c>
+      <c r="Z43">
+        <v>6.3</v>
+      </c>
+      <c r="AA43">
+        <v>3.92</v>
+      </c>
+      <c r="AB43">
+        <v>1.52</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>2.05</v>
+      </c>
+      <c r="AH43">
+        <v>1.61</v>
+      </c>
+      <c r="AI43">
+        <v>2.1</v>
+      </c>
+      <c r="AJ43">
+        <v>1.67</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>0</v>
+      </c>
+      <c r="AN43">
+        <v>1.5</v>
+      </c>
+      <c r="AO43">
+        <v>1.67</v>
+      </c>
+      <c r="AP43">
+        <v>2</v>
+      </c>
+      <c r="AQ43">
+        <v>1.25</v>
+      </c>
+      <c r="AR43">
+        <v>1.52</v>
+      </c>
+      <c r="AS43">
+        <v>1.34</v>
+      </c>
+      <c r="AT43">
+        <v>2.86</v>
+      </c>
+      <c r="AU43">
+        <v>3</v>
+      </c>
+      <c r="AV43">
+        <v>4</v>
+      </c>
+      <c r="AW43">
+        <v>8</v>
+      </c>
+      <c r="AX43">
+        <v>9</v>
+      </c>
+      <c r="AY43">
+        <v>11</v>
+      </c>
+      <c r="AZ43">
+        <v>13</v>
+      </c>
+      <c r="BA43">
+        <v>2</v>
+      </c>
+      <c r="BB43">
+        <v>8</v>
+      </c>
+      <c r="BC43">
+        <v>10</v>
+      </c>
+      <c r="BD43">
+        <v>0</v>
+      </c>
+      <c r="BE43">
+        <v>0</v>
+      </c>
+      <c r="BF43">
+        <v>0</v>
+      </c>
+      <c r="BG43">
+        <v>0</v>
+      </c>
+      <c r="BH43">
+        <v>0</v>
+      </c>
+      <c r="BI43">
+        <v>0</v>
+      </c>
+      <c r="BJ43">
+        <v>0</v>
+      </c>
+      <c r="BK43">
+        <v>0</v>
+      </c>
+      <c r="BL43">
+        <v>0</v>
+      </c>
+      <c r="BM43">
+        <v>0</v>
+      </c>
+      <c r="BN43">
+        <v>0</v>
+      </c>
+      <c r="BO43">
+        <v>0</v>
+      </c>
+      <c r="BP43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:68">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>7821474</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="2">
+        <v>45731.90625</v>
+      </c>
+      <c r="F44">
+        <v>6</v>
+      </c>
+      <c r="G44" t="s">
+        <v>74</v>
+      </c>
+      <c r="H44" t="s">
+        <v>73</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>2</v>
+      </c>
+      <c r="O44" t="s">
+        <v>91</v>
+      </c>
+      <c r="P44" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q44">
+        <v>2.75</v>
+      </c>
+      <c r="R44">
+        <v>2.2</v>
+      </c>
+      <c r="S44">
+        <v>3.75</v>
+      </c>
+      <c r="T44">
+        <v>1.36</v>
+      </c>
+      <c r="U44">
+        <v>3</v>
+      </c>
+      <c r="V44">
+        <v>2.75</v>
+      </c>
+      <c r="W44">
+        <v>1.4</v>
+      </c>
+      <c r="X44">
+        <v>7</v>
+      </c>
+      <c r="Y44">
+        <v>1.1</v>
+      </c>
+      <c r="Z44">
+        <v>2.51</v>
+      </c>
+      <c r="AA44">
+        <v>3.12</v>
+      </c>
+      <c r="AB44">
+        <v>2.85</v>
+      </c>
+      <c r="AC44">
+        <v>1.01</v>
+      </c>
+      <c r="AD44">
+        <v>8.5</v>
+      </c>
+      <c r="AE44">
+        <v>1.32</v>
+      </c>
+      <c r="AF44">
+        <v>2.88</v>
+      </c>
+      <c r="AG44">
+        <v>1.75</v>
+      </c>
+      <c r="AH44">
+        <v>1.91</v>
+      </c>
+      <c r="AI44">
+        <v>1.67</v>
+      </c>
+      <c r="AJ44">
+        <v>2.1</v>
+      </c>
+      <c r="AK44">
+        <v>1.4</v>
+      </c>
+      <c r="AL44">
+        <v>1.34</v>
+      </c>
+      <c r="AM44">
+        <v>1.51</v>
+      </c>
+      <c r="AN44">
+        <v>1</v>
+      </c>
+      <c r="AO44">
+        <v>0.5</v>
+      </c>
+      <c r="AP44">
+        <v>1</v>
+      </c>
+      <c r="AQ44">
+        <v>0.67</v>
+      </c>
+      <c r="AR44">
+        <v>1.35</v>
+      </c>
+      <c r="AS44">
+        <v>1.17</v>
+      </c>
+      <c r="AT44">
+        <v>2.52</v>
+      </c>
+      <c r="AU44">
+        <v>5</v>
+      </c>
+      <c r="AV44">
+        <v>3</v>
+      </c>
+      <c r="AW44">
+        <v>3</v>
+      </c>
+      <c r="AX44">
+        <v>11</v>
+      </c>
+      <c r="AY44">
+        <v>8</v>
+      </c>
+      <c r="AZ44">
+        <v>14</v>
+      </c>
+      <c r="BA44">
+        <v>4</v>
+      </c>
+      <c r="BB44">
+        <v>3</v>
+      </c>
+      <c r="BC44">
+        <v>7</v>
+      </c>
+      <c r="BD44">
+        <v>1.79</v>
+      </c>
+      <c r="BE44">
+        <v>6.25</v>
+      </c>
+      <c r="BF44">
+        <v>2.23</v>
+      </c>
+      <c r="BG44">
+        <v>1.47</v>
+      </c>
+      <c r="BH44">
+        <v>2.48</v>
+      </c>
+      <c r="BI44">
+        <v>1.79</v>
+      </c>
+      <c r="BJ44">
+        <v>1.91</v>
+      </c>
+      <c r="BK44">
+        <v>2.28</v>
+      </c>
+      <c r="BL44">
+        <v>1.55</v>
+      </c>
+      <c r="BM44">
+        <v>2.95</v>
+      </c>
+      <c r="BN44">
+        <v>1.33</v>
+      </c>
+      <c r="BO44">
+        <v>3.95</v>
+      </c>
+      <c r="BP44">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="147">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -373,6 +373,9 @@
     <t>['75']</t>
   </si>
   <si>
+    <t>['21', '50']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -449,6 +452,9 @@
   </si>
   <si>
     <t>['59']</t>
+  </si>
+  <si>
+    <t>['8', '65']</t>
   </si>
 </sst>
 </file>
@@ -810,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP44"/>
+  <dimension ref="A1:BP45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1478,7 +1484,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1684,7 +1690,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1890,7 +1896,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2714,7 +2720,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3001,7 +3007,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3126,7 +3132,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3332,7 +3338,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3744,7 +3750,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4156,7 +4162,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4568,7 +4574,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4980,7 +4986,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5392,7 +5398,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5598,7 +5604,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5804,7 +5810,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6010,7 +6016,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6216,7 +6222,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6422,7 +6428,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6628,7 +6634,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6834,7 +6840,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7121,7 +7127,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR31">
         <v>1.31</v>
@@ -7246,7 +7252,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7452,7 +7458,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7658,7 +7664,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7864,7 +7870,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8070,7 +8076,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8276,7 +8282,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8482,7 +8488,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8688,7 +8694,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -9718,7 +9724,7 @@
         <v>91</v>
       </c>
       <c r="P44" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -9875,6 +9881,212 @@
       </c>
       <c r="BP44">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:68">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>7821475</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="2">
+        <v>45732.40625</v>
+      </c>
+      <c r="F45">
+        <v>6</v>
+      </c>
+      <c r="G45" t="s">
+        <v>72</v>
+      </c>
+      <c r="H45" t="s">
+        <v>76</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>2</v>
+      </c>
+      <c r="L45">
+        <v>2</v>
+      </c>
+      <c r="M45">
+        <v>2</v>
+      </c>
+      <c r="N45">
+        <v>4</v>
+      </c>
+      <c r="O45" t="s">
+        <v>119</v>
+      </c>
+      <c r="P45" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q45">
+        <v>3.2</v>
+      </c>
+      <c r="R45">
+        <v>1.91</v>
+      </c>
+      <c r="S45">
+        <v>4</v>
+      </c>
+      <c r="T45">
+        <v>1.57</v>
+      </c>
+      <c r="U45">
+        <v>2.25</v>
+      </c>
+      <c r="V45">
+        <v>3.75</v>
+      </c>
+      <c r="W45">
+        <v>1.25</v>
+      </c>
+      <c r="X45">
+        <v>13</v>
+      </c>
+      <c r="Y45">
+        <v>1.04</v>
+      </c>
+      <c r="Z45">
+        <v>1.93</v>
+      </c>
+      <c r="AA45">
+        <v>3.33</v>
+      </c>
+      <c r="AB45">
+        <v>3.96</v>
+      </c>
+      <c r="AC45">
+        <v>1.08</v>
+      </c>
+      <c r="AD45">
+        <v>7</v>
+      </c>
+      <c r="AE45">
+        <v>1.5</v>
+      </c>
+      <c r="AF45">
+        <v>2.3</v>
+      </c>
+      <c r="AG45">
+        <v>2.32</v>
+      </c>
+      <c r="AH45">
+        <v>1.54</v>
+      </c>
+      <c r="AI45">
+        <v>2.2</v>
+      </c>
+      <c r="AJ45">
+        <v>1.62</v>
+      </c>
+      <c r="AK45">
+        <v>1.24</v>
+      </c>
+      <c r="AL45">
+        <v>1.31</v>
+      </c>
+      <c r="AM45">
+        <v>1.8</v>
+      </c>
+      <c r="AN45">
+        <v>1</v>
+      </c>
+      <c r="AO45">
+        <v>0</v>
+      </c>
+      <c r="AP45">
+        <v>1</v>
+      </c>
+      <c r="AQ45">
+        <v>0.33</v>
+      </c>
+      <c r="AR45">
+        <v>1.52</v>
+      </c>
+      <c r="AS45">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT45">
+        <v>2.46</v>
+      </c>
+      <c r="AU45">
+        <v>3</v>
+      </c>
+      <c r="AV45">
+        <v>3</v>
+      </c>
+      <c r="AW45">
+        <v>4</v>
+      </c>
+      <c r="AX45">
+        <v>7</v>
+      </c>
+      <c r="AY45">
+        <v>7</v>
+      </c>
+      <c r="AZ45">
+        <v>10</v>
+      </c>
+      <c r="BA45">
+        <v>7</v>
+      </c>
+      <c r="BB45">
+        <v>3</v>
+      </c>
+      <c r="BC45">
+        <v>10</v>
+      </c>
+      <c r="BD45">
+        <v>1.53</v>
+      </c>
+      <c r="BE45">
+        <v>6.65</v>
+      </c>
+      <c r="BF45">
+        <v>3.18</v>
+      </c>
+      <c r="BG45">
+        <v>1.28</v>
+      </c>
+      <c r="BH45">
+        <v>3.08</v>
+      </c>
+      <c r="BI45">
+        <v>1.53</v>
+      </c>
+      <c r="BJ45">
+        <v>2.21</v>
+      </c>
+      <c r="BK45">
+        <v>1.95</v>
+      </c>
+      <c r="BL45">
+        <v>1.77</v>
+      </c>
+      <c r="BM45">
+        <v>2.52</v>
+      </c>
+      <c r="BN45">
+        <v>1.41</v>
+      </c>
+      <c r="BO45">
+        <v>3.48</v>
+      </c>
+      <c r="BP45">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="150">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -367,7 +367,7 @@
     <t>['18', '61', '78']</t>
   </si>
   <si>
-    <t>['35', '42', '66', '90+13']</t>
+    <t>['34', '41', '66', '90+13']</t>
   </si>
   <si>
     <t>['75']</t>
@@ -376,6 +376,9 @@
     <t>['21', '50']</t>
   </si>
   <si>
+    <t>['4', '55']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -451,10 +454,16 @@
     <t>['41', '74']</t>
   </si>
   <si>
+    <t>['7']</t>
+  </si>
+  <si>
     <t>['59']</t>
   </si>
   <si>
     <t>['8', '65']</t>
+  </si>
+  <si>
+    <t>['80']</t>
   </si>
 </sst>
 </file>
@@ -816,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP45"/>
+  <dimension ref="A1:BP47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1484,7 +1493,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1690,7 +1699,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1896,7 +1905,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2183,7 +2192,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ7">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2720,7 +2729,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3132,7 +3141,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3338,7 +3347,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3416,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
         <v>1.5</v>
@@ -3625,7 +3634,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3750,7 +3759,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -3828,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ15">
         <v>0.5</v>
@@ -4162,7 +4171,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4574,7 +4583,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4986,7 +4995,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5398,7 +5407,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5479,7 +5488,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR23">
         <v>1.13</v>
@@ -5604,7 +5613,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5810,7 +5819,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6016,7 +6025,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6094,7 +6103,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
         <v>0.33</v>
@@ -6222,7 +6231,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6428,7 +6437,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6509,7 +6518,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR28">
         <v>1.09</v>
@@ -6634,7 +6643,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6840,7 +6849,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7124,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ31">
         <v>0.33</v>
@@ -7252,7 +7261,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7333,7 +7342,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR32">
         <v>1.03</v>
@@ -7458,7 +7467,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7664,7 +7673,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7870,7 +7879,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8076,7 +8085,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8282,7 +8291,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8488,7 +8497,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8694,7 +8703,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -9312,7 +9321,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9563,10 +9572,10 @@
         <v>0</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG43">
         <v>2.05</v>
@@ -9724,7 +9733,7 @@
         <v>91</v>
       </c>
       <c r="P44" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -9930,7 +9939,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q45">
         <v>3.2</v>
@@ -10087,6 +10096,418 @@
       </c>
       <c r="BP45">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:68">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>7821477</v>
+      </c>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="2">
+        <v>45732.70833333334</v>
+      </c>
+      <c r="F46">
+        <v>6</v>
+      </c>
+      <c r="G46" t="s">
+        <v>82</v>
+      </c>
+      <c r="H46" t="s">
+        <v>71</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <v>2</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
+      </c>
+      <c r="N46">
+        <v>3</v>
+      </c>
+      <c r="O46" t="s">
+        <v>120</v>
+      </c>
+      <c r="P46" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q46">
+        <v>4</v>
+      </c>
+      <c r="R46">
+        <v>2</v>
+      </c>
+      <c r="S46">
+        <v>3</v>
+      </c>
+      <c r="T46">
+        <v>1.5</v>
+      </c>
+      <c r="U46">
+        <v>2.5</v>
+      </c>
+      <c r="V46">
+        <v>3.5</v>
+      </c>
+      <c r="W46">
+        <v>1.29</v>
+      </c>
+      <c r="X46">
+        <v>11</v>
+      </c>
+      <c r="Y46">
+        <v>1.05</v>
+      </c>
+      <c r="Z46">
+        <v>3.13</v>
+      </c>
+      <c r="AA46">
+        <v>3.16</v>
+      </c>
+      <c r="AB46">
+        <v>2.3</v>
+      </c>
+      <c r="AC46">
+        <v>1.08</v>
+      </c>
+      <c r="AD46">
+        <v>7</v>
+      </c>
+      <c r="AE46">
+        <v>1.42</v>
+      </c>
+      <c r="AF46">
+        <v>2.75</v>
+      </c>
+      <c r="AG46">
+        <v>2.2</v>
+      </c>
+      <c r="AH46">
+        <v>1.55</v>
+      </c>
+      <c r="AI46">
+        <v>2</v>
+      </c>
+      <c r="AJ46">
+        <v>1.73</v>
+      </c>
+      <c r="AK46">
+        <v>1.57</v>
+      </c>
+      <c r="AL46">
+        <v>1.33</v>
+      </c>
+      <c r="AM46">
+        <v>1.36</v>
+      </c>
+      <c r="AN46">
+        <v>2</v>
+      </c>
+      <c r="AO46">
+        <v>3</v>
+      </c>
+      <c r="AP46">
+        <v>2.33</v>
+      </c>
+      <c r="AQ46">
+        <v>2</v>
+      </c>
+      <c r="AR46">
+        <v>1.72</v>
+      </c>
+      <c r="AS46">
+        <v>1.44</v>
+      </c>
+      <c r="AT46">
+        <v>3.16</v>
+      </c>
+      <c r="AU46">
+        <v>6</v>
+      </c>
+      <c r="AV46">
+        <v>3</v>
+      </c>
+      <c r="AW46">
+        <v>4</v>
+      </c>
+      <c r="AX46">
+        <v>7</v>
+      </c>
+      <c r="AY46">
+        <v>10</v>
+      </c>
+      <c r="AZ46">
+        <v>10</v>
+      </c>
+      <c r="BA46">
+        <v>3</v>
+      </c>
+      <c r="BB46">
+        <v>8</v>
+      </c>
+      <c r="BC46">
+        <v>11</v>
+      </c>
+      <c r="BD46">
+        <v>2.1</v>
+      </c>
+      <c r="BE46">
+        <v>6.1</v>
+      </c>
+      <c r="BF46">
+        <v>1.92</v>
+      </c>
+      <c r="BG46">
+        <v>1.5</v>
+      </c>
+      <c r="BH46">
+        <v>2.4</v>
+      </c>
+      <c r="BI46">
+        <v>1.84</v>
+      </c>
+      <c r="BJ46">
+        <v>1.84</v>
+      </c>
+      <c r="BK46">
+        <v>2.33</v>
+      </c>
+      <c r="BL46">
+        <v>1.52</v>
+      </c>
+      <c r="BM46">
+        <v>3.05</v>
+      </c>
+      <c r="BN46">
+        <v>1.3</v>
+      </c>
+      <c r="BO46">
+        <v>4.1</v>
+      </c>
+      <c r="BP46">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:68">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>7821480</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="2">
+        <v>45732.8125</v>
+      </c>
+      <c r="F47">
+        <v>6</v>
+      </c>
+      <c r="G47" t="s">
+        <v>80</v>
+      </c>
+      <c r="H47" t="s">
+        <v>84</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+      <c r="O47" t="s">
+        <v>90</v>
+      </c>
+      <c r="P47" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q47">
+        <v>5</v>
+      </c>
+      <c r="R47">
+        <v>2.5</v>
+      </c>
+      <c r="S47">
+        <v>2.05</v>
+      </c>
+      <c r="T47">
+        <v>1.25</v>
+      </c>
+      <c r="U47">
+        <v>3.75</v>
+      </c>
+      <c r="V47">
+        <v>2.25</v>
+      </c>
+      <c r="W47">
+        <v>1.57</v>
+      </c>
+      <c r="X47">
+        <v>5.5</v>
+      </c>
+      <c r="Y47">
+        <v>1.14</v>
+      </c>
+      <c r="Z47">
+        <v>5.7</v>
+      </c>
+      <c r="AA47">
+        <v>4.2</v>
+      </c>
+      <c r="AB47">
+        <v>1.52</v>
+      </c>
+      <c r="AC47">
+        <v>1.05</v>
+      </c>
+      <c r="AD47">
+        <v>9.25</v>
+      </c>
+      <c r="AE47">
+        <v>1.32</v>
+      </c>
+      <c r="AF47">
+        <v>3.43</v>
+      </c>
+      <c r="AG47">
+        <v>1.83</v>
+      </c>
+      <c r="AH47">
+        <v>1.91</v>
+      </c>
+      <c r="AI47">
+        <v>1.57</v>
+      </c>
+      <c r="AJ47">
+        <v>2.25</v>
+      </c>
+      <c r="AK47">
+        <v>2.15</v>
+      </c>
+      <c r="AL47">
+        <v>1.25</v>
+      </c>
+      <c r="AM47">
+        <v>1.16</v>
+      </c>
+      <c r="AN47">
+        <v>1.5</v>
+      </c>
+      <c r="AO47">
+        <v>2</v>
+      </c>
+      <c r="AP47">
+        <v>1</v>
+      </c>
+      <c r="AQ47">
+        <v>2.25</v>
+      </c>
+      <c r="AR47">
+        <v>1.51</v>
+      </c>
+      <c r="AS47">
+        <v>2.02</v>
+      </c>
+      <c r="AT47">
+        <v>3.53</v>
+      </c>
+      <c r="AU47">
+        <v>3</v>
+      </c>
+      <c r="AV47">
+        <v>4</v>
+      </c>
+      <c r="AW47">
+        <v>2</v>
+      </c>
+      <c r="AX47">
+        <v>0</v>
+      </c>
+      <c r="AY47">
+        <v>5</v>
+      </c>
+      <c r="AZ47">
+        <v>4</v>
+      </c>
+      <c r="BA47">
+        <v>9</v>
+      </c>
+      <c r="BB47">
+        <v>3</v>
+      </c>
+      <c r="BC47">
+        <v>12</v>
+      </c>
+      <c r="BD47">
+        <v>3.1</v>
+      </c>
+      <c r="BE47">
+        <v>9</v>
+      </c>
+      <c r="BF47">
+        <v>1.44</v>
+      </c>
+      <c r="BG47">
+        <v>1.27</v>
+      </c>
+      <c r="BH47">
+        <v>3.25</v>
+      </c>
+      <c r="BI47">
+        <v>1.51</v>
+      </c>
+      <c r="BJ47">
+        <v>2.3</v>
+      </c>
+      <c r="BK47">
+        <v>1.9</v>
+      </c>
+      <c r="BL47">
+        <v>1.75</v>
+      </c>
+      <c r="BM47">
+        <v>2.55</v>
+      </c>
+      <c r="BN47">
+        <v>1.43</v>
+      </c>
+      <c r="BO47">
+        <v>3.6</v>
+      </c>
+      <c r="BP47">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -373,7 +373,7 @@
     <t>['75']</t>
   </si>
   <si>
-    <t>['21', '50']</t>
+    <t>['20', '50']</t>
   </si>
   <si>
     <t>['4', '55']</t>
@@ -460,7 +460,7 @@
     <t>['59']</t>
   </si>
   <si>
-    <t>['8', '65']</t>
+    <t>['7', '65']</t>
   </si>
   <si>
     <t>['80']</t>
@@ -9623,19 +9623,19 @@
         <v>3</v>
       </c>
       <c r="AV43">
+        <v>3</v>
+      </c>
+      <c r="AW43">
         <v>4</v>
       </c>
-      <c r="AW43">
-        <v>8</v>
-      </c>
       <c r="AX43">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AY43">
         <v>11</v>
       </c>
       <c r="AZ43">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA43">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="151">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -464,6 +464,9 @@
   </si>
   <si>
     <t>['80']</t>
+  </si>
+  <si>
+    <t>['44', '87']</t>
   </si>
 </sst>
 </file>
@@ -825,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP47"/>
+  <dimension ref="A1:BP49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1159,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>1.33</v>
@@ -1368,7 +1371,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2807,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
         <v>0.67</v>
@@ -3428,7 +3431,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3631,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ14">
         <v>2</v>
@@ -5076,7 +5079,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ21">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6312,7 +6315,7 @@
         <v>3</v>
       </c>
       <c r="AQ27">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR27">
         <v>1.68</v>
@@ -6721,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>0</v>
@@ -7545,7 +7548,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ33">
         <v>1.25</v>
@@ -8578,7 +8581,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ38">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR38">
         <v>1.12</v>
@@ -10507,6 +10510,418 @@
         <v>3.6</v>
       </c>
       <c r="BP47">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:68">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>7821476</v>
+      </c>
+      <c r="C48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="2">
+        <v>45733.79166666666</v>
+      </c>
+      <c r="F48">
+        <v>6</v>
+      </c>
+      <c r="G48" t="s">
+        <v>70</v>
+      </c>
+      <c r="H48" t="s">
+        <v>77</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>90</v>
+      </c>
+      <c r="P48" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q48">
+        <v>2.75</v>
+      </c>
+      <c r="R48">
+        <v>2</v>
+      </c>
+      <c r="S48">
+        <v>4.75</v>
+      </c>
+      <c r="T48">
+        <v>1.5</v>
+      </c>
+      <c r="U48">
+        <v>2.5</v>
+      </c>
+      <c r="V48">
+        <v>3.5</v>
+      </c>
+      <c r="W48">
+        <v>1.29</v>
+      </c>
+      <c r="X48">
+        <v>11</v>
+      </c>
+      <c r="Y48">
+        <v>1.05</v>
+      </c>
+      <c r="Z48">
+        <v>2.04</v>
+      </c>
+      <c r="AA48">
+        <v>3.33</v>
+      </c>
+      <c r="AB48">
+        <v>3.59</v>
+      </c>
+      <c r="AC48">
+        <v>1.06</v>
+      </c>
+      <c r="AD48">
+        <v>6.2</v>
+      </c>
+      <c r="AE48">
+        <v>1.5</v>
+      </c>
+      <c r="AF48">
+        <v>2.4</v>
+      </c>
+      <c r="AG48">
+        <v>2.2</v>
+      </c>
+      <c r="AH48">
+        <v>1.55</v>
+      </c>
+      <c r="AI48">
+        <v>2</v>
+      </c>
+      <c r="AJ48">
+        <v>1.73</v>
+      </c>
+      <c r="AK48">
+        <v>1.25</v>
+      </c>
+      <c r="AL48">
+        <v>1.35</v>
+      </c>
+      <c r="AM48">
+        <v>1.72</v>
+      </c>
+      <c r="AN48">
+        <v>2.33</v>
+      </c>
+      <c r="AO48">
+        <v>1.5</v>
+      </c>
+      <c r="AP48">
+        <v>2</v>
+      </c>
+      <c r="AQ48">
+        <v>1.33</v>
+      </c>
+      <c r="AR48">
+        <v>1.95</v>
+      </c>
+      <c r="AS48">
+        <v>0.89</v>
+      </c>
+      <c r="AT48">
+        <v>2.84</v>
+      </c>
+      <c r="AU48">
+        <v>4</v>
+      </c>
+      <c r="AV48">
+        <v>3</v>
+      </c>
+      <c r="AW48">
+        <v>13</v>
+      </c>
+      <c r="AX48">
+        <v>8</v>
+      </c>
+      <c r="AY48">
+        <v>17</v>
+      </c>
+      <c r="AZ48">
+        <v>11</v>
+      </c>
+      <c r="BA48">
+        <v>7</v>
+      </c>
+      <c r="BB48">
+        <v>9</v>
+      </c>
+      <c r="BC48">
+        <v>16</v>
+      </c>
+      <c r="BD48">
+        <v>1.67</v>
+      </c>
+      <c r="BE48">
+        <v>6.4</v>
+      </c>
+      <c r="BF48">
+        <v>2.48</v>
+      </c>
+      <c r="BG48">
+        <v>1.55</v>
+      </c>
+      <c r="BH48">
+        <v>2.28</v>
+      </c>
+      <c r="BI48">
+        <v>1.93</v>
+      </c>
+      <c r="BJ48">
+        <v>1.77</v>
+      </c>
+      <c r="BK48">
+        <v>2.48</v>
+      </c>
+      <c r="BL48">
+        <v>1.47</v>
+      </c>
+      <c r="BM48">
+        <v>3.3</v>
+      </c>
+      <c r="BN48">
+        <v>1.28</v>
+      </c>
+      <c r="BO48">
+        <v>4.4</v>
+      </c>
+      <c r="BP48">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:68">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>7821481</v>
+      </c>
+      <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="2">
+        <v>45733.88541666666</v>
+      </c>
+      <c r="F49">
+        <v>6</v>
+      </c>
+      <c r="G49" t="s">
+        <v>81</v>
+      </c>
+      <c r="H49" t="s">
+        <v>83</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>2</v>
+      </c>
+      <c r="N49">
+        <v>2</v>
+      </c>
+      <c r="O49" t="s">
+        <v>90</v>
+      </c>
+      <c r="P49" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q49">
+        <v>3.1</v>
+      </c>
+      <c r="R49">
+        <v>2.25</v>
+      </c>
+      <c r="S49">
+        <v>3.2</v>
+      </c>
+      <c r="T49">
+        <v>1.33</v>
+      </c>
+      <c r="U49">
+        <v>3.25</v>
+      </c>
+      <c r="V49">
+        <v>2.63</v>
+      </c>
+      <c r="W49">
+        <v>1.44</v>
+      </c>
+      <c r="X49">
+        <v>6.5</v>
+      </c>
+      <c r="Y49">
+        <v>1.11</v>
+      </c>
+      <c r="Z49">
+        <v>2.59</v>
+      </c>
+      <c r="AA49">
+        <v>3.3</v>
+      </c>
+      <c r="AB49">
+        <v>2.62</v>
+      </c>
+      <c r="AC49">
+        <v>1.02</v>
+      </c>
+      <c r="AD49">
+        <v>8</v>
+      </c>
+      <c r="AE49">
+        <v>1.29</v>
+      </c>
+      <c r="AF49">
+        <v>3.04</v>
+      </c>
+      <c r="AG49">
+        <v>1.65</v>
+      </c>
+      <c r="AH49">
+        <v>2</v>
+      </c>
+      <c r="AI49">
+        <v>1.57</v>
+      </c>
+      <c r="AJ49">
+        <v>2.25</v>
+      </c>
+      <c r="AK49">
+        <v>1.43</v>
+      </c>
+      <c r="AL49">
+        <v>1.3</v>
+      </c>
+      <c r="AM49">
+        <v>1.47</v>
+      </c>
+      <c r="AN49">
+        <v>0.5</v>
+      </c>
+      <c r="AO49">
+        <v>0.67</v>
+      </c>
+      <c r="AP49">
+        <v>0.33</v>
+      </c>
+      <c r="AQ49">
+        <v>1.25</v>
+      </c>
+      <c r="AR49">
+        <v>1.21</v>
+      </c>
+      <c r="AS49">
+        <v>1.32</v>
+      </c>
+      <c r="AT49">
+        <v>2.53</v>
+      </c>
+      <c r="AU49">
+        <v>5</v>
+      </c>
+      <c r="AV49">
+        <v>6</v>
+      </c>
+      <c r="AW49">
+        <v>4</v>
+      </c>
+      <c r="AX49">
+        <v>3</v>
+      </c>
+      <c r="AY49">
+        <v>9</v>
+      </c>
+      <c r="AZ49">
+        <v>9</v>
+      </c>
+      <c r="BA49">
+        <v>3</v>
+      </c>
+      <c r="BB49">
+        <v>5</v>
+      </c>
+      <c r="BC49">
+        <v>8</v>
+      </c>
+      <c r="BD49">
+        <v>2</v>
+      </c>
+      <c r="BE49">
+        <v>6.4</v>
+      </c>
+      <c r="BF49">
+        <v>1.98</v>
+      </c>
+      <c r="BG49">
+        <v>1.4</v>
+      </c>
+      <c r="BH49">
+        <v>2.7</v>
+      </c>
+      <c r="BI49">
+        <v>1.68</v>
+      </c>
+      <c r="BJ49">
+        <v>2.05</v>
+      </c>
+      <c r="BK49">
+        <v>2.07</v>
+      </c>
+      <c r="BL49">
+        <v>1.66</v>
+      </c>
+      <c r="BM49">
+        <v>2.65</v>
+      </c>
+      <c r="BN49">
+        <v>1.41</v>
+      </c>
+      <c r="BO49">
+        <v>3.55</v>
+      </c>
+      <c r="BP49">
         <v>1.24</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="156">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -379,6 +379,12 @@
     <t>['4', '55']</t>
   </si>
   <si>
+    <t>['18', '28']</t>
+  </si>
+  <si>
+    <t>['82']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -467,6 +473,15 @@
   </si>
   <si>
     <t>['44', '87']</t>
+  </si>
+  <si>
+    <t>['32', '38', '62', '89']</t>
+  </si>
+  <si>
+    <t>['27', '59', '63']</t>
+  </si>
+  <si>
+    <t>['24', '62', '79']</t>
   </si>
 </sst>
 </file>
@@ -828,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP49"/>
+  <dimension ref="A1:BP52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1165,7 +1180,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1496,7 +1511,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1577,7 +1592,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1702,7 +1717,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1908,7 +1923,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2192,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7">
         <v>2.25</v>
@@ -2401,7 +2416,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ8">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2732,7 +2747,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3144,7 +3159,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3350,7 +3365,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3762,7 +3777,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4046,7 +4061,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ16">
         <v>0.33</v>
@@ -4174,7 +4189,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4586,7 +4601,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4667,7 +4682,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ19">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR19">
         <v>1.03</v>
@@ -4998,7 +5013,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5076,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ21">
         <v>1.25</v>
@@ -5285,7 +5300,7 @@
         <v>2</v>
       </c>
       <c r="AQ22">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR22">
         <v>1.38</v>
@@ -5410,7 +5425,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5616,7 +5631,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5697,7 +5712,7 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR24">
         <v>1.43</v>
@@ -5822,7 +5837,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5900,7 +5915,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25">
         <v>0.67</v>
@@ -6028,7 +6043,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6234,7 +6249,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6440,7 +6455,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6518,7 +6533,7 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ28">
         <v>2.25</v>
@@ -6646,7 +6661,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6852,7 +6867,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7264,7 +7279,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7470,7 +7485,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7676,7 +7691,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7754,7 +7769,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ34">
         <v>2.33</v>
@@ -7882,7 +7897,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -7963,7 +7978,7 @@
         <v>2</v>
       </c>
       <c r="AQ35">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR35">
         <v>1.59</v>
@@ -8088,7 +8103,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8169,7 +8184,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ36">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR36">
         <v>1.16</v>
@@ -8294,7 +8309,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8500,7 +8515,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8706,7 +8721,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -8784,10 +8799,10 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ39">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR39">
         <v>1.68</v>
@@ -9324,7 +9339,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9736,7 +9751,7 @@
         <v>91</v>
       </c>
       <c r="P44" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -9942,7 +9957,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q45">
         <v>3.2</v>
@@ -10148,7 +10163,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10766,7 +10781,7 @@
         <v>90</v>
       </c>
       <c r="P49" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -10923,6 +10938,624 @@
       </c>
       <c r="BP49">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:68">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>7821486</v>
+      </c>
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" s="2">
+        <v>45736.70833333334</v>
+      </c>
+      <c r="F50">
+        <v>7</v>
+      </c>
+      <c r="G50" t="s">
+        <v>75</v>
+      </c>
+      <c r="H50" t="s">
+        <v>82</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="J50">
+        <v>2</v>
+      </c>
+      <c r="K50">
+        <v>4</v>
+      </c>
+      <c r="L50">
+        <v>2</v>
+      </c>
+      <c r="M50">
+        <v>4</v>
+      </c>
+      <c r="N50">
+        <v>6</v>
+      </c>
+      <c r="O50" t="s">
+        <v>121</v>
+      </c>
+      <c r="P50" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q50">
+        <v>2.55</v>
+      </c>
+      <c r="R50">
+        <v>2</v>
+      </c>
+      <c r="S50">
+        <v>4.2</v>
+      </c>
+      <c r="T50">
+        <v>1.44</v>
+      </c>
+      <c r="U50">
+        <v>2.55</v>
+      </c>
+      <c r="V50">
+        <v>3.1</v>
+      </c>
+      <c r="W50">
+        <v>1.32</v>
+      </c>
+      <c r="X50">
+        <v>8.25</v>
+      </c>
+      <c r="Y50">
+        <v>1.06</v>
+      </c>
+      <c r="Z50">
+        <v>2.02</v>
+      </c>
+      <c r="AA50">
+        <v>3.27</v>
+      </c>
+      <c r="AB50">
+        <v>3.72</v>
+      </c>
+      <c r="AC50">
+        <v>1.07</v>
+      </c>
+      <c r="AD50">
+        <v>7.5</v>
+      </c>
+      <c r="AE50">
+        <v>1.4</v>
+      </c>
+      <c r="AF50">
+        <v>2.85</v>
+      </c>
+      <c r="AG50">
+        <v>2.15</v>
+      </c>
+      <c r="AH50">
+        <v>1.6</v>
+      </c>
+      <c r="AI50">
+        <v>1.98</v>
+      </c>
+      <c r="AJ50">
+        <v>1.73</v>
+      </c>
+      <c r="AK50">
+        <v>1.24</v>
+      </c>
+      <c r="AL50">
+        <v>1.31</v>
+      </c>
+      <c r="AM50">
+        <v>1.8</v>
+      </c>
+      <c r="AN50">
+        <v>2.33</v>
+      </c>
+      <c r="AO50">
+        <v>1.33</v>
+      </c>
+      <c r="AP50">
+        <v>1.75</v>
+      </c>
+      <c r="AQ50">
+        <v>1.75</v>
+      </c>
+      <c r="AR50">
+        <v>1.4</v>
+      </c>
+      <c r="AS50">
+        <v>1.51</v>
+      </c>
+      <c r="AT50">
+        <v>2.91</v>
+      </c>
+      <c r="AU50">
+        <v>6</v>
+      </c>
+      <c r="AV50">
+        <v>6</v>
+      </c>
+      <c r="AW50">
+        <v>5</v>
+      </c>
+      <c r="AX50">
+        <v>5</v>
+      </c>
+      <c r="AY50">
+        <v>11</v>
+      </c>
+      <c r="AZ50">
+        <v>11</v>
+      </c>
+      <c r="BA50">
+        <v>6</v>
+      </c>
+      <c r="BB50">
+        <v>1</v>
+      </c>
+      <c r="BC50">
+        <v>7</v>
+      </c>
+      <c r="BD50">
+        <v>1.58</v>
+      </c>
+      <c r="BE50">
+        <v>6.4</v>
+      </c>
+      <c r="BF50">
+        <v>2.65</v>
+      </c>
+      <c r="BG50">
+        <v>1.5</v>
+      </c>
+      <c r="BH50">
+        <v>2.4</v>
+      </c>
+      <c r="BI50">
+        <v>1.82</v>
+      </c>
+      <c r="BJ50">
+        <v>1.86</v>
+      </c>
+      <c r="BK50">
+        <v>2.33</v>
+      </c>
+      <c r="BL50">
+        <v>1.52</v>
+      </c>
+      <c r="BM50">
+        <v>3.05</v>
+      </c>
+      <c r="BN50">
+        <v>1.3</v>
+      </c>
+      <c r="BO50">
+        <v>4.1</v>
+      </c>
+      <c r="BP50">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:68">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>7821485</v>
+      </c>
+      <c r="C51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" s="2">
+        <v>45736.83333333334</v>
+      </c>
+      <c r="F51">
+        <v>7</v>
+      </c>
+      <c r="G51" t="s">
+        <v>85</v>
+      </c>
+      <c r="H51" t="s">
+        <v>79</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>3</v>
+      </c>
+      <c r="N51">
+        <v>3</v>
+      </c>
+      <c r="O51" t="s">
+        <v>90</v>
+      </c>
+      <c r="P51" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q51">
+        <v>2.05</v>
+      </c>
+      <c r="R51">
+        <v>2.15</v>
+      </c>
+      <c r="S51">
+        <v>5.75</v>
+      </c>
+      <c r="T51">
+        <v>1.4</v>
+      </c>
+      <c r="U51">
+        <v>2.7</v>
+      </c>
+      <c r="V51">
+        <v>2.87</v>
+      </c>
+      <c r="W51">
+        <v>1.36</v>
+      </c>
+      <c r="X51">
+        <v>7.5</v>
+      </c>
+      <c r="Y51">
+        <v>1.07</v>
+      </c>
+      <c r="Z51">
+        <v>1.36</v>
+      </c>
+      <c r="AA51">
+        <v>4.8</v>
+      </c>
+      <c r="AB51">
+        <v>7.9</v>
+      </c>
+      <c r="AC51">
+        <v>1.05</v>
+      </c>
+      <c r="AD51">
+        <v>8.5</v>
+      </c>
+      <c r="AE51">
+        <v>1.33</v>
+      </c>
+      <c r="AF51">
+        <v>3.2</v>
+      </c>
+      <c r="AG51">
+        <v>1.89</v>
+      </c>
+      <c r="AH51">
+        <v>1.85</v>
+      </c>
+      <c r="AI51">
+        <v>2.15</v>
+      </c>
+      <c r="AJ51">
+        <v>1.62</v>
+      </c>
+      <c r="AK51">
+        <v>1.12</v>
+      </c>
+      <c r="AL51">
+        <v>1.23</v>
+      </c>
+      <c r="AM51">
+        <v>2.45</v>
+      </c>
+      <c r="AN51">
+        <v>0.5</v>
+      </c>
+      <c r="AO51">
+        <v>1.67</v>
+      </c>
+      <c r="AP51">
+        <v>0.33</v>
+      </c>
+      <c r="AQ51">
+        <v>2</v>
+      </c>
+      <c r="AR51">
+        <v>1.54</v>
+      </c>
+      <c r="AS51">
+        <v>1.27</v>
+      </c>
+      <c r="AT51">
+        <v>2.81</v>
+      </c>
+      <c r="AU51">
+        <v>10</v>
+      </c>
+      <c r="AV51">
+        <v>7</v>
+      </c>
+      <c r="AW51">
+        <v>6</v>
+      </c>
+      <c r="AX51">
+        <v>1</v>
+      </c>
+      <c r="AY51">
+        <v>16</v>
+      </c>
+      <c r="AZ51">
+        <v>8</v>
+      </c>
+      <c r="BA51">
+        <v>13</v>
+      </c>
+      <c r="BB51">
+        <v>3</v>
+      </c>
+      <c r="BC51">
+        <v>16</v>
+      </c>
+      <c r="BD51">
+        <v>1.32</v>
+      </c>
+      <c r="BE51">
+        <v>7</v>
+      </c>
+      <c r="BF51">
+        <v>3.7</v>
+      </c>
+      <c r="BG51">
+        <v>1.49</v>
+      </c>
+      <c r="BH51">
+        <v>2.4</v>
+      </c>
+      <c r="BI51">
+        <v>1.8</v>
+      </c>
+      <c r="BJ51">
+        <v>1.89</v>
+      </c>
+      <c r="BK51">
+        <v>2.28</v>
+      </c>
+      <c r="BL51">
+        <v>1.54</v>
+      </c>
+      <c r="BM51">
+        <v>2.9</v>
+      </c>
+      <c r="BN51">
+        <v>1.34</v>
+      </c>
+      <c r="BO51">
+        <v>3.9</v>
+      </c>
+      <c r="BP51">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:68">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>7821483</v>
+      </c>
+      <c r="C52" t="s">
+        <v>68</v>
+      </c>
+      <c r="D52" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="2">
+        <v>45738.66666666666</v>
+      </c>
+      <c r="F52">
+        <v>7</v>
+      </c>
+      <c r="G52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H52" t="s">
+        <v>80</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <v>3</v>
+      </c>
+      <c r="N52">
+        <v>4</v>
+      </c>
+      <c r="O52" t="s">
+        <v>122</v>
+      </c>
+      <c r="P52" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q52">
+        <v>3.5</v>
+      </c>
+      <c r="R52">
+        <v>1.95</v>
+      </c>
+      <c r="S52">
+        <v>3.4</v>
+      </c>
+      <c r="T52">
+        <v>1.53</v>
+      </c>
+      <c r="U52">
+        <v>2.38</v>
+      </c>
+      <c r="V52">
+        <v>3.5</v>
+      </c>
+      <c r="W52">
+        <v>1.29</v>
+      </c>
+      <c r="X52">
+        <v>11</v>
+      </c>
+      <c r="Y52">
+        <v>1.05</v>
+      </c>
+      <c r="Z52">
+        <v>2.48</v>
+      </c>
+      <c r="AA52">
+        <v>3.38</v>
+      </c>
+      <c r="AB52">
+        <v>2.69</v>
+      </c>
+      <c r="AC52">
+        <v>1.07</v>
+      </c>
+      <c r="AD52">
+        <v>7.5</v>
+      </c>
+      <c r="AE52">
+        <v>1.5</v>
+      </c>
+      <c r="AF52">
+        <v>2.4</v>
+      </c>
+      <c r="AG52">
+        <v>2.2</v>
+      </c>
+      <c r="AH52">
+        <v>1.53</v>
+      </c>
+      <c r="AI52">
+        <v>2</v>
+      </c>
+      <c r="AJ52">
+        <v>1.73</v>
+      </c>
+      <c r="AK52">
+        <v>1.47</v>
+      </c>
+      <c r="AL52">
+        <v>1.33</v>
+      </c>
+      <c r="AM52">
+        <v>1.43</v>
+      </c>
+      <c r="AN52">
+        <v>0.5</v>
+      </c>
+      <c r="AO52">
+        <v>1.33</v>
+      </c>
+      <c r="AP52">
+        <v>0.33</v>
+      </c>
+      <c r="AQ52">
+        <v>1.75</v>
+      </c>
+      <c r="AR52">
+        <v>1.22</v>
+      </c>
+      <c r="AS52">
+        <v>1.49</v>
+      </c>
+      <c r="AT52">
+        <v>2.71</v>
+      </c>
+      <c r="AU52">
+        <v>-1</v>
+      </c>
+      <c r="AV52">
+        <v>-1</v>
+      </c>
+      <c r="AW52">
+        <v>-1</v>
+      </c>
+      <c r="AX52">
+        <v>-1</v>
+      </c>
+      <c r="AY52">
+        <v>-1</v>
+      </c>
+      <c r="AZ52">
+        <v>-1</v>
+      </c>
+      <c r="BA52">
+        <v>-1</v>
+      </c>
+      <c r="BB52">
+        <v>-1</v>
+      </c>
+      <c r="BC52">
+        <v>-1</v>
+      </c>
+      <c r="BD52">
+        <v>1.8</v>
+      </c>
+      <c r="BE52">
+        <v>7.5</v>
+      </c>
+      <c r="BF52">
+        <v>2.4</v>
+      </c>
+      <c r="BG52">
+        <v>1.5</v>
+      </c>
+      <c r="BH52">
+        <v>2.41</v>
+      </c>
+      <c r="BI52">
+        <v>1.85</v>
+      </c>
+      <c r="BJ52">
+        <v>1.85</v>
+      </c>
+      <c r="BK52">
+        <v>2.42</v>
+      </c>
+      <c r="BL52">
+        <v>1.53</v>
+      </c>
+      <c r="BM52">
+        <v>3.25</v>
+      </c>
+      <c r="BN52">
+        <v>1.29</v>
+      </c>
+      <c r="BO52">
+        <v>4.4</v>
+      </c>
+      <c r="BP52">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="158">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -385,6 +385,9 @@
     <t>['82']</t>
   </si>
   <si>
+    <t>['86']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -482,6 +485,9 @@
   </si>
   <si>
     <t>['24', '62', '79']</t>
+  </si>
+  <si>
+    <t>['18']</t>
   </si>
 </sst>
 </file>
@@ -843,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP52"/>
+  <dimension ref="A1:BP54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1383,7 +1389,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ3">
         <v>1.25</v>
@@ -1511,7 +1517,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1717,7 +1723,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1923,7 +1929,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2004,7 +2010,7 @@
         <v>1</v>
       </c>
       <c r="AQ6">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2747,7 +2753,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3159,7 +3165,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3365,7 +3371,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3777,7 +3783,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4189,7 +4195,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4476,7 +4482,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR18">
         <v>0.9399999999999999</v>
@@ -4601,7 +4607,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4888,7 +4894,7 @@
         <v>1</v>
       </c>
       <c r="AQ20">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR20">
         <v>1.31</v>
@@ -5013,7 +5019,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5297,7 +5303,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ22">
         <v>1.75</v>
@@ -5425,7 +5431,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5631,7 +5637,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5837,7 +5843,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6043,7 +6049,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6249,7 +6255,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6455,7 +6461,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6661,7 +6667,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6867,7 +6873,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7279,7 +7285,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7485,7 +7491,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7691,7 +7697,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7772,7 +7778,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ34">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR34">
         <v>1.43</v>
@@ -7897,7 +7903,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -7975,7 +7981,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ35">
         <v>2</v>
@@ -8103,7 +8109,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8309,7 +8315,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8515,7 +8521,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8721,7 +8727,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -9214,7 +9220,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ41">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR41">
         <v>1.25</v>
@@ -9339,7 +9345,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9751,7 +9757,7 @@
         <v>91</v>
       </c>
       <c r="P44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -9957,7 +9963,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q45">
         <v>3.2</v>
@@ -10163,7 +10169,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10781,7 +10787,7 @@
         <v>90</v>
       </c>
       <c r="P49" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -10987,7 +10993,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q50">
         <v>2.55</v>
@@ -11193,7 +11199,7 @@
         <v>90</v>
       </c>
       <c r="P51" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q51">
         <v>2.05</v>
@@ -11399,7 +11405,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11492,31 +11498,31 @@
         <v>2.71</v>
       </c>
       <c r="AU52">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV52">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AW52">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX52">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY52">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AZ52">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BA52">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB52">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC52">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD52">
         <v>1.8</v>
@@ -11556,6 +11562,418 @@
       </c>
       <c r="BP52">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:68">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>7821484</v>
+      </c>
+      <c r="C53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="2">
+        <v>45738.79166666666</v>
+      </c>
+      <c r="F53">
+        <v>7</v>
+      </c>
+      <c r="G53" t="s">
+        <v>84</v>
+      </c>
+      <c r="H53" t="s">
+        <v>78</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <v>1</v>
+      </c>
+      <c r="N53">
+        <v>2</v>
+      </c>
+      <c r="O53" t="s">
+        <v>123</v>
+      </c>
+      <c r="P53" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q53">
+        <v>1.8</v>
+      </c>
+      <c r="R53">
+        <v>2.4</v>
+      </c>
+      <c r="S53">
+        <v>9.5</v>
+      </c>
+      <c r="T53">
+        <v>1.36</v>
+      </c>
+      <c r="U53">
+        <v>3</v>
+      </c>
+      <c r="V53">
+        <v>2.63</v>
+      </c>
+      <c r="W53">
+        <v>1.44</v>
+      </c>
+      <c r="X53">
+        <v>7</v>
+      </c>
+      <c r="Y53">
+        <v>1.1</v>
+      </c>
+      <c r="Z53">
+        <v>1.28</v>
+      </c>
+      <c r="AA53">
+        <v>5.4</v>
+      </c>
+      <c r="AB53">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53">
+        <v>2.49</v>
+      </c>
+      <c r="AF53">
+        <v>1.53</v>
+      </c>
+      <c r="AG53">
+        <v>1.77</v>
+      </c>
+      <c r="AH53">
+        <v>1.98</v>
+      </c>
+      <c r="AI53">
+        <v>2.38</v>
+      </c>
+      <c r="AJ53">
+        <v>1.53</v>
+      </c>
+      <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>0</v>
+      </c>
+      <c r="AN53">
+        <v>1</v>
+      </c>
+      <c r="AO53">
+        <v>2.33</v>
+      </c>
+      <c r="AP53">
+        <v>1</v>
+      </c>
+      <c r="AQ53">
+        <v>2</v>
+      </c>
+      <c r="AR53">
+        <v>1.8</v>
+      </c>
+      <c r="AS53">
+        <v>1.2</v>
+      </c>
+      <c r="AT53">
+        <v>3</v>
+      </c>
+      <c r="AU53">
+        <v>7</v>
+      </c>
+      <c r="AV53">
+        <v>2</v>
+      </c>
+      <c r="AW53">
+        <v>1</v>
+      </c>
+      <c r="AX53">
+        <v>2</v>
+      </c>
+      <c r="AY53">
+        <v>8</v>
+      </c>
+      <c r="AZ53">
+        <v>4</v>
+      </c>
+      <c r="BA53">
+        <v>13</v>
+      </c>
+      <c r="BB53">
+        <v>1</v>
+      </c>
+      <c r="BC53">
+        <v>14</v>
+      </c>
+      <c r="BD53">
+        <v>0</v>
+      </c>
+      <c r="BE53">
+        <v>0</v>
+      </c>
+      <c r="BF53">
+        <v>0</v>
+      </c>
+      <c r="BG53">
+        <v>0</v>
+      </c>
+      <c r="BH53">
+        <v>0</v>
+      </c>
+      <c r="BI53">
+        <v>0</v>
+      </c>
+      <c r="BJ53">
+        <v>0</v>
+      </c>
+      <c r="BK53">
+        <v>0</v>
+      </c>
+      <c r="BL53">
+        <v>0</v>
+      </c>
+      <c r="BM53">
+        <v>0</v>
+      </c>
+      <c r="BN53">
+        <v>0</v>
+      </c>
+      <c r="BO53">
+        <v>0</v>
+      </c>
+      <c r="BP53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:68">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>7821487</v>
+      </c>
+      <c r="C54" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="2">
+        <v>45738.88541666666</v>
+      </c>
+      <c r="F54">
+        <v>7</v>
+      </c>
+      <c r="G54" t="s">
+        <v>71</v>
+      </c>
+      <c r="H54" t="s">
+        <v>70</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54" t="s">
+        <v>90</v>
+      </c>
+      <c r="P54" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q54">
+        <v>2.88</v>
+      </c>
+      <c r="R54">
+        <v>2.05</v>
+      </c>
+      <c r="S54">
+        <v>4.33</v>
+      </c>
+      <c r="T54">
+        <v>1.5</v>
+      </c>
+      <c r="U54">
+        <v>2.5</v>
+      </c>
+      <c r="V54">
+        <v>3.4</v>
+      </c>
+      <c r="W54">
+        <v>1.3</v>
+      </c>
+      <c r="X54">
+        <v>10</v>
+      </c>
+      <c r="Y54">
+        <v>1.06</v>
+      </c>
+      <c r="Z54">
+        <v>2.1</v>
+      </c>
+      <c r="AA54">
+        <v>3.16</v>
+      </c>
+      <c r="AB54">
+        <v>3.61</v>
+      </c>
+      <c r="AC54">
+        <v>1.02</v>
+      </c>
+      <c r="AD54">
+        <v>7.8</v>
+      </c>
+      <c r="AE54">
+        <v>1.35</v>
+      </c>
+      <c r="AF54">
+        <v>2.74</v>
+      </c>
+      <c r="AG54">
+        <v>1.6</v>
+      </c>
+      <c r="AH54">
+        <v>2.1</v>
+      </c>
+      <c r="AI54">
+        <v>1.91</v>
+      </c>
+      <c r="AJ54">
+        <v>1.8</v>
+      </c>
+      <c r="AK54">
+        <v>1.28</v>
+      </c>
+      <c r="AL54">
+        <v>1.32</v>
+      </c>
+      <c r="AM54">
+        <v>1.7</v>
+      </c>
+      <c r="AN54">
+        <v>2</v>
+      </c>
+      <c r="AO54">
+        <v>0.5</v>
+      </c>
+      <c r="AP54">
+        <v>1.75</v>
+      </c>
+      <c r="AQ54">
+        <v>0.67</v>
+      </c>
+      <c r="AR54">
+        <v>1.45</v>
+      </c>
+      <c r="AS54">
+        <v>1.23</v>
+      </c>
+      <c r="AT54">
+        <v>2.68</v>
+      </c>
+      <c r="AU54">
+        <v>2</v>
+      </c>
+      <c r="AV54">
+        <v>4</v>
+      </c>
+      <c r="AW54">
+        <v>6</v>
+      </c>
+      <c r="AX54">
+        <v>2</v>
+      </c>
+      <c r="AY54">
+        <v>8</v>
+      </c>
+      <c r="AZ54">
+        <v>6</v>
+      </c>
+      <c r="BA54">
+        <v>4</v>
+      </c>
+      <c r="BB54">
+        <v>3</v>
+      </c>
+      <c r="BC54">
+        <v>7</v>
+      </c>
+      <c r="BD54">
+        <v>1.53</v>
+      </c>
+      <c r="BE54">
+        <v>8.5</v>
+      </c>
+      <c r="BF54">
+        <v>3</v>
+      </c>
+      <c r="BG54">
+        <v>1.31</v>
+      </c>
+      <c r="BH54">
+        <v>3.15</v>
+      </c>
+      <c r="BI54">
+        <v>1.56</v>
+      </c>
+      <c r="BJ54">
+        <v>2.33</v>
+      </c>
+      <c r="BK54">
+        <v>1.93</v>
+      </c>
+      <c r="BL54">
+        <v>1.82</v>
+      </c>
+      <c r="BM54">
+        <v>2.43</v>
+      </c>
+      <c r="BN54">
+        <v>1.49</v>
+      </c>
+      <c r="BO54">
+        <v>3.22</v>
+      </c>
+      <c r="BP54">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="162">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -388,6 +388,15 @@
     <t>['86']</t>
   </si>
   <si>
+    <t>['49', '88']</t>
+  </si>
+  <si>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -484,10 +493,13 @@
     <t>['27', '59', '63']</t>
   </si>
   <si>
-    <t>['24', '62', '79']</t>
-  </si>
-  <si>
-    <t>['18']</t>
+    <t>['23', '62', '79']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
+    <t>['59', '90+7']</t>
   </si>
 </sst>
 </file>
@@ -849,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP54"/>
+  <dimension ref="A1:BP57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1517,7 +1529,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1723,7 +1735,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1801,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>1.25</v>
@@ -1929,7 +1941,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2419,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8">
         <v>1.75</v>
@@ -2625,10 +2637,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2753,7 +2765,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3165,7 +3177,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3246,7 +3258,7 @@
         <v>3</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3371,7 +3383,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3783,7 +3795,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -3864,7 +3876,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4195,7 +4207,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4479,7 +4491,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ18">
         <v>2</v>
@@ -4607,7 +4619,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4685,7 +4697,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ19">
         <v>2</v>
@@ -5019,7 +5031,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5431,7 +5443,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5509,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ23">
         <v>2.25</v>
@@ -5637,7 +5649,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5843,7 +5855,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5924,7 +5936,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ25">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR25">
         <v>0.8100000000000001</v>
@@ -6049,7 +6061,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6255,7 +6267,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6461,7 +6473,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6667,7 +6679,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6748,7 +6760,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>2.06</v>
@@ -6873,7 +6885,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7285,7 +7297,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7491,7 +7503,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7697,7 +7709,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7903,7 +7915,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8109,7 +8121,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8187,7 +8199,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ36">
         <v>1.75</v>
@@ -8315,7 +8327,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8396,7 +8408,7 @@
         <v>1</v>
       </c>
       <c r="AQ37">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR37">
         <v>1.46</v>
@@ -8521,7 +8533,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8599,7 +8611,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ38">
         <v>1.25</v>
@@ -8727,7 +8739,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -9014,7 +9026,7 @@
         <v>1</v>
       </c>
       <c r="AQ40">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR40">
         <v>1.35</v>
@@ -9217,7 +9229,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41">
         <v>0.67</v>
@@ -9345,7 +9357,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9757,7 +9769,7 @@
         <v>91</v>
       </c>
       <c r="P44" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -9963,7 +9975,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q45">
         <v>3.2</v>
@@ -10169,7 +10181,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10787,7 +10799,7 @@
         <v>90</v>
       </c>
       <c r="P49" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -10993,7 +11005,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q50">
         <v>2.55</v>
@@ -11199,7 +11211,7 @@
         <v>90</v>
       </c>
       <c r="P51" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q51">
         <v>2.05</v>
@@ -11405,7 +11417,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11611,7 +11623,7 @@
         <v>123</v>
       </c>
       <c r="P53" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11974,6 +11986,624 @@
       </c>
       <c r="BP54">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:68">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>7821482</v>
+      </c>
+      <c r="C55" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="2">
+        <v>45739.64583333334</v>
+      </c>
+      <c r="F55">
+        <v>7</v>
+      </c>
+      <c r="G55" t="s">
+        <v>73</v>
+      </c>
+      <c r="H55" t="s">
+        <v>81</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55">
+        <v>2</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>3</v>
+      </c>
+      <c r="O55" t="s">
+        <v>124</v>
+      </c>
+      <c r="P55" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q55">
+        <v>3.4</v>
+      </c>
+      <c r="R55">
+        <v>2.05</v>
+      </c>
+      <c r="S55">
+        <v>3.25</v>
+      </c>
+      <c r="T55">
+        <v>1.44</v>
+      </c>
+      <c r="U55">
+        <v>2.63</v>
+      </c>
+      <c r="V55">
+        <v>3.25</v>
+      </c>
+      <c r="W55">
+        <v>1.33</v>
+      </c>
+      <c r="X55">
+        <v>10</v>
+      </c>
+      <c r="Y55">
+        <v>1.06</v>
+      </c>
+      <c r="Z55">
+        <v>2.62</v>
+      </c>
+      <c r="AA55">
+        <v>3</v>
+      </c>
+      <c r="AB55">
+        <v>2.82</v>
+      </c>
+      <c r="AC55">
+        <v>1.05</v>
+      </c>
+      <c r="AD55">
+        <v>8</v>
+      </c>
+      <c r="AE55">
+        <v>1.3</v>
+      </c>
+      <c r="AF55">
+        <v>3.2</v>
+      </c>
+      <c r="AG55">
+        <v>1.98</v>
+      </c>
+      <c r="AH55">
+        <v>1.77</v>
+      </c>
+      <c r="AI55">
+        <v>1.8</v>
+      </c>
+      <c r="AJ55">
+        <v>1.91</v>
+      </c>
+      <c r="AK55">
+        <v>1.42</v>
+      </c>
+      <c r="AL55">
+        <v>1.34</v>
+      </c>
+      <c r="AM55">
+        <v>1.41</v>
+      </c>
+      <c r="AN55">
+        <v>0.33</v>
+      </c>
+      <c r="AO55">
+        <v>0.67</v>
+      </c>
+      <c r="AP55">
+        <v>1</v>
+      </c>
+      <c r="AQ55">
+        <v>0.5</v>
+      </c>
+      <c r="AR55">
+        <v>1.23</v>
+      </c>
+      <c r="AS55">
+        <v>1.22</v>
+      </c>
+      <c r="AT55">
+        <v>2.45</v>
+      </c>
+      <c r="AU55">
+        <v>4</v>
+      </c>
+      <c r="AV55">
+        <v>3</v>
+      </c>
+      <c r="AW55">
+        <v>6</v>
+      </c>
+      <c r="AX55">
+        <v>3</v>
+      </c>
+      <c r="AY55">
+        <v>10</v>
+      </c>
+      <c r="AZ55">
+        <v>6</v>
+      </c>
+      <c r="BA55">
+        <v>10</v>
+      </c>
+      <c r="BB55">
+        <v>4</v>
+      </c>
+      <c r="BC55">
+        <v>14</v>
+      </c>
+      <c r="BD55">
+        <v>2</v>
+      </c>
+      <c r="BE55">
+        <v>7.5</v>
+      </c>
+      <c r="BF55">
+        <v>2.05</v>
+      </c>
+      <c r="BG55">
+        <v>1.49</v>
+      </c>
+      <c r="BH55">
+        <v>2.43</v>
+      </c>
+      <c r="BI55">
+        <v>1.9</v>
+      </c>
+      <c r="BJ55">
+        <v>1.9</v>
+      </c>
+      <c r="BK55">
+        <v>2.28</v>
+      </c>
+      <c r="BL55">
+        <v>1.54</v>
+      </c>
+      <c r="BM55">
+        <v>2.95</v>
+      </c>
+      <c r="BN55">
+        <v>1.33</v>
+      </c>
+      <c r="BO55">
+        <v>3.95</v>
+      </c>
+      <c r="BP55">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:68">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>7821488</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="2">
+        <v>45739.73958333334</v>
+      </c>
+      <c r="F56">
+        <v>7</v>
+      </c>
+      <c r="G56" t="s">
+        <v>77</v>
+      </c>
+      <c r="H56" t="s">
+        <v>72</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>1</v>
+      </c>
+      <c r="N56">
+        <v>2</v>
+      </c>
+      <c r="O56" t="s">
+        <v>125</v>
+      </c>
+      <c r="P56" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q56">
+        <v>4</v>
+      </c>
+      <c r="R56">
+        <v>1.95</v>
+      </c>
+      <c r="S56">
+        <v>3.2</v>
+      </c>
+      <c r="T56">
+        <v>1.57</v>
+      </c>
+      <c r="U56">
+        <v>2.25</v>
+      </c>
+      <c r="V56">
+        <v>3.75</v>
+      </c>
+      <c r="W56">
+        <v>1.25</v>
+      </c>
+      <c r="X56">
+        <v>11</v>
+      </c>
+      <c r="Y56">
+        <v>1.05</v>
+      </c>
+      <c r="Z56">
+        <v>3.23</v>
+      </c>
+      <c r="AA56">
+        <v>2.98</v>
+      </c>
+      <c r="AB56">
+        <v>2.35</v>
+      </c>
+      <c r="AC56">
+        <v>1.1</v>
+      </c>
+      <c r="AD56">
+        <v>6.25</v>
+      </c>
+      <c r="AE56">
+        <v>1.55</v>
+      </c>
+      <c r="AF56">
+        <v>2.36</v>
+      </c>
+      <c r="AG56">
+        <v>2.37</v>
+      </c>
+      <c r="AH56">
+        <v>1.48</v>
+      </c>
+      <c r="AI56">
+        <v>2.1</v>
+      </c>
+      <c r="AJ56">
+        <v>1.67</v>
+      </c>
+      <c r="AK56">
+        <v>1.57</v>
+      </c>
+      <c r="AL56">
+        <v>1.36</v>
+      </c>
+      <c r="AM56">
+        <v>1.33</v>
+      </c>
+      <c r="AN56">
+        <v>1.33</v>
+      </c>
+      <c r="AO56">
+        <v>0.5</v>
+      </c>
+      <c r="AP56">
+        <v>1.25</v>
+      </c>
+      <c r="AQ56">
+        <v>0.67</v>
+      </c>
+      <c r="AR56">
+        <v>1.04</v>
+      </c>
+      <c r="AS56">
+        <v>1.21</v>
+      </c>
+      <c r="AT56">
+        <v>2.25</v>
+      </c>
+      <c r="AU56">
+        <v>2</v>
+      </c>
+      <c r="AV56">
+        <v>3</v>
+      </c>
+      <c r="AW56">
+        <v>1</v>
+      </c>
+      <c r="AX56">
+        <v>5</v>
+      </c>
+      <c r="AY56">
+        <v>3</v>
+      </c>
+      <c r="AZ56">
+        <v>8</v>
+      </c>
+      <c r="BA56">
+        <v>0</v>
+      </c>
+      <c r="BB56">
+        <v>6</v>
+      </c>
+      <c r="BC56">
+        <v>6</v>
+      </c>
+      <c r="BD56">
+        <v>2.1</v>
+      </c>
+      <c r="BE56">
+        <v>6.4</v>
+      </c>
+      <c r="BF56">
+        <v>1.9</v>
+      </c>
+      <c r="BG56">
+        <v>1.48</v>
+      </c>
+      <c r="BH56">
+        <v>2.45</v>
+      </c>
+      <c r="BI56">
+        <v>1.77</v>
+      </c>
+      <c r="BJ56">
+        <v>1.95</v>
+      </c>
+      <c r="BK56">
+        <v>2.25</v>
+      </c>
+      <c r="BL56">
+        <v>1.55</v>
+      </c>
+      <c r="BM56">
+        <v>2.95</v>
+      </c>
+      <c r="BN56">
+        <v>1.33</v>
+      </c>
+      <c r="BO56">
+        <v>3.95</v>
+      </c>
+      <c r="BP56">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:68">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>7821489</v>
+      </c>
+      <c r="C57" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="2">
+        <v>45739.83333333334</v>
+      </c>
+      <c r="F57">
+        <v>7</v>
+      </c>
+      <c r="G57" t="s">
+        <v>76</v>
+      </c>
+      <c r="H57" t="s">
+        <v>74</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57">
+        <v>2</v>
+      </c>
+      <c r="N57">
+        <v>3</v>
+      </c>
+      <c r="O57" t="s">
+        <v>126</v>
+      </c>
+      <c r="P57" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q57">
+        <v>2.88</v>
+      </c>
+      <c r="R57">
+        <v>2</v>
+      </c>
+      <c r="S57">
+        <v>4.33</v>
+      </c>
+      <c r="T57">
+        <v>1.53</v>
+      </c>
+      <c r="U57">
+        <v>2.38</v>
+      </c>
+      <c r="V57">
+        <v>3.5</v>
+      </c>
+      <c r="W57">
+        <v>1.29</v>
+      </c>
+      <c r="X57">
+        <v>11</v>
+      </c>
+      <c r="Y57">
+        <v>1.05</v>
+      </c>
+      <c r="Z57">
+        <v>2.2</v>
+      </c>
+      <c r="AA57">
+        <v>3.02</v>
+      </c>
+      <c r="AB57">
+        <v>3.5</v>
+      </c>
+      <c r="AC57">
+        <v>1.1</v>
+      </c>
+      <c r="AD57">
+        <v>6.82</v>
+      </c>
+      <c r="AE57">
+        <v>1.44</v>
+      </c>
+      <c r="AF57">
+        <v>2.78</v>
+      </c>
+      <c r="AG57">
+        <v>2.25</v>
+      </c>
+      <c r="AH57">
+        <v>1.53</v>
+      </c>
+      <c r="AI57">
+        <v>2</v>
+      </c>
+      <c r="AJ57">
+        <v>1.73</v>
+      </c>
+      <c r="AK57">
+        <v>1.3</v>
+      </c>
+      <c r="AL57">
+        <v>1.33</v>
+      </c>
+      <c r="AM57">
+        <v>1.65</v>
+      </c>
+      <c r="AN57">
+        <v>1.67</v>
+      </c>
+      <c r="AO57">
+        <v>0</v>
+      </c>
+      <c r="AP57">
+        <v>1.25</v>
+      </c>
+      <c r="AQ57">
+        <v>1</v>
+      </c>
+      <c r="AR57">
+        <v>1.22</v>
+      </c>
+      <c r="AS57">
+        <v>1.46</v>
+      </c>
+      <c r="AT57">
+        <v>2.68</v>
+      </c>
+      <c r="AU57">
+        <v>3</v>
+      </c>
+      <c r="AV57">
+        <v>6</v>
+      </c>
+      <c r="AW57">
+        <v>8</v>
+      </c>
+      <c r="AX57">
+        <v>9</v>
+      </c>
+      <c r="AY57">
+        <v>11</v>
+      </c>
+      <c r="AZ57">
+        <v>15</v>
+      </c>
+      <c r="BA57">
+        <v>4</v>
+      </c>
+      <c r="BB57">
+        <v>5</v>
+      </c>
+      <c r="BC57">
+        <v>9</v>
+      </c>
+      <c r="BD57">
+        <v>1.7</v>
+      </c>
+      <c r="BE57">
+        <v>6.4</v>
+      </c>
+      <c r="BF57">
+        <v>2.43</v>
+      </c>
+      <c r="BG57">
+        <v>1.54</v>
+      </c>
+      <c r="BH57">
+        <v>2.3</v>
+      </c>
+      <c r="BI57">
+        <v>1.8</v>
+      </c>
+      <c r="BJ57">
+        <v>1.91</v>
+      </c>
+      <c r="BK57">
+        <v>2.48</v>
+      </c>
+      <c r="BL57">
+        <v>1.47</v>
+      </c>
+      <c r="BM57">
+        <v>3.3</v>
+      </c>
+      <c r="BN57">
+        <v>1.28</v>
+      </c>
+      <c r="BO57">
+        <v>4.4</v>
+      </c>
+      <c r="BP57">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -391,7 +391,7 @@
     <t>['49', '88']</t>
   </si>
   <si>
-    <t>['6']</t>
+    <t>['5']</t>
   </si>
   <si>
     <t>['71']</t>
@@ -496,7 +496,7 @@
     <t>['23', '62', '79']</t>
   </si>
   <si>
-    <t>['9']</t>
+    <t>['89']</t>
   </si>
   <si>
     <t>['59', '90+7']</t>
@@ -12035,7 +12035,7 @@
         <v>124</v>
       </c>
       <c r="P55" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12241,7 +12241,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="Q56">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -499,7 +499,7 @@
     <t>['89']</t>
   </si>
   <si>
-    <t>['59', '90+7']</t>
+    <t>['60', '90+7']</t>
   </si>
 </sst>
 </file>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="167">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -397,6 +397,15 @@
     <t>['71']</t>
   </si>
   <si>
+    <t>['47']</t>
+  </si>
+  <si>
+    <t>['90+9']</t>
+  </si>
+  <si>
+    <t>['23', '83']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -500,6 +509,12 @@
   </si>
   <si>
     <t>['60', '90+7']</t>
+  </si>
+  <si>
+    <t>['87']</t>
+  </si>
+  <si>
+    <t>['9', '77']</t>
   </si>
 </sst>
 </file>
@@ -861,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP57"/>
+  <dimension ref="A1:BP61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1195,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ2">
         <v>1.75</v>
@@ -1404,7 +1419,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ3">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1529,7 +1544,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1735,7 +1750,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1941,7 +1956,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2228,7 +2243,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ7">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2640,7 +2655,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2765,7 +2780,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -2843,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ10">
         <v>0.67</v>
@@ -3049,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
         <v>0.33</v>
@@ -3177,7 +3192,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3255,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3383,7 +3398,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3461,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
         <v>1.33</v>
@@ -3795,7 +3810,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4082,7 +4097,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ16">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4207,7 +4222,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4619,7 +4634,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -5031,7 +5046,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5112,7 +5127,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ21">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5443,7 +5458,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5524,7 +5539,7 @@
         <v>1</v>
       </c>
       <c r="AQ23">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR23">
         <v>1.13</v>
@@ -5649,7 +5664,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5855,7 +5870,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5936,7 +5951,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ25">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR25">
         <v>0.8100000000000001</v>
@@ -6061,7 +6076,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6139,10 +6154,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ26">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR26">
         <v>1.13</v>
@@ -6267,7 +6282,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6345,7 +6360,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ27">
         <v>1.33</v>
@@ -6473,7 +6488,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6554,7 +6569,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ28">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR28">
         <v>1.09</v>
@@ -6679,7 +6694,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6757,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -6885,7 +6900,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7297,7 +7312,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7375,7 +7390,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ32">
         <v>2</v>
@@ -7503,7 +7518,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7709,7 +7724,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7915,7 +7930,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8121,7 +8136,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8327,7 +8342,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8408,7 +8423,7 @@
         <v>1</v>
       </c>
       <c r="AQ37">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR37">
         <v>1.46</v>
@@ -8533,7 +8548,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8614,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="AQ38">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR38">
         <v>1.12</v>
@@ -8739,7 +8754,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -9357,7 +9372,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9435,10 +9450,10 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ42">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
         <v>1.5</v>
@@ -9641,7 +9656,7 @@
         <v>1.67</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ43">
         <v>1.25</v>
@@ -9769,7 +9784,7 @@
         <v>91</v>
       </c>
       <c r="P44" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -9975,7 +9990,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q45">
         <v>3.2</v>
@@ -10181,7 +10196,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10465,10 +10480,10 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR47">
         <v>1.51</v>
@@ -10671,7 +10686,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ48">
         <v>1.33</v>
@@ -10799,7 +10814,7 @@
         <v>90</v>
       </c>
       <c r="P49" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -10880,7 +10895,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ49">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR49">
         <v>1.21</v>
@@ -11005,7 +11020,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q50">
         <v>2.55</v>
@@ -11211,7 +11226,7 @@
         <v>90</v>
       </c>
       <c r="P51" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q51">
         <v>2.05</v>
@@ -11417,7 +11432,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12116,7 +12131,7 @@
         <v>1</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR55">
         <v>1.23</v>
@@ -12241,7 +12256,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q56">
         <v>4</v>
@@ -12447,7 +12462,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12604,6 +12619,830 @@
       </c>
       <c r="BP57">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:68">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>7821493</v>
+      </c>
+      <c r="C58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="2">
+        <v>45741.83333333334</v>
+      </c>
+      <c r="F58">
+        <v>8</v>
+      </c>
+      <c r="G58" t="s">
+        <v>70</v>
+      </c>
+      <c r="H58" t="s">
+        <v>75</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>2</v>
+      </c>
+      <c r="O58" t="s">
+        <v>127</v>
+      </c>
+      <c r="P58" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q58">
+        <v>3.25</v>
+      </c>
+      <c r="R58">
+        <v>2.4</v>
+      </c>
+      <c r="S58">
+        <v>2.75</v>
+      </c>
+      <c r="T58">
+        <v>1.29</v>
+      </c>
+      <c r="U58">
+        <v>3.5</v>
+      </c>
+      <c r="V58">
+        <v>2.25</v>
+      </c>
+      <c r="W58">
+        <v>1.57</v>
+      </c>
+      <c r="X58">
+        <v>5.5</v>
+      </c>
+      <c r="Y58">
+        <v>1.14</v>
+      </c>
+      <c r="Z58">
+        <v>2.89</v>
+      </c>
+      <c r="AA58">
+        <v>3.27</v>
+      </c>
+      <c r="AB58">
+        <v>2.39</v>
+      </c>
+      <c r="AC58">
+        <v>1.04</v>
+      </c>
+      <c r="AD58">
+        <v>10.5</v>
+      </c>
+      <c r="AE58">
+        <v>1.23</v>
+      </c>
+      <c r="AF58">
+        <v>3.75</v>
+      </c>
+      <c r="AG58">
+        <v>1.68</v>
+      </c>
+      <c r="AH58">
+        <v>2.06</v>
+      </c>
+      <c r="AI58">
+        <v>1.44</v>
+      </c>
+      <c r="AJ58">
+        <v>2.63</v>
+      </c>
+      <c r="AK58">
+        <v>1.46</v>
+      </c>
+      <c r="AL58">
+        <v>1.29</v>
+      </c>
+      <c r="AM58">
+        <v>1.51</v>
+      </c>
+      <c r="AN58">
+        <v>2</v>
+      </c>
+      <c r="AO58">
+        <v>0.33</v>
+      </c>
+      <c r="AP58">
+        <v>1.8</v>
+      </c>
+      <c r="AQ58">
+        <v>0.5</v>
+      </c>
+      <c r="AR58">
+        <v>1.92</v>
+      </c>
+      <c r="AS58">
+        <v>1.39</v>
+      </c>
+      <c r="AT58">
+        <v>3.31</v>
+      </c>
+      <c r="AU58">
+        <v>3</v>
+      </c>
+      <c r="AV58">
+        <v>5</v>
+      </c>
+      <c r="AW58">
+        <v>5</v>
+      </c>
+      <c r="AX58">
+        <v>1</v>
+      </c>
+      <c r="AY58">
+        <v>8</v>
+      </c>
+      <c r="AZ58">
+        <v>6</v>
+      </c>
+      <c r="BA58">
+        <v>4</v>
+      </c>
+      <c r="BB58">
+        <v>3</v>
+      </c>
+      <c r="BC58">
+        <v>7</v>
+      </c>
+      <c r="BD58">
+        <v>1.95</v>
+      </c>
+      <c r="BE58">
+        <v>6.25</v>
+      </c>
+      <c r="BF58">
+        <v>2.07</v>
+      </c>
+      <c r="BG58">
+        <v>1.4</v>
+      </c>
+      <c r="BH58">
+        <v>2.7</v>
+      </c>
+      <c r="BI58">
+        <v>1.68</v>
+      </c>
+      <c r="BJ58">
+        <v>2.05</v>
+      </c>
+      <c r="BK58">
+        <v>2.07</v>
+      </c>
+      <c r="BL58">
+        <v>1.66</v>
+      </c>
+      <c r="BM58">
+        <v>2.65</v>
+      </c>
+      <c r="BN58">
+        <v>1.41</v>
+      </c>
+      <c r="BO58">
+        <v>3.55</v>
+      </c>
+      <c r="BP58">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:68">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>7821497</v>
+      </c>
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="2">
+        <v>45742.58333333334</v>
+      </c>
+      <c r="F59">
+        <v>8</v>
+      </c>
+      <c r="G59" t="s">
+        <v>80</v>
+      </c>
+      <c r="H59" t="s">
+        <v>81</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>1</v>
+      </c>
+      <c r="O59" t="s">
+        <v>128</v>
+      </c>
+      <c r="P59" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q59">
+        <v>2.5</v>
+      </c>
+      <c r="R59">
+        <v>2.4</v>
+      </c>
+      <c r="S59">
+        <v>3.75</v>
+      </c>
+      <c r="T59">
+        <v>1.29</v>
+      </c>
+      <c r="U59">
+        <v>3.5</v>
+      </c>
+      <c r="V59">
+        <v>2.25</v>
+      </c>
+      <c r="W59">
+        <v>1.57</v>
+      </c>
+      <c r="X59">
+        <v>5.5</v>
+      </c>
+      <c r="Y59">
+        <v>1.14</v>
+      </c>
+      <c r="Z59">
+        <v>2.04</v>
+      </c>
+      <c r="AA59">
+        <v>3.33</v>
+      </c>
+      <c r="AB59">
+        <v>3.59</v>
+      </c>
+      <c r="AC59">
+        <v>1.06</v>
+      </c>
+      <c r="AD59">
+        <v>8</v>
+      </c>
+      <c r="AE59">
+        <v>1.3</v>
+      </c>
+      <c r="AF59">
+        <v>3.3</v>
+      </c>
+      <c r="AG59">
+        <v>1.57</v>
+      </c>
+      <c r="AH59">
+        <v>2.15</v>
+      </c>
+      <c r="AI59">
+        <v>1.5</v>
+      </c>
+      <c r="AJ59">
+        <v>2.5</v>
+      </c>
+      <c r="AK59">
+        <v>1.24</v>
+      </c>
+      <c r="AL59">
+        <v>1.29</v>
+      </c>
+      <c r="AM59">
+        <v>1.83</v>
+      </c>
+      <c r="AN59">
+        <v>1</v>
+      </c>
+      <c r="AO59">
+        <v>0.5</v>
+      </c>
+      <c r="AP59">
+        <v>1.5</v>
+      </c>
+      <c r="AQ59">
+        <v>0.4</v>
+      </c>
+      <c r="AR59">
+        <v>1.4</v>
+      </c>
+      <c r="AS59">
+        <v>1.22</v>
+      </c>
+      <c r="AT59">
+        <v>2.62</v>
+      </c>
+      <c r="AU59">
+        <v>5</v>
+      </c>
+      <c r="AV59">
+        <v>3</v>
+      </c>
+      <c r="AW59">
+        <v>1</v>
+      </c>
+      <c r="AX59">
+        <v>1</v>
+      </c>
+      <c r="AY59">
+        <v>6</v>
+      </c>
+      <c r="AZ59">
+        <v>4</v>
+      </c>
+      <c r="BA59">
+        <v>0</v>
+      </c>
+      <c r="BB59">
+        <v>3</v>
+      </c>
+      <c r="BC59">
+        <v>3</v>
+      </c>
+      <c r="BD59">
+        <v>1.6</v>
+      </c>
+      <c r="BE59">
+        <v>6.75</v>
+      </c>
+      <c r="BF59">
+        <v>2.55</v>
+      </c>
+      <c r="BG59">
+        <v>1.34</v>
+      </c>
+      <c r="BH59">
+        <v>2.9</v>
+      </c>
+      <c r="BI59">
+        <v>1.58</v>
+      </c>
+      <c r="BJ59">
+        <v>2.2</v>
+      </c>
+      <c r="BK59">
+        <v>1.95</v>
+      </c>
+      <c r="BL59">
+        <v>1.75</v>
+      </c>
+      <c r="BM59">
+        <v>2.45</v>
+      </c>
+      <c r="BN59">
+        <v>1.48</v>
+      </c>
+      <c r="BO59">
+        <v>3.15</v>
+      </c>
+      <c r="BP59">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="60" spans="1:68">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>7821495</v>
+      </c>
+      <c r="C60" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" s="2">
+        <v>45742.6875</v>
+      </c>
+      <c r="F60">
+        <v>8</v>
+      </c>
+      <c r="G60" t="s">
+        <v>79</v>
+      </c>
+      <c r="H60" t="s">
+        <v>84</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>2</v>
+      </c>
+      <c r="L60">
+        <v>2</v>
+      </c>
+      <c r="M60">
+        <v>2</v>
+      </c>
+      <c r="N60">
+        <v>4</v>
+      </c>
+      <c r="O60" t="s">
+        <v>129</v>
+      </c>
+      <c r="P60" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q60">
+        <v>3.75</v>
+      </c>
+      <c r="R60">
+        <v>2.38</v>
+      </c>
+      <c r="S60">
+        <v>2.6</v>
+      </c>
+      <c r="T60">
+        <v>1.3</v>
+      </c>
+      <c r="U60">
+        <v>3.4</v>
+      </c>
+      <c r="V60">
+        <v>2.5</v>
+      </c>
+      <c r="W60">
+        <v>1.5</v>
+      </c>
+      <c r="X60">
+        <v>6</v>
+      </c>
+      <c r="Y60">
+        <v>1.13</v>
+      </c>
+      <c r="Z60">
+        <v>3.77</v>
+      </c>
+      <c r="AA60">
+        <v>3.27</v>
+      </c>
+      <c r="AB60">
+        <v>2.01</v>
+      </c>
+      <c r="AC60">
+        <v>1.04</v>
+      </c>
+      <c r="AD60">
+        <v>10.5</v>
+      </c>
+      <c r="AE60">
+        <v>1.23</v>
+      </c>
+      <c r="AF60">
+        <v>3.75</v>
+      </c>
+      <c r="AG60">
+        <v>1.65</v>
+      </c>
+      <c r="AH60">
+        <v>2.13</v>
+      </c>
+      <c r="AI60">
+        <v>1.53</v>
+      </c>
+      <c r="AJ60">
+        <v>2.38</v>
+      </c>
+      <c r="AK60">
+        <v>1.8</v>
+      </c>
+      <c r="AL60">
+        <v>1.27</v>
+      </c>
+      <c r="AM60">
+        <v>1.28</v>
+      </c>
+      <c r="AN60">
+        <v>3</v>
+      </c>
+      <c r="AO60">
+        <v>2.25</v>
+      </c>
+      <c r="AP60">
+        <v>2.5</v>
+      </c>
+      <c r="AQ60">
+        <v>2</v>
+      </c>
+      <c r="AR60">
+        <v>1.47</v>
+      </c>
+      <c r="AS60">
+        <v>1.77</v>
+      </c>
+      <c r="AT60">
+        <v>3.24</v>
+      </c>
+      <c r="AU60">
+        <v>8</v>
+      </c>
+      <c r="AV60">
+        <v>5</v>
+      </c>
+      <c r="AW60">
+        <v>2</v>
+      </c>
+      <c r="AX60">
+        <v>4</v>
+      </c>
+      <c r="AY60">
+        <v>10</v>
+      </c>
+      <c r="AZ60">
+        <v>9</v>
+      </c>
+      <c r="BA60">
+        <v>6</v>
+      </c>
+      <c r="BB60">
+        <v>4</v>
+      </c>
+      <c r="BC60">
+        <v>10</v>
+      </c>
+      <c r="BD60">
+        <v>2.75</v>
+      </c>
+      <c r="BE60">
+        <v>8.5</v>
+      </c>
+      <c r="BF60">
+        <v>1.55</v>
+      </c>
+      <c r="BG60">
+        <v>1.31</v>
+      </c>
+      <c r="BH60">
+        <v>2.92</v>
+      </c>
+      <c r="BI60">
+        <v>1.7</v>
+      </c>
+      <c r="BJ60">
+        <v>2.05</v>
+      </c>
+      <c r="BK60">
+        <v>2.01</v>
+      </c>
+      <c r="BL60">
+        <v>1.68</v>
+      </c>
+      <c r="BM60">
+        <v>2.62</v>
+      </c>
+      <c r="BN60">
+        <v>1.38</v>
+      </c>
+      <c r="BO60">
+        <v>3.68</v>
+      </c>
+      <c r="BP60">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:68">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>7821496</v>
+      </c>
+      <c r="C61" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="2">
+        <v>45742.79166666666</v>
+      </c>
+      <c r="F61">
+        <v>8</v>
+      </c>
+      <c r="G61" t="s">
+        <v>78</v>
+      </c>
+      <c r="H61" t="s">
+        <v>83</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>1</v>
+      </c>
+      <c r="N61">
+        <v>1</v>
+      </c>
+      <c r="O61" t="s">
+        <v>90</v>
+      </c>
+      <c r="P61" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q61">
+        <v>3.75</v>
+      </c>
+      <c r="R61">
+        <v>2</v>
+      </c>
+      <c r="S61">
+        <v>3.1</v>
+      </c>
+      <c r="T61">
+        <v>1.5</v>
+      </c>
+      <c r="U61">
+        <v>2.5</v>
+      </c>
+      <c r="V61">
+        <v>3.4</v>
+      </c>
+      <c r="W61">
+        <v>1.3</v>
+      </c>
+      <c r="X61">
+        <v>10</v>
+      </c>
+      <c r="Y61">
+        <v>1.06</v>
+      </c>
+      <c r="Z61">
+        <v>3.21</v>
+      </c>
+      <c r="AA61">
+        <v>3.27</v>
+      </c>
+      <c r="AB61">
+        <v>2.21</v>
+      </c>
+      <c r="AC61">
+        <v>3.61</v>
+      </c>
+      <c r="AD61">
+        <v>1.29</v>
+      </c>
+      <c r="AE61">
+        <v>1.48</v>
+      </c>
+      <c r="AF61">
+        <v>2.37</v>
+      </c>
+      <c r="AG61">
+        <v>2.2</v>
+      </c>
+      <c r="AH61">
+        <v>1.6</v>
+      </c>
+      <c r="AI61">
+        <v>1.91</v>
+      </c>
+      <c r="AJ61">
+        <v>1.8</v>
+      </c>
+      <c r="AK61">
+        <v>0</v>
+      </c>
+      <c r="AL61">
+        <v>0</v>
+      </c>
+      <c r="AM61">
+        <v>0</v>
+      </c>
+      <c r="AN61">
+        <v>2</v>
+      </c>
+      <c r="AO61">
+        <v>1.25</v>
+      </c>
+      <c r="AP61">
+        <v>1.5</v>
+      </c>
+      <c r="AQ61">
+        <v>1.6</v>
+      </c>
+      <c r="AR61">
+        <v>1.33</v>
+      </c>
+      <c r="AS61">
+        <v>1.3</v>
+      </c>
+      <c r="AT61">
+        <v>2.63</v>
+      </c>
+      <c r="AU61">
+        <v>4</v>
+      </c>
+      <c r="AV61">
+        <v>3</v>
+      </c>
+      <c r="AW61">
+        <v>6</v>
+      </c>
+      <c r="AX61">
+        <v>0</v>
+      </c>
+      <c r="AY61">
+        <v>10</v>
+      </c>
+      <c r="AZ61">
+        <v>3</v>
+      </c>
+      <c r="BA61">
+        <v>4</v>
+      </c>
+      <c r="BB61">
+        <v>5</v>
+      </c>
+      <c r="BC61">
+        <v>9</v>
+      </c>
+      <c r="BD61">
+        <v>0</v>
+      </c>
+      <c r="BE61">
+        <v>0</v>
+      </c>
+      <c r="BF61">
+        <v>0</v>
+      </c>
+      <c r="BG61">
+        <v>0</v>
+      </c>
+      <c r="BH61">
+        <v>0</v>
+      </c>
+      <c r="BI61">
+        <v>0</v>
+      </c>
+      <c r="BJ61">
+        <v>0</v>
+      </c>
+      <c r="BK61">
+        <v>0</v>
+      </c>
+      <c r="BL61">
+        <v>0</v>
+      </c>
+      <c r="BM61">
+        <v>0</v>
+      </c>
+      <c r="BN61">
+        <v>0</v>
+      </c>
+      <c r="BO61">
+        <v>0</v>
+      </c>
+      <c r="BP61">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -523,13 +523,13 @@
     <t>['8', '76']</t>
   </si>
   <si>
+    <t>['25']</t>
+  </si>
+  <si>
     <t>['57', '75']</t>
   </si>
   <si>
-    <t>['12']</t>
-  </si>
-  <si>
-    <t>['74']</t>
+    <t>['73']</t>
   </si>
 </sst>
 </file>
@@ -13504,10 +13504,10 @@
         <v>2</v>
       </c>
       <c r="O62" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="P62" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="Q62">
         <v>3.5</v>
@@ -13713,7 +13713,7 @@
         <v>90</v>
       </c>
       <c r="P63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -13919,7 +13919,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="Q64">
         <v>2.75</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="175">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -412,6 +412,9 @@
     <t>['69']</t>
   </si>
   <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -530,6 +533,12 @@
   </si>
   <si>
     <t>['73']</t>
+  </si>
+  <si>
+    <t>['74', '84']</t>
+  </si>
+  <si>
+    <t>['12']</t>
   </si>
 </sst>
 </file>
@@ -891,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP65"/>
+  <dimension ref="A1:BP68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1559,7 +1568,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1640,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1765,7 +1774,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1843,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ5">
         <v>1.6</v>
@@ -1971,7 +1980,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2052,7 +2061,7 @@
         <v>1</v>
       </c>
       <c r="AQ6">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2464,7 +2473,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ8">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2795,7 +2804,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3207,7 +3216,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3413,7 +3422,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3697,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ14">
         <v>1.75</v>
@@ -3825,7 +3834,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4109,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ16">
         <v>0.5</v>
@@ -4237,7 +4246,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4524,7 +4533,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR18">
         <v>0.9399999999999999</v>
@@ -4649,7 +4658,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4730,7 +4739,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ19">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR19">
         <v>1.03</v>
@@ -5061,7 +5070,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5348,7 +5357,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ22">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>1.38</v>
@@ -5473,7 +5482,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5551,7 +5560,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ23">
         <v>2</v>
@@ -5679,7 +5688,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5885,7 +5894,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6091,7 +6100,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6297,7 +6306,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6503,7 +6512,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6581,7 +6590,7 @@
         <v>1.5</v>
       </c>
       <c r="AP28">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ28">
         <v>2</v>
@@ -6709,7 +6718,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6915,7 +6924,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7327,7 +7336,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7533,7 +7542,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7611,7 +7620,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ33">
         <v>1.6</v>
@@ -7739,7 +7748,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7820,7 +7829,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ34">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR34">
         <v>1.43</v>
@@ -7945,7 +7954,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8026,7 +8035,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ35">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR35">
         <v>1.59</v>
@@ -8151,7 +8160,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8357,7 +8366,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8563,7 +8572,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8641,7 +8650,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ38">
         <v>1.6</v>
@@ -8769,7 +8778,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -8850,7 +8859,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ39">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR39">
         <v>1.68</v>
@@ -9387,7 +9396,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9799,7 +9808,7 @@
         <v>91</v>
       </c>
       <c r="P44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10005,7 +10014,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q45">
         <v>3.2</v>
@@ -10211,7 +10220,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10829,7 +10838,7 @@
         <v>90</v>
       </c>
       <c r="P49" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -10907,7 +10916,7 @@
         <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ49">
         <v>1.6</v>
@@ -11035,7 +11044,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q50">
         <v>2.55</v>
@@ -11241,7 +11250,7 @@
         <v>90</v>
       </c>
       <c r="P51" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q51">
         <v>2.05</v>
@@ -11322,7 +11331,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ51">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR51">
         <v>1.54</v>
@@ -11447,7 +11456,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11525,10 +11534,10 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ52">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR52">
         <v>1.22</v>
@@ -11734,7 +11743,7 @@
         <v>1</v>
       </c>
       <c r="AQ53">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR53">
         <v>1.8</v>
@@ -12143,7 +12152,7 @@
         <v>0.67</v>
       </c>
       <c r="AP55">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ55">
         <v>0.4</v>
@@ -12271,7 +12280,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q56">
         <v>4</v>
@@ -12477,7 +12486,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12683,7 +12692,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q58">
         <v>3.25</v>
@@ -13095,7 +13104,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q60">
         <v>3.75</v>
@@ -13507,7 +13516,7 @@
         <v>127</v>
       </c>
       <c r="P62" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q62">
         <v>3.5</v>
@@ -13713,7 +13722,7 @@
         <v>90</v>
       </c>
       <c r="P63" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -13919,7 +13928,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14125,7 +14134,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q65">
         <v>3.3</v>
@@ -14282,6 +14291,624 @@
       </c>
       <c r="BP65">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="66" spans="1:68">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>7821499</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45745.70833333334</v>
+      </c>
+      <c r="F66">
+        <v>9</v>
+      </c>
+      <c r="G66" t="s">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s">
+        <v>78</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="M66">
+        <v>2</v>
+      </c>
+      <c r="N66">
+        <v>3</v>
+      </c>
+      <c r="O66" t="s">
+        <v>132</v>
+      </c>
+      <c r="P66" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q66">
+        <v>3.5</v>
+      </c>
+      <c r="R66">
+        <v>1.95</v>
+      </c>
+      <c r="S66">
+        <v>3.5</v>
+      </c>
+      <c r="T66">
+        <v>1.53</v>
+      </c>
+      <c r="U66">
+        <v>2.38</v>
+      </c>
+      <c r="V66">
+        <v>3.75</v>
+      </c>
+      <c r="W66">
+        <v>1.25</v>
+      </c>
+      <c r="X66">
+        <v>11</v>
+      </c>
+      <c r="Y66">
+        <v>1.05</v>
+      </c>
+      <c r="Z66">
+        <v>2.84</v>
+      </c>
+      <c r="AA66">
+        <v>3.11</v>
+      </c>
+      <c r="AB66">
+        <v>2.52</v>
+      </c>
+      <c r="AC66">
+        <v>1.07</v>
+      </c>
+      <c r="AD66">
+        <v>7</v>
+      </c>
+      <c r="AE66">
+        <v>1.42</v>
+      </c>
+      <c r="AF66">
+        <v>2.62</v>
+      </c>
+      <c r="AG66">
+        <v>2.1</v>
+      </c>
+      <c r="AH66">
+        <v>1.6</v>
+      </c>
+      <c r="AI66">
+        <v>2.1</v>
+      </c>
+      <c r="AJ66">
+        <v>1.67</v>
+      </c>
+      <c r="AK66">
+        <v>1.55</v>
+      </c>
+      <c r="AL66">
+        <v>1.34</v>
+      </c>
+      <c r="AM66">
+        <v>1.42</v>
+      </c>
+      <c r="AN66">
+        <v>0.33</v>
+      </c>
+      <c r="AO66">
+        <v>2</v>
+      </c>
+      <c r="AP66">
+        <v>0.25</v>
+      </c>
+      <c r="AQ66">
+        <v>2.2</v>
+      </c>
+      <c r="AR66">
+        <v>1.21</v>
+      </c>
+      <c r="AS66">
+        <v>1.07</v>
+      </c>
+      <c r="AT66">
+        <v>2.28</v>
+      </c>
+      <c r="AU66">
+        <v>5</v>
+      </c>
+      <c r="AV66">
+        <v>6</v>
+      </c>
+      <c r="AW66">
+        <v>1</v>
+      </c>
+      <c r="AX66">
+        <v>2</v>
+      </c>
+      <c r="AY66">
+        <v>6</v>
+      </c>
+      <c r="AZ66">
+        <v>8</v>
+      </c>
+      <c r="BA66">
+        <v>6</v>
+      </c>
+      <c r="BB66">
+        <v>6</v>
+      </c>
+      <c r="BC66">
+        <v>12</v>
+      </c>
+      <c r="BD66">
+        <v>1.95</v>
+      </c>
+      <c r="BE66">
+        <v>8</v>
+      </c>
+      <c r="BF66">
+        <v>2.05</v>
+      </c>
+      <c r="BG66">
+        <v>1.44</v>
+      </c>
+      <c r="BH66">
+        <v>2.6</v>
+      </c>
+      <c r="BI66">
+        <v>1.78</v>
+      </c>
+      <c r="BJ66">
+        <v>2.03</v>
+      </c>
+      <c r="BK66">
+        <v>2.25</v>
+      </c>
+      <c r="BL66">
+        <v>1.63</v>
+      </c>
+      <c r="BM66">
+        <v>2.8</v>
+      </c>
+      <c r="BN66">
+        <v>1.38</v>
+      </c>
+      <c r="BO66">
+        <v>3.8</v>
+      </c>
+      <c r="BP66">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:68">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>7821500</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45745.80208333334</v>
+      </c>
+      <c r="F67">
+        <v>9</v>
+      </c>
+      <c r="G67" t="s">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s">
+        <v>79</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
+        <v>90</v>
+      </c>
+      <c r="P67" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q67">
+        <v>3.75</v>
+      </c>
+      <c r="R67">
+        <v>2</v>
+      </c>
+      <c r="S67">
+        <v>3.25</v>
+      </c>
+      <c r="T67">
+        <v>1.5</v>
+      </c>
+      <c r="U67">
+        <v>2.5</v>
+      </c>
+      <c r="V67">
+        <v>3.5</v>
+      </c>
+      <c r="W67">
+        <v>1.29</v>
+      </c>
+      <c r="X67">
+        <v>11</v>
+      </c>
+      <c r="Y67">
+        <v>1.05</v>
+      </c>
+      <c r="Z67">
+        <v>2.86</v>
+      </c>
+      <c r="AA67">
+        <v>3.11</v>
+      </c>
+      <c r="AB67">
+        <v>2.51</v>
+      </c>
+      <c r="AC67">
+        <v>1.04</v>
+      </c>
+      <c r="AD67">
+        <v>8.5</v>
+      </c>
+      <c r="AE67">
+        <v>1.33</v>
+      </c>
+      <c r="AF67">
+        <v>3</v>
+      </c>
+      <c r="AG67">
+        <v>1.91</v>
+      </c>
+      <c r="AH67">
+        <v>1.75</v>
+      </c>
+      <c r="AI67">
+        <v>1.91</v>
+      </c>
+      <c r="AJ67">
+        <v>1.8</v>
+      </c>
+      <c r="AK67">
+        <v>1.58</v>
+      </c>
+      <c r="AL67">
+        <v>1.31</v>
+      </c>
+      <c r="AM67">
+        <v>1.37</v>
+      </c>
+      <c r="AN67">
+        <v>0.33</v>
+      </c>
+      <c r="AO67">
+        <v>2</v>
+      </c>
+      <c r="AP67">
+        <v>0.25</v>
+      </c>
+      <c r="AQ67">
+        <v>2.2</v>
+      </c>
+      <c r="AR67">
+        <v>1.1</v>
+      </c>
+      <c r="AS67">
+        <v>1.29</v>
+      </c>
+      <c r="AT67">
+        <v>2.39</v>
+      </c>
+      <c r="AU67">
+        <v>6</v>
+      </c>
+      <c r="AV67">
+        <v>4</v>
+      </c>
+      <c r="AW67">
+        <v>7</v>
+      </c>
+      <c r="AX67">
+        <v>5</v>
+      </c>
+      <c r="AY67">
+        <v>13</v>
+      </c>
+      <c r="AZ67">
+        <v>9</v>
+      </c>
+      <c r="BA67">
+        <v>4</v>
+      </c>
+      <c r="BB67">
+        <v>2</v>
+      </c>
+      <c r="BC67">
+        <v>6</v>
+      </c>
+      <c r="BD67">
+        <v>2.05</v>
+      </c>
+      <c r="BE67">
+        <v>6</v>
+      </c>
+      <c r="BF67">
+        <v>2.16</v>
+      </c>
+      <c r="BG67">
+        <v>1.42</v>
+      </c>
+      <c r="BH67">
+        <v>2.62</v>
+      </c>
+      <c r="BI67">
+        <v>1.73</v>
+      </c>
+      <c r="BJ67">
+        <v>2.07</v>
+      </c>
+      <c r="BK67">
+        <v>2.17</v>
+      </c>
+      <c r="BL67">
+        <v>1.67</v>
+      </c>
+      <c r="BM67">
+        <v>2.7</v>
+      </c>
+      <c r="BN67">
+        <v>1.4</v>
+      </c>
+      <c r="BO67">
+        <v>3.6</v>
+      </c>
+      <c r="BP67">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:68">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>7821498</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="2">
+        <v>45746.41666666666</v>
+      </c>
+      <c r="F68">
+        <v>9</v>
+      </c>
+      <c r="G68" t="s">
+        <v>73</v>
+      </c>
+      <c r="H68" t="s">
+        <v>80</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68" t="s">
+        <v>90</v>
+      </c>
+      <c r="P68" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q68">
+        <v>3.75</v>
+      </c>
+      <c r="R68">
+        <v>2.1</v>
+      </c>
+      <c r="S68">
+        <v>2.88</v>
+      </c>
+      <c r="T68">
+        <v>1.4</v>
+      </c>
+      <c r="U68">
+        <v>2.75</v>
+      </c>
+      <c r="V68">
+        <v>3</v>
+      </c>
+      <c r="W68">
+        <v>1.36</v>
+      </c>
+      <c r="X68">
+        <v>8</v>
+      </c>
+      <c r="Y68">
+        <v>1.08</v>
+      </c>
+      <c r="Z68">
+        <v>3.21</v>
+      </c>
+      <c r="AA68">
+        <v>3.27</v>
+      </c>
+      <c r="AB68">
+        <v>2.21</v>
+      </c>
+      <c r="AC68">
+        <v>1.05</v>
+      </c>
+      <c r="AD68">
+        <v>8</v>
+      </c>
+      <c r="AE68">
+        <v>1.36</v>
+      </c>
+      <c r="AF68">
+        <v>2.9</v>
+      </c>
+      <c r="AG68">
+        <v>1.92</v>
+      </c>
+      <c r="AH68">
+        <v>1.82</v>
+      </c>
+      <c r="AI68">
+        <v>1.73</v>
+      </c>
+      <c r="AJ68">
+        <v>2</v>
+      </c>
+      <c r="AK68">
+        <v>1.66</v>
+      </c>
+      <c r="AL68">
+        <v>1.31</v>
+      </c>
+      <c r="AM68">
+        <v>1.32</v>
+      </c>
+      <c r="AN68">
+        <v>1</v>
+      </c>
+      <c r="AO68">
+        <v>1.75</v>
+      </c>
+      <c r="AP68">
+        <v>0.8</v>
+      </c>
+      <c r="AQ68">
+        <v>2</v>
+      </c>
+      <c r="AR68">
+        <v>1.34</v>
+      </c>
+      <c r="AS68">
+        <v>1.56</v>
+      </c>
+      <c r="AT68">
+        <v>2.9</v>
+      </c>
+      <c r="AU68">
+        <v>2</v>
+      </c>
+      <c r="AV68">
+        <v>3</v>
+      </c>
+      <c r="AW68">
+        <v>3</v>
+      </c>
+      <c r="AX68">
+        <v>2</v>
+      </c>
+      <c r="AY68">
+        <v>5</v>
+      </c>
+      <c r="AZ68">
+        <v>5</v>
+      </c>
+      <c r="BA68">
+        <v>11</v>
+      </c>
+      <c r="BB68">
+        <v>6</v>
+      </c>
+      <c r="BC68">
+        <v>17</v>
+      </c>
+      <c r="BD68">
+        <v>2.12</v>
+      </c>
+      <c r="BE68">
+        <v>6.4</v>
+      </c>
+      <c r="BF68">
+        <v>1.86</v>
+      </c>
+      <c r="BG68">
+        <v>1.33</v>
+      </c>
+      <c r="BH68">
+        <v>3</v>
+      </c>
+      <c r="BI68">
+        <v>1.59</v>
+      </c>
+      <c r="BJ68">
+        <v>2.31</v>
+      </c>
+      <c r="BK68">
+        <v>1.98</v>
+      </c>
+      <c r="BL68">
+        <v>1.82</v>
+      </c>
+      <c r="BM68">
+        <v>2.52</v>
+      </c>
+      <c r="BN68">
+        <v>1.5</v>
+      </c>
+      <c r="BO68">
+        <v>3.2</v>
+      </c>
+      <c r="BP68">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="179">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -415,6 +415,12 @@
     <t>['90+5']</t>
   </si>
   <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['16']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -539,6 +545,12 @@
   </si>
   <si>
     <t>['12']</t>
+  </si>
+  <si>
+    <t>['20', '90+4']</t>
+  </si>
+  <si>
+    <t>['28', '76']</t>
   </si>
 </sst>
 </file>
@@ -900,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP68"/>
+  <dimension ref="A1:BP71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1237,7 +1249,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ2">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1568,7 +1580,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1774,7 +1786,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1980,7 +1992,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2264,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ7">
         <v>2</v>
@@ -2804,7 +2816,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3216,7 +3228,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3422,7 +3434,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3834,7 +3846,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -3915,7 +3927,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4246,7 +4258,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4324,7 +4336,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ17">
         <v>1.6</v>
@@ -4658,7 +4670,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4945,7 +4957,7 @@
         <v>1</v>
       </c>
       <c r="AQ20">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR20">
         <v>1.31</v>
@@ -5070,7 +5082,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5148,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ21">
         <v>1.6</v>
@@ -5482,7 +5494,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5688,7 +5700,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5769,7 +5781,7 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR24">
         <v>1.43</v>
@@ -5894,7 +5906,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -5972,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ25">
         <v>0.4</v>
@@ -6100,7 +6112,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6306,7 +6318,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6512,7 +6524,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6718,7 +6730,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6924,7 +6936,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7336,7 +7348,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7542,7 +7554,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7748,7 +7760,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7826,7 +7838,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34">
         <v>2.2</v>
@@ -7954,7 +7966,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8160,7 +8172,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8241,7 +8253,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ36">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR36">
         <v>1.16</v>
@@ -8366,7 +8378,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8444,7 +8456,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ37">
         <v>0.4</v>
@@ -8572,7 +8584,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8778,7 +8790,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -8856,7 +8868,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ39">
         <v>2</v>
@@ -9065,7 +9077,7 @@
         <v>1</v>
       </c>
       <c r="AQ40">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR40">
         <v>1.35</v>
@@ -9271,7 +9283,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ41">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR41">
         <v>1.25</v>
@@ -9396,7 +9408,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9808,7 +9820,7 @@
         <v>91</v>
       </c>
       <c r="P44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10014,7 +10026,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q45">
         <v>3.2</v>
@@ -10220,7 +10232,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10838,7 +10850,7 @@
         <v>90</v>
       </c>
       <c r="P49" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11044,7 +11056,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q50">
         <v>2.55</v>
@@ -11122,10 +11134,10 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ50">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR50">
         <v>1.4</v>
@@ -11250,7 +11262,7 @@
         <v>90</v>
       </c>
       <c r="P51" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q51">
         <v>2.05</v>
@@ -11328,7 +11340,7 @@
         <v>1.67</v>
       </c>
       <c r="AP51">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ51">
         <v>2.2</v>
@@ -11456,7 +11468,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11740,7 +11752,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ53">
         <v>2.2</v>
@@ -11949,7 +11961,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ54">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR54">
         <v>1.45</v>
@@ -12280,7 +12292,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q56">
         <v>4</v>
@@ -12361,7 +12373,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ56">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR56">
         <v>1.04</v>
@@ -12486,7 +12498,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12692,7 +12704,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q58">
         <v>3.25</v>
@@ -13104,7 +13116,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q60">
         <v>3.75</v>
@@ -13516,7 +13528,7 @@
         <v>127</v>
       </c>
       <c r="P62" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q62">
         <v>3.5</v>
@@ -13722,7 +13734,7 @@
         <v>90</v>
       </c>
       <c r="P63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -13928,7 +13940,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14134,7 +14146,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q65">
         <v>3.3</v>
@@ -14340,7 +14352,7 @@
         <v>132</v>
       </c>
       <c r="P66" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q66">
         <v>3.5</v>
@@ -14752,7 +14764,7 @@
         <v>90</v>
       </c>
       <c r="P68" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q68">
         <v>3.75</v>
@@ -14909,6 +14921,624 @@
       </c>
       <c r="BP68">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:68">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>7821501</v>
+      </c>
+      <c r="C69" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="2">
+        <v>45746.625</v>
+      </c>
+      <c r="F69">
+        <v>9</v>
+      </c>
+      <c r="G69" t="s">
+        <v>84</v>
+      </c>
+      <c r="H69" t="s">
+        <v>82</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69">
+        <v>2</v>
+      </c>
+      <c r="N69">
+        <v>3</v>
+      </c>
+      <c r="O69" t="s">
+        <v>133</v>
+      </c>
+      <c r="P69" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q69">
+        <v>1.91</v>
+      </c>
+      <c r="R69">
+        <v>2.5</v>
+      </c>
+      <c r="S69">
+        <v>6.5</v>
+      </c>
+      <c r="T69">
+        <v>1.3</v>
+      </c>
+      <c r="U69">
+        <v>3.4</v>
+      </c>
+      <c r="V69">
+        <v>2.5</v>
+      </c>
+      <c r="W69">
+        <v>1.5</v>
+      </c>
+      <c r="X69">
+        <v>6</v>
+      </c>
+      <c r="Y69">
+        <v>1.13</v>
+      </c>
+      <c r="Z69">
+        <v>1.43</v>
+      </c>
+      <c r="AA69">
+        <v>4.33</v>
+      </c>
+      <c r="AB69">
+        <v>7.2</v>
+      </c>
+      <c r="AC69">
+        <v>1.03</v>
+      </c>
+      <c r="AD69">
+        <v>10</v>
+      </c>
+      <c r="AE69">
+        <v>1.22</v>
+      </c>
+      <c r="AF69">
+        <v>4</v>
+      </c>
+      <c r="AG69">
+        <v>1.6</v>
+      </c>
+      <c r="AH69">
+        <v>2.1</v>
+      </c>
+      <c r="AI69">
+        <v>1.8</v>
+      </c>
+      <c r="AJ69">
+        <v>1.91</v>
+      </c>
+      <c r="AK69">
+        <v>1.09</v>
+      </c>
+      <c r="AL69">
+        <v>1.18</v>
+      </c>
+      <c r="AM69">
+        <v>2.9</v>
+      </c>
+      <c r="AN69">
+        <v>1</v>
+      </c>
+      <c r="AO69">
+        <v>1.75</v>
+      </c>
+      <c r="AP69">
+        <v>0.75</v>
+      </c>
+      <c r="AQ69">
+        <v>2</v>
+      </c>
+      <c r="AR69">
+        <v>1.78</v>
+      </c>
+      <c r="AS69">
+        <v>1.47</v>
+      </c>
+      <c r="AT69">
+        <v>3.25</v>
+      </c>
+      <c r="AU69">
+        <v>3</v>
+      </c>
+      <c r="AV69">
+        <v>3</v>
+      </c>
+      <c r="AW69">
+        <v>1</v>
+      </c>
+      <c r="AX69">
+        <v>0</v>
+      </c>
+      <c r="AY69">
+        <v>4</v>
+      </c>
+      <c r="AZ69">
+        <v>3</v>
+      </c>
+      <c r="BA69">
+        <v>5</v>
+      </c>
+      <c r="BB69">
+        <v>1</v>
+      </c>
+      <c r="BC69">
+        <v>6</v>
+      </c>
+      <c r="BD69">
+        <v>1.22</v>
+      </c>
+      <c r="BE69">
+        <v>10</v>
+      </c>
+      <c r="BF69">
+        <v>5.05</v>
+      </c>
+      <c r="BG69">
+        <v>1.29</v>
+      </c>
+      <c r="BH69">
+        <v>3.04</v>
+      </c>
+      <c r="BI69">
+        <v>1.7</v>
+      </c>
+      <c r="BJ69">
+        <v>2.05</v>
+      </c>
+      <c r="BK69">
+        <v>2.05</v>
+      </c>
+      <c r="BL69">
+        <v>1.7</v>
+      </c>
+      <c r="BM69">
+        <v>2.56</v>
+      </c>
+      <c r="BN69">
+        <v>1.4</v>
+      </c>
+      <c r="BO69">
+        <v>3.5</v>
+      </c>
+      <c r="BP69">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:68">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>7821503</v>
+      </c>
+      <c r="C70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="2">
+        <v>45746.75</v>
+      </c>
+      <c r="F70">
+        <v>9</v>
+      </c>
+      <c r="G70" t="s">
+        <v>75</v>
+      </c>
+      <c r="H70" t="s">
+        <v>72</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>2</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70">
+        <v>2</v>
+      </c>
+      <c r="O70" t="s">
+        <v>134</v>
+      </c>
+      <c r="P70" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q70">
+        <v>2.88</v>
+      </c>
+      <c r="R70">
+        <v>2.1</v>
+      </c>
+      <c r="S70">
+        <v>4</v>
+      </c>
+      <c r="T70">
+        <v>1.44</v>
+      </c>
+      <c r="U70">
+        <v>2.63</v>
+      </c>
+      <c r="V70">
+        <v>3.25</v>
+      </c>
+      <c r="W70">
+        <v>1.33</v>
+      </c>
+      <c r="X70">
+        <v>9</v>
+      </c>
+      <c r="Y70">
+        <v>1.07</v>
+      </c>
+      <c r="Z70">
+        <v>2.24</v>
+      </c>
+      <c r="AA70">
+        <v>3.23</v>
+      </c>
+      <c r="AB70">
+        <v>3.18</v>
+      </c>
+      <c r="AC70">
+        <v>1.08</v>
+      </c>
+      <c r="AD70">
+        <v>6.5</v>
+      </c>
+      <c r="AE70">
+        <v>1.48</v>
+      </c>
+      <c r="AF70">
+        <v>2.5</v>
+      </c>
+      <c r="AG70">
+        <v>2.1</v>
+      </c>
+      <c r="AH70">
+        <v>1.61</v>
+      </c>
+      <c r="AI70">
+        <v>1.8</v>
+      </c>
+      <c r="AJ70">
+        <v>1.91</v>
+      </c>
+      <c r="AK70">
+        <v>1.36</v>
+      </c>
+      <c r="AL70">
+        <v>1.33</v>
+      </c>
+      <c r="AM70">
+        <v>1.57</v>
+      </c>
+      <c r="AN70">
+        <v>1.75</v>
+      </c>
+      <c r="AO70">
+        <v>0.67</v>
+      </c>
+      <c r="AP70">
+        <v>1.6</v>
+      </c>
+      <c r="AQ70">
+        <v>0.75</v>
+      </c>
+      <c r="AR70">
+        <v>1.41</v>
+      </c>
+      <c r="AS70">
+        <v>1.21</v>
+      </c>
+      <c r="AT70">
+        <v>2.62</v>
+      </c>
+      <c r="AU70">
+        <v>4</v>
+      </c>
+      <c r="AV70">
+        <v>8</v>
+      </c>
+      <c r="AW70">
+        <v>5</v>
+      </c>
+      <c r="AX70">
+        <v>5</v>
+      </c>
+      <c r="AY70">
+        <v>9</v>
+      </c>
+      <c r="AZ70">
+        <v>13</v>
+      </c>
+      <c r="BA70">
+        <v>3</v>
+      </c>
+      <c r="BB70">
+        <v>4</v>
+      </c>
+      <c r="BC70">
+        <v>7</v>
+      </c>
+      <c r="BD70">
+        <v>1.61</v>
+      </c>
+      <c r="BE70">
+        <v>8</v>
+      </c>
+      <c r="BF70">
+        <v>2.69</v>
+      </c>
+      <c r="BG70">
+        <v>1.34</v>
+      </c>
+      <c r="BH70">
+        <v>2.78</v>
+      </c>
+      <c r="BI70">
+        <v>1.7</v>
+      </c>
+      <c r="BJ70">
+        <v>2.05</v>
+      </c>
+      <c r="BK70">
+        <v>2.05</v>
+      </c>
+      <c r="BL70">
+        <v>1.7</v>
+      </c>
+      <c r="BM70">
+        <v>2.78</v>
+      </c>
+      <c r="BN70">
+        <v>1.34</v>
+      </c>
+      <c r="BO70">
+        <v>3.3</v>
+      </c>
+      <c r="BP70">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:68">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>7821502</v>
+      </c>
+      <c r="C71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="2">
+        <v>45746.85416666666</v>
+      </c>
+      <c r="F71">
+        <v>9</v>
+      </c>
+      <c r="G71" t="s">
+        <v>85</v>
+      </c>
+      <c r="H71" t="s">
+        <v>70</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>2</v>
+      </c>
+      <c r="N71">
+        <v>2</v>
+      </c>
+      <c r="O71" t="s">
+        <v>90</v>
+      </c>
+      <c r="P71" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q71">
+        <v>1.91</v>
+      </c>
+      <c r="R71">
+        <v>2.3</v>
+      </c>
+      <c r="S71">
+        <v>8</v>
+      </c>
+      <c r="T71">
+        <v>1.4</v>
+      </c>
+      <c r="U71">
+        <v>2.75</v>
+      </c>
+      <c r="V71">
+        <v>3</v>
+      </c>
+      <c r="W71">
+        <v>1.36</v>
+      </c>
+      <c r="X71">
+        <v>8</v>
+      </c>
+      <c r="Y71">
+        <v>1.08</v>
+      </c>
+      <c r="Z71">
+        <v>1.37</v>
+      </c>
+      <c r="AA71">
+        <v>4.5</v>
+      </c>
+      <c r="AB71">
+        <v>8.5</v>
+      </c>
+      <c r="AC71">
+        <v>1.04</v>
+      </c>
+      <c r="AD71">
+        <v>8.5</v>
+      </c>
+      <c r="AE71">
+        <v>1.33</v>
+      </c>
+      <c r="AF71">
+        <v>3</v>
+      </c>
+      <c r="AG71">
+        <v>1.92</v>
+      </c>
+      <c r="AH71">
+        <v>1.82</v>
+      </c>
+      <c r="AI71">
+        <v>2.25</v>
+      </c>
+      <c r="AJ71">
+        <v>1.57</v>
+      </c>
+      <c r="AK71">
+        <v>1.1</v>
+      </c>
+      <c r="AL71">
+        <v>1.21</v>
+      </c>
+      <c r="AM71">
+        <v>2.65</v>
+      </c>
+      <c r="AN71">
+        <v>0.33</v>
+      </c>
+      <c r="AO71">
+        <v>0.67</v>
+      </c>
+      <c r="AP71">
+        <v>0.25</v>
+      </c>
+      <c r="AQ71">
+        <v>1.25</v>
+      </c>
+      <c r="AR71">
+        <v>1.82</v>
+      </c>
+      <c r="AS71">
+        <v>1.15</v>
+      </c>
+      <c r="AT71">
+        <v>2.97</v>
+      </c>
+      <c r="AU71">
+        <v>2</v>
+      </c>
+      <c r="AV71">
+        <v>5</v>
+      </c>
+      <c r="AW71">
+        <v>4</v>
+      </c>
+      <c r="AX71">
+        <v>3</v>
+      </c>
+      <c r="AY71">
+        <v>6</v>
+      </c>
+      <c r="AZ71">
+        <v>8</v>
+      </c>
+      <c r="BA71">
+        <v>7</v>
+      </c>
+      <c r="BB71">
+        <v>9</v>
+      </c>
+      <c r="BC71">
+        <v>16</v>
+      </c>
+      <c r="BD71">
+        <v>1.21</v>
+      </c>
+      <c r="BE71">
+        <v>8.4</v>
+      </c>
+      <c r="BF71">
+        <v>5.8</v>
+      </c>
+      <c r="BG71">
+        <v>1.38</v>
+      </c>
+      <c r="BH71">
+        <v>2.8</v>
+      </c>
+      <c r="BI71">
+        <v>1.66</v>
+      </c>
+      <c r="BJ71">
+        <v>2.18</v>
+      </c>
+      <c r="BK71">
+        <v>2.08</v>
+      </c>
+      <c r="BL71">
+        <v>1.72</v>
+      </c>
+      <c r="BM71">
+        <v>2.62</v>
+      </c>
+      <c r="BN71">
+        <v>1.42</v>
+      </c>
+      <c r="BO71">
+        <v>3.4</v>
+      </c>
+      <c r="BP71">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="182">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -418,7 +418,13 @@
     <t>['62']</t>
   </si>
   <si>
-    <t>['16']</t>
+    <t>['15']</t>
+  </si>
+  <si>
+    <t>['45', '50']</t>
+  </si>
+  <si>
+    <t>['64', '73']</t>
   </si>
   <si>
     <t>['11']</t>
@@ -544,13 +550,16 @@
     <t>['74', '84']</t>
   </si>
   <si>
-    <t>['12']</t>
-  </si>
-  <si>
-    <t>['20', '90+4']</t>
-  </si>
-  <si>
-    <t>['28', '76']</t>
+    <t>['19', '90+4']</t>
+  </si>
+  <si>
+    <t>['10']</t>
+  </si>
+  <si>
+    <t>['27', '76']</t>
+  </si>
+  <si>
+    <t>['43']</t>
   </si>
 </sst>
 </file>
@@ -912,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP71"/>
+  <dimension ref="A1:BP73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1452,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>1.6</v>
@@ -1580,7 +1589,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1786,7 +1795,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1992,7 +2001,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2688,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9">
         <v>0.4</v>
@@ -2816,7 +2825,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3103,7 +3112,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3228,7 +3237,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3309,7 +3318,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3434,7 +3443,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3846,7 +3855,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -4258,7 +4267,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4542,7 +4551,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ18">
         <v>2.2</v>
@@ -4670,7 +4679,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -5082,7 +5091,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5366,7 +5375,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ22">
         <v>2</v>
@@ -5494,7 +5503,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5700,7 +5709,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5906,7 +5915,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6112,7 +6121,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6318,7 +6327,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6524,7 +6533,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6730,7 +6739,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6811,7 +6820,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR29">
         <v>2.06</v>
@@ -6936,7 +6945,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7223,7 +7232,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ31">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR31">
         <v>1.31</v>
@@ -7348,7 +7357,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7554,7 +7563,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7760,7 +7769,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7966,7 +7975,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8044,7 +8053,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
         <v>2.2</v>
@@ -8172,7 +8181,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8250,7 +8259,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ36">
         <v>2</v>
@@ -8378,7 +8387,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8584,7 +8593,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8790,7 +8799,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -9408,7 +9417,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9820,7 +9829,7 @@
         <v>91</v>
       </c>
       <c r="P44" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10026,7 +10035,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q45">
         <v>3.2</v>
@@ -10107,7 +10116,7 @@
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR45">
         <v>1.52</v>
@@ -10232,7 +10241,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10850,7 +10859,7 @@
         <v>90</v>
       </c>
       <c r="P49" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11056,7 +11065,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q50">
         <v>2.55</v>
@@ -11262,7 +11271,7 @@
         <v>90</v>
       </c>
       <c r="P51" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q51">
         <v>2.05</v>
@@ -11468,7 +11477,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11958,7 +11967,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ54">
         <v>1.25</v>
@@ -12292,7 +12301,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q56">
         <v>4</v>
@@ -12370,7 +12379,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ56">
         <v>0.75</v>
@@ -12498,7 +12507,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12579,7 +12588,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR57">
         <v>1.22</v>
@@ -12704,7 +12713,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q58">
         <v>3.25</v>
@@ -13116,7 +13125,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q60">
         <v>3.75</v>
@@ -13528,7 +13537,7 @@
         <v>127</v>
       </c>
       <c r="P62" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q62">
         <v>3.5</v>
@@ -13734,7 +13743,7 @@
         <v>90</v>
       </c>
       <c r="P63" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -13940,7 +13949,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14146,7 +14155,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q65">
         <v>3.3</v>
@@ -14352,7 +14361,7 @@
         <v>132</v>
       </c>
       <c r="P66" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q66">
         <v>3.5</v>
@@ -14764,7 +14773,7 @@
         <v>90</v>
       </c>
       <c r="P68" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="Q68">
         <v>3.75</v>
@@ -14970,7 +14979,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15176,7 +15185,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15382,7 +15391,7 @@
         <v>90</v>
       </c>
       <c r="P71" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q71">
         <v>1.91</v>
@@ -15539,6 +15548,418 @@
       </c>
       <c r="BP71">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:68">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>7821505</v>
+      </c>
+      <c r="C72" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45747.79166666666</v>
+      </c>
+      <c r="F72">
+        <v>9</v>
+      </c>
+      <c r="G72" t="s">
+        <v>77</v>
+      </c>
+      <c r="H72" t="s">
+        <v>76</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>2</v>
+      </c>
+      <c r="L72">
+        <v>2</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>3</v>
+      </c>
+      <c r="O72" t="s">
+        <v>135</v>
+      </c>
+      <c r="P72" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q72">
+        <v>3.5</v>
+      </c>
+      <c r="R72">
+        <v>1.95</v>
+      </c>
+      <c r="S72">
+        <v>3.5</v>
+      </c>
+      <c r="T72">
+        <v>1.53</v>
+      </c>
+      <c r="U72">
+        <v>2.38</v>
+      </c>
+      <c r="V72">
+        <v>3.5</v>
+      </c>
+      <c r="W72">
+        <v>1.29</v>
+      </c>
+      <c r="X72">
+        <v>11</v>
+      </c>
+      <c r="Y72">
+        <v>1.05</v>
+      </c>
+      <c r="Z72">
+        <v>2.63</v>
+      </c>
+      <c r="AA72">
+        <v>3.03</v>
+      </c>
+      <c r="AB72">
+        <v>2.78</v>
+      </c>
+      <c r="AC72">
+        <v>1.1</v>
+      </c>
+      <c r="AD72">
+        <v>5.75</v>
+      </c>
+      <c r="AE72">
+        <v>1.54</v>
+      </c>
+      <c r="AF72">
+        <v>2.37</v>
+      </c>
+      <c r="AG72">
+        <v>2.25</v>
+      </c>
+      <c r="AH72">
+        <v>1.53</v>
+      </c>
+      <c r="AI72">
+        <v>1.91</v>
+      </c>
+      <c r="AJ72">
+        <v>1.8</v>
+      </c>
+      <c r="AK72">
+        <v>1.44</v>
+      </c>
+      <c r="AL72">
+        <v>1.38</v>
+      </c>
+      <c r="AM72">
+        <v>1.42</v>
+      </c>
+      <c r="AN72">
+        <v>1.25</v>
+      </c>
+      <c r="AO72">
+        <v>0.33</v>
+      </c>
+      <c r="AP72">
+        <v>1.6</v>
+      </c>
+      <c r="AQ72">
+        <v>0.25</v>
+      </c>
+      <c r="AR72">
+        <v>0.95</v>
+      </c>
+      <c r="AS72">
+        <v>1.04</v>
+      </c>
+      <c r="AT72">
+        <v>1.99</v>
+      </c>
+      <c r="AU72">
+        <v>6</v>
+      </c>
+      <c r="AV72">
+        <v>5</v>
+      </c>
+      <c r="AW72">
+        <v>4</v>
+      </c>
+      <c r="AX72">
+        <v>4</v>
+      </c>
+      <c r="AY72">
+        <v>10</v>
+      </c>
+      <c r="AZ72">
+        <v>9</v>
+      </c>
+      <c r="BA72">
+        <v>6</v>
+      </c>
+      <c r="BB72">
+        <v>5</v>
+      </c>
+      <c r="BC72">
+        <v>11</v>
+      </c>
+      <c r="BD72">
+        <v>1.76</v>
+      </c>
+      <c r="BE72">
+        <v>7.9</v>
+      </c>
+      <c r="BF72">
+        <v>2.36</v>
+      </c>
+      <c r="BG72">
+        <v>1.38</v>
+      </c>
+      <c r="BH72">
+        <v>2.8</v>
+      </c>
+      <c r="BI72">
+        <v>1.65</v>
+      </c>
+      <c r="BJ72">
+        <v>2.2</v>
+      </c>
+      <c r="BK72">
+        <v>2.06</v>
+      </c>
+      <c r="BL72">
+        <v>1.74</v>
+      </c>
+      <c r="BM72">
+        <v>2.62</v>
+      </c>
+      <c r="BN72">
+        <v>1.42</v>
+      </c>
+      <c r="BO72">
+        <v>3.4</v>
+      </c>
+      <c r="BP72">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="73" spans="1:68">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>7821504</v>
+      </c>
+      <c r="C73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45747.88541666666</v>
+      </c>
+      <c r="F73">
+        <v>9</v>
+      </c>
+      <c r="G73" t="s">
+        <v>71</v>
+      </c>
+      <c r="H73" t="s">
+        <v>74</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>2</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>2</v>
+      </c>
+      <c r="O73" t="s">
+        <v>136</v>
+      </c>
+      <c r="P73" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q73">
+        <v>2.38</v>
+      </c>
+      <c r="R73">
+        <v>2.2</v>
+      </c>
+      <c r="S73">
+        <v>5</v>
+      </c>
+      <c r="T73">
+        <v>1.4</v>
+      </c>
+      <c r="U73">
+        <v>2.75</v>
+      </c>
+      <c r="V73">
+        <v>2.75</v>
+      </c>
+      <c r="W73">
+        <v>1.4</v>
+      </c>
+      <c r="X73">
+        <v>8</v>
+      </c>
+      <c r="Y73">
+        <v>1.08</v>
+      </c>
+      <c r="Z73">
+        <v>1.75</v>
+      </c>
+      <c r="AA73">
+        <v>3.57</v>
+      </c>
+      <c r="AB73">
+        <v>4.6</v>
+      </c>
+      <c r="AC73">
+        <v>1.03</v>
+      </c>
+      <c r="AD73">
+        <v>9</v>
+      </c>
+      <c r="AE73">
+        <v>1.29</v>
+      </c>
+      <c r="AF73">
+        <v>3.3</v>
+      </c>
+      <c r="AG73">
+        <v>1.63</v>
+      </c>
+      <c r="AH73">
+        <v>2.15</v>
+      </c>
+      <c r="AI73">
+        <v>1.8</v>
+      </c>
+      <c r="AJ73">
+        <v>1.91</v>
+      </c>
+      <c r="AK73">
+        <v>1.21</v>
+      </c>
+      <c r="AL73">
+        <v>1.26</v>
+      </c>
+      <c r="AM73">
+        <v>2</v>
+      </c>
+      <c r="AN73">
+        <v>1.75</v>
+      </c>
+      <c r="AO73">
+        <v>1</v>
+      </c>
+      <c r="AP73">
+        <v>2</v>
+      </c>
+      <c r="AQ73">
+        <v>0.75</v>
+      </c>
+      <c r="AR73">
+        <v>1.37</v>
+      </c>
+      <c r="AS73">
+        <v>1.55</v>
+      </c>
+      <c r="AT73">
+        <v>2.92</v>
+      </c>
+      <c r="AU73">
+        <v>9</v>
+      </c>
+      <c r="AV73">
+        <v>6</v>
+      </c>
+      <c r="AW73">
+        <v>8</v>
+      </c>
+      <c r="AX73">
+        <v>4</v>
+      </c>
+      <c r="AY73">
+        <v>17</v>
+      </c>
+      <c r="AZ73">
+        <v>10</v>
+      </c>
+      <c r="BA73">
+        <v>11</v>
+      </c>
+      <c r="BB73">
+        <v>1</v>
+      </c>
+      <c r="BC73">
+        <v>12</v>
+      </c>
+      <c r="BD73">
+        <v>1.43</v>
+      </c>
+      <c r="BE73">
+        <v>8.5</v>
+      </c>
+      <c r="BF73">
+        <v>3.32</v>
+      </c>
+      <c r="BG73">
+        <v>1.33</v>
+      </c>
+      <c r="BH73">
+        <v>3</v>
+      </c>
+      <c r="BI73">
+        <v>1.59</v>
+      </c>
+      <c r="BJ73">
+        <v>2.31</v>
+      </c>
+      <c r="BK73">
+        <v>1.98</v>
+      </c>
+      <c r="BL73">
+        <v>1.81</v>
+      </c>
+      <c r="BM73">
+        <v>2.55</v>
+      </c>
+      <c r="BN73">
+        <v>1.49</v>
+      </c>
+      <c r="BO73">
+        <v>3.2</v>
+      </c>
+      <c r="BP73">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="181">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -421,7 +421,7 @@
     <t>['15']</t>
   </si>
   <si>
-    <t>['45', '50']</t>
+    <t>['44', '50']</t>
   </si>
   <si>
     <t>['64', '73']</t>
@@ -557,9 +557,6 @@
   </si>
   <si>
     <t>['27', '76']</t>
-  </si>
-  <si>
-    <t>['43']</t>
   </si>
 </sst>
 </file>
@@ -15597,7 +15594,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>181</v>
+        <v>102</v>
       </c>
       <c r="Q72">
         <v>3.5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="184">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -427,6 +427,9 @@
     <t>['64', '73']</t>
   </si>
   <si>
+    <t>['3', '31', '42', '66']</t>
+  </si>
+  <si>
     <t>['11']</t>
   </si>
   <si>
@@ -557,6 +560,12 @@
   </si>
   <si>
     <t>['27', '76']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
+    <t>['27']</t>
   </si>
 </sst>
 </file>
@@ -918,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP73"/>
+  <dimension ref="A1:BP75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1461,7 +1470,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1586,7 +1595,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1664,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ4">
         <v>2.2</v>
@@ -1792,7 +1801,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q5">
         <v>8.5</v>
@@ -1873,7 +1882,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ5">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1998,7 +2007,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -2822,7 +2831,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q10">
         <v>2.74</v>
@@ -3234,7 +3243,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q12">
         <v>2.59</v>
@@ -3440,7 +3449,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3852,7 +3861,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q15">
         <v>3.8</v>
@@ -3930,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>0.75</v>
@@ -4264,7 +4273,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -4345,7 +4354,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ17">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4676,7 +4685,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q19">
         <v>3.35</v>
@@ -4960,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ20">
         <v>1.25</v>
@@ -5088,7 +5097,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -5169,7 +5178,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ21">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5500,7 +5509,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q23">
         <v>8.5</v>
@@ -5706,7 +5715,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5912,7 +5921,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6118,7 +6127,7 @@
         <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
@@ -6324,7 +6333,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -6530,7 +6539,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q28">
         <v>6.5</v>
@@ -6736,7 +6745,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q29">
         <v>2.65</v>
@@ -6942,7 +6951,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -7020,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ30">
         <v>0.75</v>
@@ -7226,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>0.25</v>
@@ -7354,7 +7363,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7560,7 +7569,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -7641,7 +7650,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ33">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR33">
         <v>0.93</v>
@@ -7766,7 +7775,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q34">
         <v>2.35</v>
@@ -7972,7 +7981,7 @@
         <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -8178,7 +8187,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8384,7 +8393,7 @@
         <v>113</v>
       </c>
       <c r="P37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8590,7 +8599,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q38">
         <v>3.25</v>
@@ -8671,7 +8680,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ38">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR38">
         <v>1.12</v>
@@ -8796,7 +8805,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q39">
         <v>2.05</v>
@@ -9414,7 +9423,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9701,7 +9710,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ43">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR43">
         <v>1.52</v>
@@ -9826,7 +9835,7 @@
         <v>91</v>
       </c>
       <c r="P44" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10032,7 +10041,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q45">
         <v>3.2</v>
@@ -10110,7 +10119,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ45">
         <v>0.25</v>
@@ -10238,7 +10247,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q46">
         <v>4</v>
@@ -10316,7 +10325,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>1.75</v>
@@ -10856,7 +10865,7 @@
         <v>90</v>
       </c>
       <c r="P49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -10937,7 +10946,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ49">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR49">
         <v>1.21</v>
@@ -11062,7 +11071,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q50">
         <v>2.55</v>
@@ -11268,7 +11277,7 @@
         <v>90</v>
       </c>
       <c r="P51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q51">
         <v>2.05</v>
@@ -11474,7 +11483,7 @@
         <v>122</v>
       </c>
       <c r="P52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12298,7 +12307,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q56">
         <v>4</v>
@@ -12504,7 +12513,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12710,7 +12719,7 @@
         <v>127</v>
       </c>
       <c r="P58" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q58">
         <v>3.25</v>
@@ -13122,7 +13131,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q60">
         <v>3.75</v>
@@ -13409,7 +13418,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ61">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR61">
         <v>1.33</v>
@@ -13534,7 +13543,7 @@
         <v>127</v>
       </c>
       <c r="P62" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q62">
         <v>3.5</v>
@@ -13612,7 +13621,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ62">
         <v>1.75</v>
@@ -13740,7 +13749,7 @@
         <v>90</v>
       </c>
       <c r="P63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q63">
         <v>6</v>
@@ -13818,10 +13827,10 @@
         <v>1.25</v>
       </c>
       <c r="AP63">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ63">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR63">
         <v>1.67</v>
@@ -13946,7 +13955,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14152,7 +14161,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q65">
         <v>3.3</v>
@@ -14358,7 +14367,7 @@
         <v>132</v>
       </c>
       <c r="P66" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q66">
         <v>3.5</v>
@@ -14770,7 +14779,7 @@
         <v>90</v>
       </c>
       <c r="P68" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q68">
         <v>3.75</v>
@@ -14976,7 +14985,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15182,7 +15191,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15388,7 +15397,7 @@
         <v>90</v>
       </c>
       <c r="P71" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q71">
         <v>1.91</v>
@@ -15957,6 +15966,418 @@
       </c>
       <c r="BP73">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:68">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>7821511</v>
+      </c>
+      <c r="C74" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="2">
+        <v>45752.5625</v>
+      </c>
+      <c r="F74">
+        <v>10</v>
+      </c>
+      <c r="G74" t="s">
+        <v>82</v>
+      </c>
+      <c r="H74" t="s">
+        <v>83</v>
+      </c>
+      <c r="I74">
+        <v>3</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74">
+        <v>4</v>
+      </c>
+      <c r="L74">
+        <v>4</v>
+      </c>
+      <c r="M74">
+        <v>1</v>
+      </c>
+      <c r="N74">
+        <v>5</v>
+      </c>
+      <c r="O74" t="s">
+        <v>137</v>
+      </c>
+      <c r="P74" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q74">
+        <v>3</v>
+      </c>
+      <c r="R74">
+        <v>2</v>
+      </c>
+      <c r="S74">
+        <v>4</v>
+      </c>
+      <c r="T74">
+        <v>1.5</v>
+      </c>
+      <c r="U74">
+        <v>2.5</v>
+      </c>
+      <c r="V74">
+        <v>3.4</v>
+      </c>
+      <c r="W74">
+        <v>1.3</v>
+      </c>
+      <c r="X74">
+        <v>10</v>
+      </c>
+      <c r="Y74">
+        <v>1.06</v>
+      </c>
+      <c r="Z74">
+        <v>2.15</v>
+      </c>
+      <c r="AA74">
+        <v>3.33</v>
+      </c>
+      <c r="AB74">
+        <v>3.28</v>
+      </c>
+      <c r="AC74">
+        <v>1.03</v>
+      </c>
+      <c r="AD74">
+        <v>7.6</v>
+      </c>
+      <c r="AE74">
+        <v>1.36</v>
+      </c>
+      <c r="AF74">
+        <v>2.7</v>
+      </c>
+      <c r="AG74">
+        <v>2.25</v>
+      </c>
+      <c r="AH74">
+        <v>1.53</v>
+      </c>
+      <c r="AI74">
+        <v>2</v>
+      </c>
+      <c r="AJ74">
+        <v>1.73</v>
+      </c>
+      <c r="AK74">
+        <v>1.33</v>
+      </c>
+      <c r="AL74">
+        <v>1.31</v>
+      </c>
+      <c r="AM74">
+        <v>1.78</v>
+      </c>
+      <c r="AN74">
+        <v>1.75</v>
+      </c>
+      <c r="AO74">
+        <v>1.6</v>
+      </c>
+      <c r="AP74">
+        <v>2</v>
+      </c>
+      <c r="AQ74">
+        <v>1.33</v>
+      </c>
+      <c r="AR74">
+        <v>1.52</v>
+      </c>
+      <c r="AS74">
+        <v>1.28</v>
+      </c>
+      <c r="AT74">
+        <v>2.8</v>
+      </c>
+      <c r="AU74">
+        <v>6</v>
+      </c>
+      <c r="AV74">
+        <v>4</v>
+      </c>
+      <c r="AW74">
+        <v>4</v>
+      </c>
+      <c r="AX74">
+        <v>3</v>
+      </c>
+      <c r="AY74">
+        <v>10</v>
+      </c>
+      <c r="AZ74">
+        <v>7</v>
+      </c>
+      <c r="BA74">
+        <v>3</v>
+      </c>
+      <c r="BB74">
+        <v>5</v>
+      </c>
+      <c r="BC74">
+        <v>8</v>
+      </c>
+      <c r="BD74">
+        <v>1.98</v>
+      </c>
+      <c r="BE74">
+        <v>6.1</v>
+      </c>
+      <c r="BF74">
+        <v>2.23</v>
+      </c>
+      <c r="BG74">
+        <v>1.38</v>
+      </c>
+      <c r="BH74">
+        <v>2.62</v>
+      </c>
+      <c r="BI74">
+        <v>1.78</v>
+      </c>
+      <c r="BJ74">
+        <v>2.01</v>
+      </c>
+      <c r="BK74">
+        <v>2.26</v>
+      </c>
+      <c r="BL74">
+        <v>1.62</v>
+      </c>
+      <c r="BM74">
+        <v>2.92</v>
+      </c>
+      <c r="BN74">
+        <v>1.31</v>
+      </c>
+      <c r="BO74">
+        <v>0</v>
+      </c>
+      <c r="BP74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:68">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>7821509</v>
+      </c>
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="2">
+        <v>45752.66666666666</v>
+      </c>
+      <c r="F75">
+        <v>10</v>
+      </c>
+      <c r="G75" t="s">
+        <v>72</v>
+      </c>
+      <c r="H75" t="s">
+        <v>85</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75" t="s">
+        <v>90</v>
+      </c>
+      <c r="P75" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q75">
+        <v>3.3</v>
+      </c>
+      <c r="R75">
+        <v>1.88</v>
+      </c>
+      <c r="S75">
+        <v>3.4</v>
+      </c>
+      <c r="T75">
+        <v>1.53</v>
+      </c>
+      <c r="U75">
+        <v>2.3</v>
+      </c>
+      <c r="V75">
+        <v>3.5</v>
+      </c>
+      <c r="W75">
+        <v>1.25</v>
+      </c>
+      <c r="X75">
+        <v>10.5</v>
+      </c>
+      <c r="Y75">
+        <v>1.04</v>
+      </c>
+      <c r="Z75">
+        <v>3.81</v>
+      </c>
+      <c r="AA75">
+        <v>3.72</v>
+      </c>
+      <c r="AB75">
+        <v>1.85</v>
+      </c>
+      <c r="AC75">
+        <v>1.1</v>
+      </c>
+      <c r="AD75">
+        <v>6.25</v>
+      </c>
+      <c r="AE75">
+        <v>1.49</v>
+      </c>
+      <c r="AF75">
+        <v>2.45</v>
+      </c>
+      <c r="AG75">
+        <v>2.2</v>
+      </c>
+      <c r="AH75">
+        <v>1.55</v>
+      </c>
+      <c r="AI75">
+        <v>2.1</v>
+      </c>
+      <c r="AJ75">
+        <v>1.65</v>
+      </c>
+      <c r="AK75">
+        <v>1.42</v>
+      </c>
+      <c r="AL75">
+        <v>1.36</v>
+      </c>
+      <c r="AM75">
+        <v>1.46</v>
+      </c>
+      <c r="AN75">
+        <v>1</v>
+      </c>
+      <c r="AO75">
+        <v>1.6</v>
+      </c>
+      <c r="AP75">
+        <v>0.83</v>
+      </c>
+      <c r="AQ75">
+        <v>1.83</v>
+      </c>
+      <c r="AR75">
+        <v>1.4</v>
+      </c>
+      <c r="AS75">
+        <v>1.35</v>
+      </c>
+      <c r="AT75">
+        <v>2.75</v>
+      </c>
+      <c r="AU75">
+        <v>4</v>
+      </c>
+      <c r="AV75">
+        <v>8</v>
+      </c>
+      <c r="AW75">
+        <v>2</v>
+      </c>
+      <c r="AX75">
+        <v>5</v>
+      </c>
+      <c r="AY75">
+        <v>6</v>
+      </c>
+      <c r="AZ75">
+        <v>13</v>
+      </c>
+      <c r="BA75">
+        <v>2</v>
+      </c>
+      <c r="BB75">
+        <v>5</v>
+      </c>
+      <c r="BC75">
+        <v>7</v>
+      </c>
+      <c r="BD75">
+        <v>2</v>
+      </c>
+      <c r="BE75">
+        <v>7.5</v>
+      </c>
+      <c r="BF75">
+        <v>2.1</v>
+      </c>
+      <c r="BG75">
+        <v>1.43</v>
+      </c>
+      <c r="BH75">
+        <v>2.63</v>
+      </c>
+      <c r="BI75">
+        <v>1.77</v>
+      </c>
+      <c r="BJ75">
+        <v>1.95</v>
+      </c>
+      <c r="BK75">
+        <v>2.22</v>
+      </c>
+      <c r="BL75">
+        <v>1.62</v>
+      </c>
+      <c r="BM75">
+        <v>2.85</v>
+      </c>
+      <c r="BN75">
+        <v>1.37</v>
+      </c>
+      <c r="BO75">
+        <v>3.9</v>
+      </c>
+      <c r="BP75">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="184">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -927,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP75"/>
+  <dimension ref="A1:BP77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2500,7 +2500,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ8">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
         <v>0.4</v>
@@ -2912,7 +2912,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ10">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR10">
         <v>1.56</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ11">
         <v>0.25</v>
@@ -4557,7 +4557,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18">
         <v>2.2</v>
@@ -5384,7 +5384,7 @@
         <v>2</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR22">
         <v>1.38</v>
@@ -7032,7 +7032,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ30">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR30">
         <v>1.6</v>
@@ -7441,7 +7441,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ32">
         <v>1.75</v>
@@ -8265,7 +8265,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
         <v>2</v>
@@ -8886,7 +8886,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ39">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR39">
         <v>1.68</v>
@@ -9707,7 +9707,7 @@
         <v>1.67</v>
       </c>
       <c r="AP43">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ43">
         <v>1.83</v>
@@ -9916,7 +9916,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR44">
         <v>1.35</v>
@@ -11564,7 +11564,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ52">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR52">
         <v>1.22</v>
@@ -12385,7 +12385,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
         <v>0.75</v>
@@ -13415,7 +13415,7 @@
         <v>1.25</v>
       </c>
       <c r="AP61">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ61">
         <v>1.33</v>
@@ -14036,7 +14036,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ64">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR64">
         <v>1.22</v>
@@ -14860,7 +14860,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ68">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR68">
         <v>1.34</v>
@@ -15681,7 +15681,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ72">
         <v>0.25</v>
@@ -15982,7 +15982,7 @@
         <v>69</v>
       </c>
       <c r="E74" s="2">
-        <v>45752.5625</v>
+        <v>45752.54166666666</v>
       </c>
       <c r="F74">
         <v>10</v>
@@ -16378,6 +16378,418 @@
       </c>
       <c r="BP75">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:68">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>7821513</v>
+      </c>
+      <c r="C76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="2">
+        <v>45752.77083333334</v>
+      </c>
+      <c r="F76">
+        <v>10</v>
+      </c>
+      <c r="G76" t="s">
+        <v>78</v>
+      </c>
+      <c r="H76" t="s">
+        <v>80</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="O76" t="s">
+        <v>90</v>
+      </c>
+      <c r="P76" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q76">
+        <v>3.4</v>
+      </c>
+      <c r="R76">
+        <v>1.83</v>
+      </c>
+      <c r="S76">
+        <v>4</v>
+      </c>
+      <c r="T76">
+        <v>1.62</v>
+      </c>
+      <c r="U76">
+        <v>2.2</v>
+      </c>
+      <c r="V76">
+        <v>4</v>
+      </c>
+      <c r="W76">
+        <v>1.22</v>
+      </c>
+      <c r="X76">
+        <v>13</v>
+      </c>
+      <c r="Y76">
+        <v>1.04</v>
+      </c>
+      <c r="Z76">
+        <v>2.63</v>
+      </c>
+      <c r="AA76">
+        <v>2.95</v>
+      </c>
+      <c r="AB76">
+        <v>2.85</v>
+      </c>
+      <c r="AC76">
+        <v>1.12</v>
+      </c>
+      <c r="AD76">
+        <v>6.35</v>
+      </c>
+      <c r="AE76">
+        <v>1.53</v>
+      </c>
+      <c r="AF76">
+        <v>2.2</v>
+      </c>
+      <c r="AG76">
+        <v>2.69</v>
+      </c>
+      <c r="AH76">
+        <v>1.41</v>
+      </c>
+      <c r="AI76">
+        <v>2.38</v>
+      </c>
+      <c r="AJ76">
+        <v>1.53</v>
+      </c>
+      <c r="AK76">
+        <v>1.34</v>
+      </c>
+      <c r="AL76">
+        <v>1.4</v>
+      </c>
+      <c r="AM76">
+        <v>1.6</v>
+      </c>
+      <c r="AN76">
+        <v>1.5</v>
+      </c>
+      <c r="AO76">
+        <v>2</v>
+      </c>
+      <c r="AP76">
+        <v>1.2</v>
+      </c>
+      <c r="AQ76">
+        <v>2.17</v>
+      </c>
+      <c r="AR76">
+        <v>1.38</v>
+      </c>
+      <c r="AS76">
+        <v>1.44</v>
+      </c>
+      <c r="AT76">
+        <v>2.82</v>
+      </c>
+      <c r="AU76">
+        <v>3</v>
+      </c>
+      <c r="AV76">
+        <v>3</v>
+      </c>
+      <c r="AW76">
+        <v>5</v>
+      </c>
+      <c r="AX76">
+        <v>14</v>
+      </c>
+      <c r="AY76">
+        <v>8</v>
+      </c>
+      <c r="AZ76">
+        <v>17</v>
+      </c>
+      <c r="BA76">
+        <v>6</v>
+      </c>
+      <c r="BB76">
+        <v>3</v>
+      </c>
+      <c r="BC76">
+        <v>9</v>
+      </c>
+      <c r="BD76">
+        <v>1.92</v>
+      </c>
+      <c r="BE76">
+        <v>6.15</v>
+      </c>
+      <c r="BF76">
+        <v>2.3</v>
+      </c>
+      <c r="BG76">
+        <v>1.31</v>
+      </c>
+      <c r="BH76">
+        <v>2.92</v>
+      </c>
+      <c r="BI76">
+        <v>1.66</v>
+      </c>
+      <c r="BJ76">
+        <v>2.18</v>
+      </c>
+      <c r="BK76">
+        <v>2.08</v>
+      </c>
+      <c r="BL76">
+        <v>1.72</v>
+      </c>
+      <c r="BM76">
+        <v>2.66</v>
+      </c>
+      <c r="BN76">
+        <v>1.37</v>
+      </c>
+      <c r="BO76">
+        <v>3.72</v>
+      </c>
+      <c r="BP76">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:68">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>7821506</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F77">
+        <v>10</v>
+      </c>
+      <c r="G77" t="s">
+        <v>77</v>
+      </c>
+      <c r="H77" t="s">
+        <v>73</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77" t="s">
+        <v>90</v>
+      </c>
+      <c r="P77" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q77">
+        <v>3.25</v>
+      </c>
+      <c r="R77">
+        <v>1.91</v>
+      </c>
+      <c r="S77">
+        <v>4</v>
+      </c>
+      <c r="T77">
+        <v>1.62</v>
+      </c>
+      <c r="U77">
+        <v>2.2</v>
+      </c>
+      <c r="V77">
+        <v>4</v>
+      </c>
+      <c r="W77">
+        <v>1.22</v>
+      </c>
+      <c r="X77">
+        <v>13</v>
+      </c>
+      <c r="Y77">
+        <v>1.04</v>
+      </c>
+      <c r="Z77">
+        <v>2.37</v>
+      </c>
+      <c r="AA77">
+        <v>2.88</v>
+      </c>
+      <c r="AB77">
+        <v>3.33</v>
+      </c>
+      <c r="AC77">
+        <v>1.04</v>
+      </c>
+      <c r="AD77">
+        <v>6.75</v>
+      </c>
+      <c r="AE77">
+        <v>1.53</v>
+      </c>
+      <c r="AF77">
+        <v>2.3</v>
+      </c>
+      <c r="AG77">
+        <v>2.3</v>
+      </c>
+      <c r="AH77">
+        <v>1.5</v>
+      </c>
+      <c r="AI77">
+        <v>2.25</v>
+      </c>
+      <c r="AJ77">
+        <v>1.57</v>
+      </c>
+      <c r="AK77">
+        <v>1.3</v>
+      </c>
+      <c r="AL77">
+        <v>1.34</v>
+      </c>
+      <c r="AM77">
+        <v>1.55</v>
+      </c>
+      <c r="AN77">
+        <v>1.6</v>
+      </c>
+      <c r="AO77">
+        <v>0.75</v>
+      </c>
+      <c r="AP77">
+        <v>1.5</v>
+      </c>
+      <c r="AQ77">
+        <v>0.8</v>
+      </c>
+      <c r="AR77">
+        <v>1.08</v>
+      </c>
+      <c r="AS77">
+        <v>1.32</v>
+      </c>
+      <c r="AT77">
+        <v>2.4</v>
+      </c>
+      <c r="AU77">
+        <v>2</v>
+      </c>
+      <c r="AV77">
+        <v>4</v>
+      </c>
+      <c r="AW77">
+        <v>5</v>
+      </c>
+      <c r="AX77">
+        <v>7</v>
+      </c>
+      <c r="AY77">
+        <v>7</v>
+      </c>
+      <c r="AZ77">
+        <v>11</v>
+      </c>
+      <c r="BA77">
+        <v>3</v>
+      </c>
+      <c r="BB77">
+        <v>8</v>
+      </c>
+      <c r="BC77">
+        <v>11</v>
+      </c>
+      <c r="BD77">
+        <v>1.75</v>
+      </c>
+      <c r="BE77">
+        <v>6.1</v>
+      </c>
+      <c r="BF77">
+        <v>2.33</v>
+      </c>
+      <c r="BG77">
+        <v>1.54</v>
+      </c>
+      <c r="BH77">
+        <v>2.3</v>
+      </c>
+      <c r="BI77">
+        <v>1.92</v>
+      </c>
+      <c r="BJ77">
+        <v>1.78</v>
+      </c>
+      <c r="BK77">
+        <v>2.43</v>
+      </c>
+      <c r="BL77">
+        <v>1.48</v>
+      </c>
+      <c r="BM77">
+        <v>3.2</v>
+      </c>
+      <c r="BN77">
+        <v>1.28</v>
+      </c>
+      <c r="BO77">
+        <v>4.35</v>
+      </c>
+      <c r="BP77">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="186">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -566,6 +566,12 @@
   </si>
   <si>
     <t>['27']</t>
+  </si>
+  <si>
+    <t>['7', '31', '63', '75']</t>
+  </si>
+  <si>
+    <t>['38']</t>
   </si>
 </sst>
 </file>
@@ -927,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP77"/>
+  <dimension ref="A1:BP81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1261,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
         <v>2</v>
@@ -2085,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ6">
         <v>2.2</v>
@@ -2294,7 +2300,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ7">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2497,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ8">
         <v>2.17</v>
@@ -2706,7 +2712,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2909,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
         <v>0.8</v>
@@ -3321,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ12">
         <v>0.75</v>
@@ -3736,7 +3742,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ14">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4148,7 +4154,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4763,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ19">
         <v>2.2</v>
@@ -5590,7 +5596,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR23">
         <v>1.13</v>
@@ -5793,7 +5799,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ24">
         <v>2</v>
@@ -6002,7 +6008,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ25">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR25">
         <v>0.8100000000000001</v>
@@ -6208,7 +6214,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ26">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AR26">
         <v>1.13</v>
@@ -6411,7 +6417,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ27">
         <v>1.25</v>
@@ -6620,7 +6626,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR28">
         <v>1.09</v>
@@ -6823,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>0.75</v>
@@ -7444,7 +7450,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ32">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR32">
         <v>1.03</v>
@@ -8474,7 +8480,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ37">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR37">
         <v>1.46</v>
@@ -9089,7 +9095,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ40">
         <v>0.75</v>
@@ -9295,7 +9301,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ41">
         <v>1.25</v>
@@ -9501,10 +9507,10 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>1.5</v>
@@ -9913,7 +9919,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ44">
         <v>0.8</v>
@@ -10328,7 +10334,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR46">
         <v>1.72</v>
@@ -10534,7 +10540,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR47">
         <v>1.51</v>
@@ -10737,7 +10743,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48">
         <v>1.25</v>
@@ -12182,7 +12188,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ55">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
         <v>1.23</v>
@@ -12591,7 +12597,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ57">
         <v>0.75</v>
@@ -12797,10 +12803,10 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AR58">
         <v>1.92</v>
@@ -13006,7 +13012,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ59">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR59">
         <v>1.4</v>
@@ -13209,10 +13215,10 @@
         <v>2.25</v>
       </c>
       <c r="AP60">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ60">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -13624,7 +13630,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ62">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR62">
         <v>1.42</v>
@@ -14033,7 +14039,7 @@
         <v>0.67</v>
       </c>
       <c r="AP64">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ64">
         <v>0.8</v>
@@ -14239,7 +14245,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ65">
         <v>1.25</v>
@@ -16221,7 +16227,7 @@
         <v>90</v>
       </c>
       <c r="P75" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="Q75">
         <v>3.3</v>
@@ -16790,6 +16796,830 @@
       </c>
       <c r="BP77">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:68">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>7821512</v>
+      </c>
+      <c r="C78" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45753.60416666666</v>
+      </c>
+      <c r="F78">
+        <v>10</v>
+      </c>
+      <c r="G78" t="s">
+        <v>79</v>
+      </c>
+      <c r="H78" t="s">
+        <v>81</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78" t="s">
+        <v>90</v>
+      </c>
+      <c r="P78" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q78">
+        <v>2.25</v>
+      </c>
+      <c r="R78">
+        <v>2.15</v>
+      </c>
+      <c r="S78">
+        <v>4.75</v>
+      </c>
+      <c r="T78">
+        <v>1.37</v>
+      </c>
+      <c r="U78">
+        <v>2.85</v>
+      </c>
+      <c r="V78">
+        <v>2.65</v>
+      </c>
+      <c r="W78">
+        <v>1.42</v>
+      </c>
+      <c r="X78">
+        <v>6.75</v>
+      </c>
+      <c r="Y78">
+        <v>1.09</v>
+      </c>
+      <c r="Z78">
+        <v>1.68</v>
+      </c>
+      <c r="AA78">
+        <v>3.8</v>
+      </c>
+      <c r="AB78">
+        <v>4.7</v>
+      </c>
+      <c r="AC78">
+        <v>1.01</v>
+      </c>
+      <c r="AD78">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE78">
+        <v>1.22</v>
+      </c>
+      <c r="AF78">
+        <v>3.5</v>
+      </c>
+      <c r="AG78">
+        <v>1.87</v>
+      </c>
+      <c r="AH78">
+        <v>1.87</v>
+      </c>
+      <c r="AI78">
+        <v>1.82</v>
+      </c>
+      <c r="AJ78">
+        <v>1.85</v>
+      </c>
+      <c r="AK78">
+        <v>1.18</v>
+      </c>
+      <c r="AL78">
+        <v>1.23</v>
+      </c>
+      <c r="AM78">
+        <v>2.05</v>
+      </c>
+      <c r="AN78">
+        <v>2.5</v>
+      </c>
+      <c r="AO78">
+        <v>0.4</v>
+      </c>
+      <c r="AP78">
+        <v>2.2</v>
+      </c>
+      <c r="AQ78">
+        <v>0.5</v>
+      </c>
+      <c r="AR78">
+        <v>1.52</v>
+      </c>
+      <c r="AS78">
+        <v>1.18</v>
+      </c>
+      <c r="AT78">
+        <v>2.7</v>
+      </c>
+      <c r="AU78">
+        <v>2</v>
+      </c>
+      <c r="AV78">
+        <v>3</v>
+      </c>
+      <c r="AW78">
+        <v>5</v>
+      </c>
+      <c r="AX78">
+        <v>2</v>
+      </c>
+      <c r="AY78">
+        <v>7</v>
+      </c>
+      <c r="AZ78">
+        <v>5</v>
+      </c>
+      <c r="BA78">
+        <v>7</v>
+      </c>
+      <c r="BB78">
+        <v>4</v>
+      </c>
+      <c r="BC78">
+        <v>11</v>
+      </c>
+      <c r="BD78">
+        <v>1.58</v>
+      </c>
+      <c r="BE78">
+        <v>6.4</v>
+      </c>
+      <c r="BF78">
+        <v>2.63</v>
+      </c>
+      <c r="BG78">
+        <v>1.47</v>
+      </c>
+      <c r="BH78">
+        <v>2.48</v>
+      </c>
+      <c r="BI78">
+        <v>1.77</v>
+      </c>
+      <c r="BJ78">
+        <v>1.93</v>
+      </c>
+      <c r="BK78">
+        <v>2.23</v>
+      </c>
+      <c r="BL78">
+        <v>1.56</v>
+      </c>
+      <c r="BM78">
+        <v>2.9</v>
+      </c>
+      <c r="BN78">
+        <v>1.34</v>
+      </c>
+      <c r="BO78">
+        <v>3.9</v>
+      </c>
+      <c r="BP78">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="79" spans="1:68">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7821510</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45753.72916666666</v>
+      </c>
+      <c r="F79">
+        <v>10</v>
+      </c>
+      <c r="G79" t="s">
+        <v>70</v>
+      </c>
+      <c r="H79" t="s">
+        <v>84</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2</v>
+      </c>
+      <c r="K79">
+        <v>2</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>4</v>
+      </c>
+      <c r="N79">
+        <v>4</v>
+      </c>
+      <c r="O79" t="s">
+        <v>90</v>
+      </c>
+      <c r="P79" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q79">
+        <v>5</v>
+      </c>
+      <c r="R79">
+        <v>2.25</v>
+      </c>
+      <c r="S79">
+        <v>2.3</v>
+      </c>
+      <c r="T79">
+        <v>1.4</v>
+      </c>
+      <c r="U79">
+        <v>2.75</v>
+      </c>
+      <c r="V79">
+        <v>2.75</v>
+      </c>
+      <c r="W79">
+        <v>1.4</v>
+      </c>
+      <c r="X79">
+        <v>8</v>
+      </c>
+      <c r="Y79">
+        <v>1.08</v>
+      </c>
+      <c r="Z79">
+        <v>5.2</v>
+      </c>
+      <c r="AA79">
+        <v>3.97</v>
+      </c>
+      <c r="AB79">
+        <v>1.6</v>
+      </c>
+      <c r="AC79">
+        <v>0</v>
+      </c>
+      <c r="AD79">
+        <v>0</v>
+      </c>
+      <c r="AE79">
+        <v>0</v>
+      </c>
+      <c r="AF79">
+        <v>0</v>
+      </c>
+      <c r="AG79">
+        <v>1.85</v>
+      </c>
+      <c r="AH79">
+        <v>1.89</v>
+      </c>
+      <c r="AI79">
+        <v>1.8</v>
+      </c>
+      <c r="AJ79">
+        <v>1.91</v>
+      </c>
+      <c r="AK79">
+        <v>0</v>
+      </c>
+      <c r="AL79">
+        <v>0</v>
+      </c>
+      <c r="AM79">
+        <v>0</v>
+      </c>
+      <c r="AN79">
+        <v>1.8</v>
+      </c>
+      <c r="AO79">
+        <v>2</v>
+      </c>
+      <c r="AP79">
+        <v>1.5</v>
+      </c>
+      <c r="AQ79">
+        <v>2.17</v>
+      </c>
+      <c r="AR79">
+        <v>1.74</v>
+      </c>
+      <c r="AS79">
+        <v>1.7</v>
+      </c>
+      <c r="AT79">
+        <v>3.44</v>
+      </c>
+      <c r="AU79">
+        <v>3</v>
+      </c>
+      <c r="AV79">
+        <v>5</v>
+      </c>
+      <c r="AW79">
+        <v>9</v>
+      </c>
+      <c r="AX79">
+        <v>4</v>
+      </c>
+      <c r="AY79">
+        <v>12</v>
+      </c>
+      <c r="AZ79">
+        <v>9</v>
+      </c>
+      <c r="BA79">
+        <v>7</v>
+      </c>
+      <c r="BB79">
+        <v>1</v>
+      </c>
+      <c r="BC79">
+        <v>8</v>
+      </c>
+      <c r="BD79">
+        <v>0</v>
+      </c>
+      <c r="BE79">
+        <v>0</v>
+      </c>
+      <c r="BF79">
+        <v>0</v>
+      </c>
+      <c r="BG79">
+        <v>0</v>
+      </c>
+      <c r="BH79">
+        <v>0</v>
+      </c>
+      <c r="BI79">
+        <v>0</v>
+      </c>
+      <c r="BJ79">
+        <v>0</v>
+      </c>
+      <c r="BK79">
+        <v>0</v>
+      </c>
+      <c r="BL79">
+        <v>0</v>
+      </c>
+      <c r="BM79">
+        <v>0</v>
+      </c>
+      <c r="BN79">
+        <v>0</v>
+      </c>
+      <c r="BO79">
+        <v>0</v>
+      </c>
+      <c r="BP79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7821508</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45753.83333333334</v>
+      </c>
+      <c r="F80">
+        <v>10</v>
+      </c>
+      <c r="G80" t="s">
+        <v>74</v>
+      </c>
+      <c r="H80" t="s">
+        <v>75</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="K80">
+        <v>1</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>1</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
+      <c r="O80" t="s">
+        <v>90</v>
+      </c>
+      <c r="P80" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q80">
+        <v>3.75</v>
+      </c>
+      <c r="R80">
+        <v>2.1</v>
+      </c>
+      <c r="S80">
+        <v>3</v>
+      </c>
+      <c r="T80">
+        <v>1.4</v>
+      </c>
+      <c r="U80">
+        <v>2.75</v>
+      </c>
+      <c r="V80">
+        <v>3</v>
+      </c>
+      <c r="W80">
+        <v>1.36</v>
+      </c>
+      <c r="X80">
+        <v>9</v>
+      </c>
+      <c r="Y80">
+        <v>1.07</v>
+      </c>
+      <c r="Z80">
+        <v>3.29</v>
+      </c>
+      <c r="AA80">
+        <v>3.03</v>
+      </c>
+      <c r="AB80">
+        <v>2.29</v>
+      </c>
+      <c r="AC80">
+        <v>1.02</v>
+      </c>
+      <c r="AD80">
+        <v>7.8</v>
+      </c>
+      <c r="AE80">
+        <v>1.28</v>
+      </c>
+      <c r="AF80">
+        <v>3.05</v>
+      </c>
+      <c r="AG80">
+        <v>1.98</v>
+      </c>
+      <c r="AH80">
+        <v>1.77</v>
+      </c>
+      <c r="AI80">
+        <v>1.73</v>
+      </c>
+      <c r="AJ80">
+        <v>2</v>
+      </c>
+      <c r="AK80">
+        <v>1.61</v>
+      </c>
+      <c r="AL80">
+        <v>1.32</v>
+      </c>
+      <c r="AM80">
+        <v>1.34</v>
+      </c>
+      <c r="AN80">
+        <v>1</v>
+      </c>
+      <c r="AO80">
+        <v>0.5</v>
+      </c>
+      <c r="AP80">
+        <v>0.83</v>
+      </c>
+      <c r="AQ80">
+        <v>1</v>
+      </c>
+      <c r="AR80">
+        <v>1.3</v>
+      </c>
+      <c r="AS80">
+        <v>1.31</v>
+      </c>
+      <c r="AT80">
+        <v>2.61</v>
+      </c>
+      <c r="AU80">
+        <v>5</v>
+      </c>
+      <c r="AV80">
+        <v>7</v>
+      </c>
+      <c r="AW80">
+        <v>1</v>
+      </c>
+      <c r="AX80">
+        <v>3</v>
+      </c>
+      <c r="AY80">
+        <v>6</v>
+      </c>
+      <c r="AZ80">
+        <v>10</v>
+      </c>
+      <c r="BA80">
+        <v>3</v>
+      </c>
+      <c r="BB80">
+        <v>7</v>
+      </c>
+      <c r="BC80">
+        <v>10</v>
+      </c>
+      <c r="BD80">
+        <v>2.33</v>
+      </c>
+      <c r="BE80">
+        <v>6.4</v>
+      </c>
+      <c r="BF80">
+        <v>1.73</v>
+      </c>
+      <c r="BG80">
+        <v>1.41</v>
+      </c>
+      <c r="BH80">
+        <v>2.65</v>
+      </c>
+      <c r="BI80">
+        <v>1.68</v>
+      </c>
+      <c r="BJ80">
+        <v>2.02</v>
+      </c>
+      <c r="BK80">
+        <v>2.08</v>
+      </c>
+      <c r="BL80">
+        <v>1.65</v>
+      </c>
+      <c r="BM80">
+        <v>2.65</v>
+      </c>
+      <c r="BN80">
+        <v>1.4</v>
+      </c>
+      <c r="BO80">
+        <v>3.55</v>
+      </c>
+      <c r="BP80">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7821507</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45754.8125</v>
+      </c>
+      <c r="F81">
+        <v>10</v>
+      </c>
+      <c r="G81" t="s">
+        <v>76</v>
+      </c>
+      <c r="H81" t="s">
+        <v>71</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81" t="s">
+        <v>90</v>
+      </c>
+      <c r="P81" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q81">
+        <v>2.65</v>
+      </c>
+      <c r="R81">
+        <v>2</v>
+      </c>
+      <c r="S81">
+        <v>3.9</v>
+      </c>
+      <c r="T81">
+        <v>1.44</v>
+      </c>
+      <c r="U81">
+        <v>2.55</v>
+      </c>
+      <c r="V81">
+        <v>3.1</v>
+      </c>
+      <c r="W81">
+        <v>1.31</v>
+      </c>
+      <c r="X81">
+        <v>8.5</v>
+      </c>
+      <c r="Y81">
+        <v>1.06</v>
+      </c>
+      <c r="Z81">
+        <v>3.45</v>
+      </c>
+      <c r="AA81">
+        <v>3.35</v>
+      </c>
+      <c r="AB81">
+        <v>2.08</v>
+      </c>
+      <c r="AC81">
+        <v>1.07</v>
+      </c>
+      <c r="AD81">
+        <v>7.75</v>
+      </c>
+      <c r="AE81">
+        <v>1.39</v>
+      </c>
+      <c r="AF81">
+        <v>2.75</v>
+      </c>
+      <c r="AG81">
+        <v>1.98</v>
+      </c>
+      <c r="AH81">
+        <v>1.77</v>
+      </c>
+      <c r="AI81">
+        <v>1.98</v>
+      </c>
+      <c r="AJ81">
+        <v>1.73</v>
+      </c>
+      <c r="AK81">
+        <v>1.29</v>
+      </c>
+      <c r="AL81">
+        <v>1.3</v>
+      </c>
+      <c r="AM81">
+        <v>1.72</v>
+      </c>
+      <c r="AN81">
+        <v>1.2</v>
+      </c>
+      <c r="AO81">
+        <v>1.75</v>
+      </c>
+      <c r="AP81">
+        <v>1.17</v>
+      </c>
+      <c r="AQ81">
+        <v>1.6</v>
+      </c>
+      <c r="AR81">
+        <v>1.28</v>
+      </c>
+      <c r="AS81">
+        <v>1.64</v>
+      </c>
+      <c r="AT81">
+        <v>2.92</v>
+      </c>
+      <c r="AU81">
+        <v>2</v>
+      </c>
+      <c r="AV81">
+        <v>0</v>
+      </c>
+      <c r="AW81">
+        <v>6</v>
+      </c>
+      <c r="AX81">
+        <v>4</v>
+      </c>
+      <c r="AY81">
+        <v>8</v>
+      </c>
+      <c r="AZ81">
+        <v>4</v>
+      </c>
+      <c r="BA81">
+        <v>5</v>
+      </c>
+      <c r="BB81">
+        <v>5</v>
+      </c>
+      <c r="BC81">
+        <v>10</v>
+      </c>
+      <c r="BD81">
+        <v>1.91</v>
+      </c>
+      <c r="BE81">
+        <v>7.5</v>
+      </c>
+      <c r="BF81">
+        <v>2.2</v>
+      </c>
+      <c r="BG81">
+        <v>1.3</v>
+      </c>
+      <c r="BH81">
+        <v>3.05</v>
+      </c>
+      <c r="BI81">
+        <v>1.7</v>
+      </c>
+      <c r="BJ81">
+        <v>2.05</v>
+      </c>
+      <c r="BK81">
+        <v>1.89</v>
+      </c>
+      <c r="BL81">
+        <v>1.8</v>
+      </c>
+      <c r="BM81">
+        <v>2.35</v>
+      </c>
+      <c r="BN81">
+        <v>1.5</v>
+      </c>
+      <c r="BO81">
+        <v>3.05</v>
+      </c>
+      <c r="BP81">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="185">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -563,9 +563,6 @@
   </si>
   <si>
     <t>['43']</t>
-  </si>
-  <si>
-    <t>['27']</t>
   </si>
   <si>
     <t>['7', '31', '63', '75']</t>
@@ -16433,7 +16430,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17051,7 +17048,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q79">
         <v>5</v>
@@ -17257,7 +17254,7 @@
         <v>90</v>
       </c>
       <c r="P80" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q80">
         <v>3.75</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Uruguay Primera División_2025.xlsx
@@ -17427,7 +17427,7 @@
         <v>69</v>
       </c>
       <c r="E81" s="2">
-        <v>45754.8125</v>
+        <v>45754.66666666666</v>
       </c>
       <c r="F81">
         <v>10</v>
